--- a/docs/examples/demo-control-2_FERG.xlsx
+++ b/docs/examples/demo-control-2_FERG.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C440"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -517,7 +517,7 @@
         <v>[R_01_闪光]</v>
       </c>
       <c r="C11" t="str">
-        <v>白色光: 0.01 cd·s/m²</v>
+        <v>b白色光:0.01cd.m-2,5ms</v>
       </c>
     </row>
     <row r="12">
@@ -528,7 +528,7 @@
         <v>[R_01_闪光背景]</v>
       </c>
       <c r="C12" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="13">
@@ -539,7 +539,7 @@
         <v>[R_01_采样]</v>
       </c>
       <c r="C13" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="14">
@@ -550,7 +550,7 @@
         <v>[R_01_分析时间]</v>
       </c>
       <c r="C14" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="15">
@@ -572,7 +572,7 @@
         <v>[R_01_详细数据(uv)]</v>
       </c>
       <c r="C16" t="str">
-        <v>2.39,-2.89,1.1,1.55,-2.98,2.05,0.5,-2.66,2.71,-0.62,-1.96,2.99,-1.66,-0.99,2.85,-2.46,0.12,2.31,-2.92,1.22,1.45,-2.97,2.14,0.38,-2.6,2.76,-0.75,-1.87,2.99,-1.77,-0.88,2.8,-2.55,0.22,2.2,-2.98,1.28,1.28,-3.02,2.14,0.15,-2.67,2.65,-1.05,-2,2.72,-2.19,-1.15,2.31,-3.14,-0.28,1.39,-3.86,0.4,0.02,-4.33,0.67,-1.75,-4.64,0.36,-3.83,-4.93,-0.71,-6.16,-5.4,-2.65,-8.7,-6.3,-5.53,-11.45,-7.88,-9.34,-14.46,-10.38,-14.02,-17.79,-13.95,-19.46,-21.54,-18.67,-25.45,-25.75,-24.46,-31.78,-30.45,-31.12,-38.14,-35.56,-38.28,-44.19,-40.9,-45.44,-49.56,-46.15,-52,-53.85,-50.88,-57.28,-56.66,-54.58,-60.63,-57.6,-56.64,-61.43,-56.3,-56.48,-59.17,-52.49,-53.55,-53.52,-45.93,-47.42,-44.32,-36.51,-37.8,-31.61,-24.18,-24.57,-15.6,-9.01,-7.81,3.34,8.86,12.22,24.75,29.24,35.11,48.14,51.87,60.36,73.01,76.44,87.38,98.92,102.62,115.56,125.47,130.06,144.32,152.37,158.37,173.12,179.37,187.12,201.49,206.26,215.87,229.04,232.83,244.15,255.43,258.88,271.44,280.4,284.13,297.27,303.7,308.24,321.15,325.15,330.83,342.62,344.54,351.43,361.29,361.66,369.57,376.85,376.31,384.78,389.06,388.25,396.61,397.78,397.25,404.72,402.95,403.08,408.86,404.61,405.54,408.93,402.86,404.46,404.96,397.84,399.76,397.13,389.74,391.47,385.76,378.79,379.69,371.27,365.24,364.66,354.17,349.32,346.73,334.99,331.33,326.37,314.28,311.54,304.12,292.56,290.28,280.58,270.28,267.9,256.36,247.85,244.77,232.07,225.6,221.29,208.26,203.78,197.88,185.4,182.57,174.98,163.84,162.14,152.98,143.84,142.6,132.27,125.53,124.05,113.15,108.92,106.6,95.87,93.96,90.37,80.56,80.52,75.45,67.26,68.44,61.97,55.92,57.55,50.01,46.4,47.72,39.63,38.48,38.81,30.87,31.89,30.78,23.69,26.35,23.58,18,21.59,17.23,13.63,17.36,11.76,10.38,13.49,7.19,8.01,9.84,3.53,6.24,6.37,0.77,4.83,3.08,-1.18,3.54,0.02,-2.41,2.17,-2.72,-3.09,0.61,-5.07,-3.42,-1.19,-6.95,-3.6,-3.24,-8.34,-3.82,-5.46,-9.26,-4.27,-7.74,-9.77,-5.08,-9.95,-9.98,-6.32,-11.97,-10.06,-7.99,-13.69,-10.17,-10.05,-15.06,-10.49,-12.39,-16.07,-11.15,-14.87,-16.78,-12.26,-17.35,-17.27,-13.87,-19.68,-17.7,-15.96,-21.75,-18.22,-18.46,-23.49,-18.99,-21.24,-24.9,-20.13,-24.17,-26.01,-21.73,-27.08,-26.93,-23.82,-29.82,-27.79,-26.38,-32.27,-28.74,-29.33,-34.37,-29.93,-32.51,-36.11,-31.47,-35.79,-37.53,-33.45,-39,-38.73,-35.87,-41.97,-39.84,-38.71,-44.6,-41,-41.86,-46.82,-42.36,-45.18,-48.61,-44.02,-48.52,-50.03,-46.05,-51.69,-51.18,-48.46,-54.54,-52.18,-51.2,-56.96,-53.17,-54.17,-58.9,-54.29,-57.21,-60.33,-55.65,-60.16,-61.32,-57.3,-62.86,-61.97,-59.25,-65.14,-62.41,-61.44,-66.92,-62.78,-63.77,-68.12,-63.23,-66.09,-68.76,-63.85,-68.24,-68.9,-64.7,-70.04,-68.65,-65.8,-71.37,-68.15,-67.07,-72.13,-67.55,-68.42,-72.28,-67,-69.71,-71.83,-66.61,-70.78,-70.86,-66.43,-71.48,-69.51,-66.47,-71.67,-67.91,-66.68,-71.28,-66.24,-66.96,-70.29,-64.63,-67.17,-68.73,-63.21,-67.17,-66.68,-62.04,-66.81,-64.3,-61.12,-65.97,-61.73,-60.4,-64.6,-59.15,-59.79,-62.67,-56.71,-59.16,-60.24,-54.53,-58.36,-57.4,-52.66,-57.25,-54.31,-51.11,-55.73,-51.13,-49.84,-53.74,-48.04,-48.73,-51.28,-45.17,-47.66,-48.4,-42.65,-46.49,-45.22,-40.53,-45.07,-41.87,-38.8,-43.32,-38.53,-37.41,-41.17,-35.36,-36.25,-38.62,-32.52,-35.19,-35.73,-30.09,-34.07,-32.61,-28.12,-32.76,-29.42,-26.61,-31.15,-26.3,-25.49,-29.21,-23.43,-24.62,-26.91,-20.93,-23.88,-24.33,-18.9,-23.11,-21.57,-17.38,-22.17</v>
+        <v>-7.45,-20.55,-11.19,-11.19,-21.3,-8.72,-15.91,-19.71,-8.18,-20.22,-16.5,-9.95,-22.85,-12.9,-13.58,-23.05,-10.26,-17.97,-20.88,-9.56,-21.75,-17.12,-11.1,-23.68,-13.09,-14.38,-23.12,-10.11,-18.27,-20.23,-9.14,-21.41,-15.9,-10.42,-22.64,-11.47,-13.39,-21.41,-8.28,-16.91,-17.99,-7.24,-19.62,-13.34,-8.52,-20.44,-8.83,-11.51,-18.91,-5.81,-15.03,-15.36,-5.13,-17.76,-10.89,-6.87,-18.66,-6.89,-10.43,-17.43,-4.47,-14.58,-14.32,-4.99,-17.88,-10.55,-7.86,-19.74,-7.8,-12.48,-19.78,-7.67,-18.26,-17.89,-10.13,-23.02,-16.51,-13.82,-26.04,-16.85,-22.47,-30.48,-19.4,-32.34,-31.27,-20.85,-36.55,-28.09,-28.93,-46.85,-36.25,-45.1,-50.96,-38.96,-47.44,-47.18,-45.26,-55.18,-54.55,-51.74,-73.77,-57.99,-59.05,-68.13,-69.92,-72.17,-70.05,-68.18,-87.87,-65.75,-74.28,-87.8,-68.8,-67.66,-64.6,-56.02,-76.37,-56.95,-44.42,-70.82,-40.74,-50.21,-59.72,-43.17,-34.86,-43.09,-27.96,-24.55,-7.81,-13.18,-19.61,8.41,10.46,17.34,39.01,41.34,44.26,45.31,43.1,56.35,72.15,78.47,85.34,107.97,103.57,104.07,130.31,113.4,144.04,126.18,150.76,158.74,182.87,184.65,205.48,173.53,221.94,208.82,200.64,233,232.76,220.23,245.79,258.64,243.63,277.42,254.13,266.1,279.54,327.34,312.14,314.67,347.68,360.09,278.51,297.53,309.33,309.96,314.53,312.84,331.48,307.29,375.07,388.62,352.27,333.58,365.94,306.05,370.67,317.96,355.77,343.31,320.57,360.57,305.56,347.76,273.96,301.69,328.14,304.81,319.68,276.9,270.85,302.73,238.48,298.45,249.72,223.16,270.3,228.44,234.47,260.32,244.37,215,229.75,217.8,198.68,202.2,172.82,182.89,181.94,164.08,177.96,131.4,149.83,141.83,118.79,135.51,125.06,95.97,109.52,102.39,82.57,95.14,73.93,75.39,69.49,66.19,65.9,57.11,44.11,58.48,42.4,33,40.47,32.08,30.22,38.37,16.38,24.2,19.89,13.27,25.17,13.44,5.76,17.33,-0.39,5.22,8.08,-4.25,5.83,1.51,-8.6,3.46,-8.69,-9.43,-1.84,-14.74,-10.45,-6.44,-19.24,-7.82,-14.05,-20.05,-9.42,-19.98,-19.21,-9.89,-23.38,-16.12,-14.86,-25.85,-15.01,-19.35,-26.13,-13.1,-24.8,-24.42,-15.63,-27.76,-20.65,-18.73,-30.48,-18.75,-22.37,-27.24,-15.76,-28.8,-27.59,-19.2,-28.63,-24.14,-22.13,-32.32,-17.57,-26.26,-29.45,-19.67,-32.25,-29.26,-16.8,-29.8,-19.78,-24.16,-33.99,-22.62,-25.25,-29.58,-17.1,-29.17,-25.72,-22.75,-38.21,-22.26,-29.62,-34.13,-25.76,-31.99,-31.06,-24.03,-32.69,-34.07,-27.5,-44.96,-25.75,-27.39,-39.13,-27.48,-42.35,-43.77,-26.1,-47.73,-37.54,-40.39,-40.13,-41.4,-37.88,-44.38,-30.05,-51.17,-43.37,-35.2,-45.34,-55.99,-41.98,-53.02,-48.86,-52.23,-58.32,-54.77,-47.1,-55.3,-43.42,-56.2,-54.21,-42.54,-61.77,-46.22,-70.34,-75.82,-51.65,-58.04,-77.46,-52.75,-57.56,-69.73,-59.93,-81.85,-56.19,-56.72,-62.63,-58.13,-63.81,-81.1,-68.01,-74.94,-53.52,-77.69,-69.51,-62.22,-63.7,-64.8,-75.2,-78.02,-61.79,-58.61,-71.15,-78.7,-75.03,-89.15,-60.74,-66.13,-82.61,-58.19,-62.99,-69.69,-57.1,-93.76,-66,-54.97,-82.45,-66.4,-57.02,-67.33,-74.58,-76.09,-75.91,-59.09,-68.75,-83.65,-66.36,-85.26,-64,-86.81,-78.87,-58.77,-86.6,-63.13,-48.77,-64.3,-56.67,-77.82,-83.58,-72.12,-72.44,-63.81,-69.94,-69.14,-73.47,-48.22,-79.26,-78.15,-51.95,-77.88,-59.69,-78.91,-64.31,-73.72,-76.85,-75.7,-51.03,-77.38,-56.19,-76.24,-75.26,-48.46,-55.2,-67.2,-44.4,-76.64,-57.88,-59.04,-63.37,-57.2,-65.33,-68.61,-46.22,-56.51,-58.91,-55.57,-60.35,-63.09,-51.18,-65.77,-46.17,-43.95,-62.77,-46.1,-51.67,-43.51,-42.85,-61.38,-47.5,-45.69,-57.69,-42.59,-40.23,-50.65,-39.94,-48.34,-39.18,-27.01,-48.68,-32.78,-33.5,-41.32,-34.64,-33.1,-38.78,-30.78</v>
       </c>
     </row>
     <row r="17">
@@ -583,7 +583,7 @@
         <v>[R_01_标记]</v>
       </c>
       <c r="C17" t="str">
-        <v>a: 15.4ms -91.0uv b: 34.4ms 417.3uv</v>
+        <v>a: 15.5ms -45.4uv b: 34.8ms 164.6uv</v>
       </c>
     </row>
     <row r="18">
@@ -616,7 +616,7 @@
         <v>[L_01_闪光]</v>
       </c>
       <c r="C20" t="str">
-        <v>白色光: 0.01 cd·s/m²</v>
+        <v>b白色光:0.01cd.m-2,5ms</v>
       </c>
     </row>
     <row r="21">
@@ -627,7 +627,7 @@
         <v>[L_01_闪光背景]</v>
       </c>
       <c r="C21" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="22">
@@ -638,7 +638,7 @@
         <v>[L_01_采样]</v>
       </c>
       <c r="C22" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="23">
@@ -649,7 +649,7 @@
         <v>[L_01_分析时间]</v>
       </c>
       <c r="C23" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="24">
@@ -671,7 +671,7 @@
         <v>[L_01_详细数据(uv)]</v>
       </c>
       <c r="C25" t="str">
-        <v>1.57,-2.68,2.99,-2.41,1.12,0.5,-1.98,2.87,-2.91,2.08,-0.64,-0.99,2.33,-2.97,2.74,-1.69,0.14,1.45,-2.61,3,-2.5,1.25,0.36,-1.87,2.82,-2.94,2.18,-0.79,-0.86,2.22,-2.96,2.78,-1.83,0.26,1.29,-2.57,2.96,-2.63,1.31,0.13,-1.85,2.65,-3.11,2.1,-1.13,-0.97,1.83,-3.29,2.41,-2.44,-0.18,0.48,-3.3,2.02,-3.78,0.18,-1.46,-3.41,0.67,-5.32,-0.31,-4.11,-4.06,-1.92,-7.36,-2.16,-7.71,-5.81,-6.08,-10.33,-5.88,-12.54,-9.24,-12.06,-14.71,-11.83,-18.82,-14.81,-19.96,-20.79,-20.08,-26.57,-22.58,-29.46,-28.49,-30.18,-35.32,-32.01,-39.69,-37.1,-40.96,-44,-41.83,-49.12,-45.21,-50.57,-50.91,-50.03,-55.69,-50.8,-56.63,-53.98,-54.22,-57.11,-51.63,-56.74,-51.11,-52.06,-51.38,-45.7,-48.94,-40.73,-41.83,-37.24,-31.75,-32.2,-22.15,-22.78,-14.48,-9.5,-6.61,4.31,4.75,16.07,20.34,26.69,37.45,39.48,52.77,56.34,65.88,75.59,79.59,93.64,96.73,108.83,116.87,123.09,136.7,139.72,153.51,159.61,168.06,180.17,183.63,198.06,202.29,212.71,222.55,226.91,240.84,243.56,255.39,262.46,268.02,280.35,282.05,294.44,298.56,305.34,315.08,316.29,328.19,329.49,337.2,343.59,344.77,355.05,353.9,361.95,364.56,365.99,373.59,370.57,378.15,376.94,378.73,382.81,378.59,384.81,380.13,382.16,382.25,377.52,381.54,374.09,376.06,372.1,367.49,368.62,359.36,360.83,353.23,349.2,347.04,337.07,337.53,327.07,323.88,318.39,308.75,307.74,295.51,293.15,284.63,276.24,273.36,260.6,258.85,247.97,241.43,236.5,224.42,222.88,210.56,206.15,199.18,188.83,187.02,174.31,171.93,163.2,155.35,152.77,140.77,140.01,130.03,125.04,121.31,111,111.22,100.67,98.53,93.44,85.59,86.01,75.72,76.02,69.61,64.65,64.54,55.33,57.37,49.93,47.96,46.72,39.31,42.21,34.25,35,32.26,27.22,30.05,22.23,25.11,20.82,18.44,20.36,13.4,17.61,12,12.25,12.63,7.22,11.81,5.4,7.96,6.46,3.11,7.17,0.64,4.9,1.52,0.51,3.24,-2.65,2.52,-2.42,-1.11,-0.26,-4.79,0.38,-5.54,-2.22,-3.5,-6.14,-1.82,-7.96,-3.22,-6.54,-6.99,-4.25,-9.81,-4.42,-9.37,-7.66,-6.97,-11.21,-6.04,-11.97,-8.41,-9.94,-12.32,-8.18,-14.31,-9.48,-13.07,-13.31,-10.87,-16.37,-11.05,-16.25,-14.38,-14.06,-18.2,-13.22,-19.34,-15.71,-17.63,-19.87,-16.04,-22.27,-17.46,-21.42,-21.52,-19.46,-24.96,-19.77,-25.26,-23.28,-23.37,-27.44,-22.69,-29,-25.31,-27.63,-29.74,-26.22,-32.52,-27.74,-32.03,-31.97,-30.27,-35.74,-30.65,-36.38,-34.25,-34.71,-38.63,-34.07,-40.5,-36.7,-39.34,-41.25,-37.97,-44.25,-39.42,-43.96,-43.65,-42.22,-47.54,-42.47,-48.33,-45.95,-46.66,-50.33,-45.86,-52.27,-48.25,-51.09,-52.66,-49.51,-55.63,-50.64,-55.27,-54.59,-53.3,-58.32,-53.16,-58.99,-56.23,-57.06,-60.32,-55.8,-62.05,-57.68,-60.58,-61.66,-58.51,-64.32,-59.04,-63.63,-62.44,-61.16,-65.74,-60.36,-66.02,-62.77,-63.59,-66.31,-61.65,-67.6,-62.78,-65.61,-66.11,-62.86,-68.25,-62.6,-67.04,-65.25,-63.91,-67.96,-62.3,-67.71,-63.9,-64.65,-66.78,-61.93,-67.52,-62.22,-64.95,-64.83,-61.47,-66.4,-60.37,-64.65,-62.27,-60.86,-64.39,-58.47,-63.64,-59.31,-60.01,-61.58,-56.58,-61.85,-56.13,-58.8,-58.12,-54.72,-59.25,-52.94,-57.12,-54.23,-52.84,-55.93,-49.86,-54.87,-50.12,-50.89,-51.99,-46.97,-52.01,-46.01,-48.74,-47.62,-44.31,-48.56,-42.1,-46.31,-43.05,-41.83,-44.59,-38.52,-43.5,-38.48,-39.45,-40.22,-35.34,-40.29,-34.15,-37.07,-35.65,-32.57,-36.67,-30.22,-34.57,-31.08,-30.16,-32.72,-26.8,-31.87,-26.72,-28,-28.57,-23.95,-28.9,-22.76,-25.97,-24.37,-21.64,-25.68,-19.34,-23.93,-20.32,-19.78,-22.24,-16.55,-21.78,-16.59</v>
+        <v>-5.71,2.03,0.21,-6,2.2,-1.16,-6.14,2.24,-2.54,-6.12,2.14,-3.89,-5.93,1.92,-5.15,-5.58,1.58,-6.27,-5.08,1.15,-7.21,-4.43,0.64,-7.94,-3.67,0.06,-8.42,-2.82,-0.55,-8.65,-1.91,-1.19,-8.61,-0.97,-1.82,-8.31,-0.04,-2.44,-7.76,0.85,-3.01,-6.98,1.65,-3.53,-6.02,2.35,-3.98,-4.89,2.9,-4.36,-3.66,3.28,-4.64,-2.37,3.47,-4.85,-1.08,3.46,-4.96,0.16,3.22,-5,1.28,2.78,-5.01,2.2,2.07,-4.95,2.88,1.17,-4.94,3.37,-0.22,-5.23,3.09,-1.75,-5.52,2.38,-3.69,-5.76,1.28,-5.62,-7.54,-0.2,-9.46,-8.91,-2.43,-13.31,-10.4,-7.63,-19.12,-16.17,-12.56,-22.23,-21.51,-16.26,-31.24,-24.74,-28.47,-39.04,-35.16,-38.86,-46.75,-36.91,-47.34,-50.21,-49.49,-50.19,-60.47,-57.45,-51,-69.1,-57.04,-61.37,-71.18,-65.93,-72.76,-74.68,-48.82,-64.08,-73.38,-59.16,-67.89,-58.42,-60.62,-55.79,-44.69,-39.16,-45.61,-29.88,-36.91,-26.7,-33.35,-21.33,-28.56,-3.63,-3.98,1.91,4.78,16.56,15.33,21.6,34.76,32.82,55.81,50.17,54.37,82.08,72.81,88.06,101.84,108.21,99.5,134.46,122.28,142.14,164.03,150.24,147.99,161.57,168.74,177.9,178.98,192.79,190.17,197.89,198.78,223.54,259.52,270.16,283.26,237.29,288.55,288.85,266.19,323.53,329.77,274,276.51,342.97,289.76,352.6,357.22,334.27,377.16,366.42,351.51,359.12,370.02,380.4,335.48,314.41,314.31,316.67,350.47,367.42,383.57,379.79,334.09,296.64,307.08,295.39,320.18,328.52,325.53,296.89,312.12,265.57,263.86,304.68,237.7,263.22,228.07,222.54,246.29,217.59,244.21,216.45,221.24,189.65,185.04,166.87,199.85,165.87,177.53,173.59,152.25,140.11,139.55,143.56,128.87,120.6,122.41,91.46,97.46,101.5,86.53,90.03,84.53,66.4,70.73,60.29,55.58,57.97,42.81,46.27,46.98,38.33,31.92,41.11,29.39,29.72,30.8,22.05,21.96,21.16,11.18,13.84,16.08,9.35,11.54,13.36,2.73,8.24,9.13,0.1,5.33,4.98,-3.46,4.68,1.3,-5.41,2.34,-2.19,-7.2,1.28,-4.46,-7.99,0.21,-6.81,-9.49,-1.34,-9.51,-8.71,-2.04,-11.52,-9.75,-4.37,-12.24,-8.81,-3.73,-12.55,-9.69,-7.21,-14.27,-8.95,-7.58,-15.03,-9.23,-9.53,-16.86,-7.57,-8.08,-16.39,-8.23,-10.29,-16.64,-8.37,-14.1,-14.61,-9.52,-13.09,-17.13,-10.9,-17.11,-13.58,-7.61,-16.04,-14.92,-11.4,-19.22,-18.99,-12.13,-16.51,-11.83,-15.54,-18.34,-12.47,-13.75,-18.17,-11.9,-14.08,-18.81,-16.2,-15.15,-25.08,-16.08,-14.96,-20.05,-16.23,-19.11,-31.22,-15.1,-20.56,-26.24,-24.64,-28.91,-32.42,-20.39,-24.31,-23.85,-21.36,-41.15,-32.71,-27.78,-32.57,-30.94,-27.98,-40.6,-29.42,-25.4,-51.31,-38.62,-37.94,-46.73,-29.02,-28.77,-57.09,-28.98,-41.53,-54.34,-37.63,-41.85,-40.8,-39.98,-58.97,-42.86,-35.57,-47.08,-66.07,-45.44,-59.42,-53.31,-39.71,-63.88,-52.91,-38.35,-70.96,-50.87,-58.33,-69.71,-47.22,-56.93,-61.48,-69.05,-64.47,-50.85,-48.03,-44.21,-70.93,-53.86,-54.3,-50.69,-64.18,-52.42,-63.89,-54.08,-63.69,-57.52,-67.93,-59.47,-71.24,-49.33,-53.53,-50.83,-43.71,-60.35,-68.71,-43.22,-72.79,-49.26,-59.2,-53.77,-74.86,-62.02,-68.18,-46.1,-42.04,-77.4,-70.89,-44.03,-67.43,-59.36,-66.05,-78.57,-68.65,-50.02,-47.28,-46.1,-66.44,-65.2,-62.64,-66.41,-54.88,-48.28,-65.06,-55.12,-48.73,-61.04,-55.22,-62,-55.12,-42.47,-37.99,-55.11,-51.92,-40.35,-51.56,-59.59,-45.79,-46,-41.23,-50.33,-58.76,-48.37,-54.11,-62.05,-49.25,-39.6,-40.82,-41.84,-41.42,-44.08,-33.4,-48.68,-44.37,-34.31,-45.44,-53.76,-29.59,-37.51,-44.98,-28.13,-37.14,-35.06,-34.32,-39.76,-37.58,-23.21,-37.14,-26.67,-30.68,-41.32,-29.29,-29.89,-29.99,-21.21,-19.95,-29.5,-18.58</v>
       </c>
     </row>
     <row r="26">
@@ -682,7 +682,7 @@
         <v>[L_01_标记]</v>
       </c>
       <c r="C26" t="str">
-        <v>a: 15.4ms -85.5uv b: 34.4ms 392.3uv</v>
+        <v>a: 15.6ms -39.1uv b: 35.1ms 183.8uv</v>
       </c>
     </row>
     <row r="27">
@@ -693,7 +693,7 @@
         <v>[R_02_名字]</v>
       </c>
       <c r="C27" t="str">
-        <v>FERG(2)_dMax</v>
+        <v>FERG(2)_dRod</v>
       </c>
     </row>
     <row r="28">
@@ -715,7 +715,7 @@
         <v>[R_02_闪光]</v>
       </c>
       <c r="C29" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.03cd.m-2,5ms</v>
       </c>
     </row>
     <row r="30">
@@ -726,7 +726,7 @@
         <v>[R_02_闪光背景]</v>
       </c>
       <c r="C30" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="31">
@@ -737,7 +737,7 @@
         <v>[R_02_采样]</v>
       </c>
       <c r="C31" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="32">
@@ -748,7 +748,7 @@
         <v>[R_02_分析时间]</v>
       </c>
       <c r="C32" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="33">
@@ -770,7 +770,7 @@
         <v>[R_02_详细数据(uv)]</v>
       </c>
       <c r="C34" t="str">
-        <v>1.57,-2.68,2.99,-2.41,1.12,0.5,-1.98,2.87,-2.91,2.08,-0.64,-0.99,2.32,-2.98,2.73,-1.7,0.13,1.43,-2.64,2.96,-2.54,1.19,0.28,-1.96,2.7,-3.09,1.99,-1.02,-1.15,1.87,-3.4,2.25,-2.47,-0.51,0.36,-3.7,1.61,-4.23,-0.58,-2.11,-4.5,-0.46,-6.75,-2.14,-6.06,-6.67,-4.74,-10.84,-6.23,-12.3,-11.39,-12.22,-17.62,-14.1,-21.84,-19.98,-23.89,-28.27,-26.79,-35.55,-33.45,-40.3,-43.44,-44.6,-53.45,-51.74,-60.82,-62.47,-66.28,-74.04,-73,-82.94,-82.76,-88.47,-93.73,-93.14,-102.05,-99.52,-105.67,-106.96,-106.13,-111.86,-106.43,-111.14,-107.23,-105.19,-105.77,-97.05,-98.44,-88.7,-84.51,-78.61,-66.63,-63.25,-47.83,-40.86,-28.11,-13.38,-4.51,15.57,25.51,44.49,61.05,75.38,98.45,111.22,134.97,152.32,171.42,195.57,210.8,237.42,254.63,277.37,300.8,318.04,345.48,361.92,386.91,408.17,426.91,453.21,468.53,494.2,512.29,531.87,555.27,569.31,593.98,608.26,627.82,646.85,659.45,681.36,691.53,709.94,723.48,734.39,751.85,757.88,773.82,781.2,790.05,801.67,803.74,815.9,816.97,823.33,828.22,826.76,834.02,829.22,832.7,830.62,826.26,827.92,818.25,818.6,810.04,803.55,799.47,786.36,783.5,769.63,761.83,752.42,737.56,731.61,714.12,705.75,691.93,676.98,668.28,649.1,640.73,623.8,610.17,599.16,580.22,572.15,553.61,542.27,529.5,512.44,504.69,486.05,477.41,463.45,449.46,441.81,424.4,418.32,403.79,393.43,385.54,370.4,366.27,351.75,345.03,336.51,324.33,321.22,307.32,303.7,294.29,285.35,282.25,269.54,268.1,257.77,251.98,247.97,236.96,236.62,225.58,222.53,216.98,208.07,207.71,196.45,195.49,188.14,181.6,180.27,169.44,169.77,160.77,156.66,153.7,144.05,144.8,134.67,132.83,127.91,120.11,120.48,110.01,110.03,103.23,97.77,97.07,87.17,88.45,80.15,77.26,75.03,66.57,68.37,59.24,58.8,54.83,48.53,50.07,40.93,42.5,36.87,33.16,33.74,25.45,28.33,21.41,20.36,19.45,12.77,16.12,8.48,9.84,7.17,2.67,5.6,-2.02,1.17,-3.25,-5.27,-3.53,-10.37,-6.14,-11.99,-11.55,-11.56,-16.93,-12.56,-19.27,-16.71,-18.73,-22.1,-18.49,-25.32,-21.26,-25.22,-26.33,-24.21,-30.38,-25.6,-31.14,-30.01,-29.88,-34.69,-30.06,-36.54,-33.52,-35.57,-38.46,-34.83,-41.47,-37.14,-41.22,-41.94,-39.98,-45.95,-41.09,-46.75,-45.33,-45.46,-50.04,-45.49,-52.05,-48.83,-51.16,-53.81,-50.38,-57,-52.58,-56.91,-57.38,-55.68,-61.53,-56.68,-62.51,-60.85,-61.26,-65.63,-61.18,-67.78,-64.36,-66.94,-69.3,-66.02,-72.55,-67.99,-72.49,-72.63,-71.11,-76.74,-71.82,-77.69,-75.7,-76.27,-80.3,-75.84,-82.34,-78.61,-81.3,-83.25,-79.99,-86.29,-81.46,-85.98,-85.64,-84.17,-89.43,-84.3,-90.07,-87.6,-88.2,-91.74,-87.13,-93.4,-89.22,-91.88,-93.26,-89.91,-95.82,-90.61,-95.01,-94.08,-92.53,-97.28,-91.84,-97.38,-94.32,-94.84,-97.78,-92.93,-98.84,-94.12,-96.66,-97.38,-93.86,-99.29,-93.62,-97.82,-96.23,-94.54,-98.71,-92.91,-98.16,-94.47,-94.86,-97.16,-92.05,-97.56,-92.3,-94.68,-94.73,-91.04,-95.97,-89.87,-93.86,-91.62,-89.82,-93.42,-87.3,-92.27,-88,-88.31,-89.99,-84.69,-89.84,-84.1,-86.39,-85.84,-82.05,-86.55,-80.1,-83.96,-81.17,-79.35,-82.47,-76.15,-80.93,-76.2,-76.52,-77.7,-72.33,-77.23,-71.15,-73.47,-72.43,-68.68,-72.88,-66.23,-70.09,-66.88,-65.18,-67.95,-61.58,-66.3,-61.26,-61.74,-62.57,-57.28,-62.06,-55.8,-58.28,-56.92,-53.36,-57.38,-50.69,-54.68,-51.2,-49.77,-52.33,-46.06,-50.85,-45.64,-46.42,-47.02,-41.97,-46.75,-40.45,-43.2,-41.64,-38.4,-42.36,-35.77,-39.98,-36.36,-35.31,-37.75,-31.71,-36.66,-31.4,-32.57,-33.03,-28.3,-33.16,-26.92,-30.03,-28.34,-25.52,-29.47,-23.05,-27.56,-23.87,-23.25,-25.63,-19.88,-25.03,-19.77</v>
+        <v>-3.98,-2.66,-15.41,5.28,-19.15,3.07,-12.18,-7.54,-0.59,-17.52,5.68,-18.28,1.34,-9.02,-9.71,2.53,-17.73,6.79,-15.49,0.5,-4.48,-10.48,6.37,-16.21,8.31,-11.19,0.29,0.9,-10.17,10.36,-13.44,9.74,-6.04,0.26,6.35,-9.3,13.77,-10.11,10.47,-0.87,-0.15,11.04,-8.48,15.89,-6.96,9.91,3.49,-1.48,14.12,-8.35,16.05,-4.72,7.52,6.32,-4.24,14.85,-9.44,13.47,-3.82,2.69,6.65,-8.94,12.52,-12.35,7.47,-6.4,-5.6,4.39,-15.54,6.42,-17.59,-3.39,-12.05,-17.92,-3.86,-29.26,-4.09,-26.22,-14.46,-17.95,-28.39,-14.62,-42.44,-23.28,-44.69,-34.85,-33.55,-54.26,-24.73,-59.4,-39.83,-49.2,-48.95,-39.77,-61.94,-36.35,-60.86,-44.17,-54.32,-58.13,-41.59,-73.56,-45.56,-57.89,-45.27,-56.98,-59.99,-45.66,-74,-49.52,-53.53,-54.11,-30.99,-40.48,-23.41,-38.43,-13.89,-25.25,-17.75,-8.48,-18.29,25.1,4.12,20.11,32.92,28.69,53.26,32.08,62.98,44.53,85.54,73.18,69.88,113.3,76.98,129.9,108.42,137.19,136.39,151.35,169.19,155.68,184.46,158.88,202.9,194.57,195.51,221.45,195.19,256.02,245.17,257.99,230.03,267.44,245.2,257.92,257.19,264.64,265.1,323.32,271.97,343.82,268.85,313.98,357.76,320.34,372.62,296.6,381.44,366.96,364.46,342.72,311.4,378.21,322.31,387.94,382.07,348.3,330.84,353.12,332.64,335.33,324.52,320.55,346.8,318.46,356,380.55,317.11,334.63,302.87,292,301.27,300.75,271.99,310.58,284.69,309.17,283.12,296.55,269.7,290.77,222.66,216.3,230.59,234.92,236.56,180.15,189.6,205.69,196.95,193.82,170.98,186.82,152.05,179.83,171.4,144.09,135.58,128.18,129.42,118.9,131.55,125.19,89.92,121.23,74.2,104.38,81.79,83.39,90.76,60.95,81,60.07,67.64,60.96,45.82,55.35,36.71,53.92,28.41,45.88,37.48,24.06,42.9,13.55,36.91,12.18,24.59,21.3,8.35,24.63,1.25,22.2,2.31,7.72,13.14,-5.98,15.79,-8.38,8.81,-2.19,-3.86,6.34,-14.43,9.79,-13.11,1.29,-4.86,-12.22,4.09,-20.03,5.07,-15.83,-5.17,-5.05,-16.5,3.68,-20.04,1.05,-15.52,-7.86,-2.62,-19.95,2.23,-19.32,-1.02,-12.28,-10.43,-2.46,-20.34,3.63,-20.68,-3.18,-8.73,-13.58,2.18,-21.28,2.65,-16.08,-3.45,-7.84,-16.88,1.57,-17.36,2.89,-16.33,-5.82,-4.18,-17.41,1.3,-16.98,1.87,-12.81,-12.77,-2.32,-18.51,3.48,-17.83,-8.39,-9.64,-19.11,-4.92,-27.98,0.25,-25.38,-7.98,-15.38,-22.95,-10.79,-27.25,-15.65,-28.43,-24.54,-20.76,-36.55,-5.97,-35.07,-22.21,-39.6,-37.84,-28.19,-40.37,-12.63,-49.47,-26.46,-36.49,-32.66,-22.07,-58.52,-26.68,-45.37,-31.61,-42.42,-42.62,-35.74,-62.07,-22.47,-41.98,-42.83,-50.35,-55.91,-25.83,-68.18,-36.69,-49.29,-54.89,-41.21,-49.33,-33.58,-59.74,-37.86,-56.61,-60.87,-54.24,-63.86,-35.94,-71.33,-58.33,-45.32,-59.61,-57.32,-74.98,-34.7,-71.91,-42.04,-43.09,-74.71,-46.89,-61.31,-48.68,-48.58,-37.59,-51.65,-59.09,-35.65,-57.36,-47.51,-70.98,-58.33,-34.33,-46.77,-40.27,-47.69,-61.86,-61.45,-71.6,-44.71,-75.45,-43.24,-74.6,-42.76,-36.23,-48.19,-31.75,-62.39,-32.83,-66.68,-51.8,-55.15,-59.01,-36.37,-56.26,-56.37,-50.54,-59.78,-32.76,-58.89,-25.34,-50.22,-44.8,-39.97,-64.23,-35.27,-73.32,-29.43,-59.55,-42.97,-63.6,-57.8,-28.96,-59.39,-31.43,-54.38,-50.94,-54.92,-58.3,-25.28,-53.9,-36.21,-61.87,-52.4,-47.7,-67.62,-40.99,-62.53,-48.06,-39.98,-49.39,-36.44,-48.05,-31.66,-54.89,-40.6,-29.16,-34.73,-31.02,-47.76,-16.33,-47.94,-31.98,-28.71,-32.28,-10.04,-42.44,-19.51,-23.11,-21.04,-11.72,-37.34,-8.13,-24.8,-7.99,-22.26,-24.35,-10.28,-21.71,-1.94,-28.63,-8.8,-12.36,-22.86,-0.26,-20.76,-0.11,-21.93,-5.12,-3.16,-19.97,4.83</v>
       </c>
     </row>
     <row r="35">
@@ -781,7 +781,7 @@
         <v>[R_02_标记]</v>
       </c>
       <c r="C35" t="str">
-        <v>a: 17.4ms -181.9uv b: 38.4ms 813.2uv</v>
+        <v>a: 16.5ms -34.3uv b: 38.2ms 174.7uv</v>
       </c>
     </row>
     <row r="36">
@@ -792,7 +792,7 @@
         <v>[L_02_名字]</v>
       </c>
       <c r="C36" t="str">
-        <v>FERG(2)_dMax</v>
+        <v>FERG(2)_dRod</v>
       </c>
     </row>
     <row r="37">
@@ -814,7 +814,7 @@
         <v>[L_02_闪光]</v>
       </c>
       <c r="C38" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.03cd.m-2,5ms</v>
       </c>
     </row>
     <row r="39">
@@ -825,7 +825,7 @@
         <v>[L_02_闪光背景]</v>
       </c>
       <c r="C39" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="40">
@@ -836,7 +836,7 @@
         <v>[L_02_采样]</v>
       </c>
       <c r="C40" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="41">
@@ -847,7 +847,7 @@
         <v>[L_02_分析时间]</v>
       </c>
       <c r="C41" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="42">
@@ -869,7 +869,7 @@
         <v>[L_02_详细数据(uv)]</v>
       </c>
       <c r="C43" t="str">
-        <v>0.54,-1.07,1.55,-1.99,2.36,-2.66,2.87,-2.98,2.99,-2.91,2.73,-2.46,2.11,-1.7,1.21,-0.71,0.15,0.36,-0.94,1.38,-1.91,2.2,-2.65,2.72,-3.07,2.86,-3.13,2.57,-2.83,1.88,-2.24,0.85,-1.48,-0.42,-0.69,-1.84,-0.04,-3.29,0.3,-4.68,0.17,-5.96,-0.56,-7.13,-1.98,-8.23,-4.13,-9.39,-7.03,-10.77,-10.62,-12.55,-14.85,-14.95,-19.65,-18.17,-24.93,-22.36,-30.62,-27.63,-36.66,-34,-43,-41.41,-49.6,-49.7,-56.43,-58.61,-63.41,-67.8,-70.46,-76.88,-77.42,-85.39,-84.07,-92.87,-90.15,-98.85,-95.28,-102.91,-99.05,-104.66,-101,-103.78,-100.66,-100.02,-97.55,-93.21,-91.25,-83.24,-81.42,-70.06,-67.82,-53.7,-50.34,-34.21,-28.98,-11.68,-3.9,13.77,24.62,41.98,56.21,72.8,90.43,106.03,126.77,141.44,164.75,178.78,203.87,217.74,243.69,257.99,283.84,299.14,323.99,340.78,363.89,382.48,403.31,423.77,442.09,464.2,480.06,503.35,517.05,540.81,552.85,576.23,587.24,609.31,619.91,639.82,650.57,667.56,678.84,692.41,704.37,714.28,726.8,733.1,745.8,748.83,761.11,761.43,772.53,770.84,779.97,777.03,783.42,779.94,782.98,779.52,778.82,775.76,771.22,768.65,760.47,758.25,746.93,744.69,730.95,728.15,712.88,708.89,693.03,687.26,671.7,663.67,649.14,638.56,625.57,612.4,601.21,585.68,576.23,558.84,550.82,532.28,525.18,506.34,499.51,481.28,474.05,457.25,449.05,434.35,424.74,412.59,401.36,391.91,379.13,372.24,358.23,353.47,338.77,335.51,320.8,318.26,304.31,301.69,289.2,285.77,275.33,270.52,262.5,255.96,250.47,242.15,239.01,229.13,227.91,216.92,216.97,205.52,206.06,194.89,195.1,184.93,184.07,175.53,173.03,166.54,162.04,157.8,151.24,149.14,140.74,140.43,130.65,131.56,121.08,122.48,112.07,113.2,103.63,103.75,95.71,94.26,88.25,84.87,81.12,75.73,74.23,67.02,67.45,58.87,60.7,51.39,53.92,44.65,47.1,38.65,40.29,33.34,33.55,28.63,27.01,24.39,20.78,20.46,15.02,16.71,9.82,13.01,5.27,9.25,1.41,5.4,-1.78,1.45,-4.37,-2.55,-6.48,-6.52,-8.24,-10.33,-9.82,-13.88,-11.38,-17.06,-13.06,-19.78,-14.97,-22,-17.16,-23.73,-19.63,-25.02,-22.33,-25.98,-25.19,-26.74,-28.07,-27.45,-30.85,-28.26,-33.41,-29.31,-35.64,-30.68,-37.5,-32.43,-38.95,-34.55,-40.05,-37,-40.86,-39.69,-41.52,-42.47,-42.15,-45.22,-42.9,-47.8,-43.89,-50.1,-45.23,-52.04,-46.95,-53.59,-49.06,-54.78,-51.52,-55.67,-54.21,-56.38,-57.02,-57.03,-59.81,-57.76,-62.42,-58.71,-64.75,-59.96,-66.71,-61.57,-68.25,-63.56,-69.4,-65.86,-70.22,-68.39,-70.8,-71.03,-71.27,-73.64,-71.78,-76.07,-72.44,-78.19,-73.37,-79.92,-74.63,-81.2,-76.22,-82.06,-78.11,-82.53,-80.21,-82.72,-82.41,-82.75,-84.57,-82.76,-86.54,-82.89,-88.19,-83.24,-89.43,-83.87,-90.2,-84.82,-90.51,-86.06,-90.41,-87.5,-89.98,-89.03,-89.36,-90.52,-88.67,-91.82,-88.07,-92.81,-87.65,-93.39,-87.51,-93.49,-87.66,-93.12,-88.1,-92.32,-88.76,-91.17,-89.52,-89.79,-90.25,-88.34,-90.83,-86.95,-91.1,-85.73,-90.98,-84.79,-90.41,-84.15,-89.36,-83.8,-87.88,-83.7,-86.05,-83.74,-84,-83.8,-81.86,-83.72,-79.78,-83.39,-77.89,-82.7,-76.27,-81.58,-74.98,-80.01,-74.02,-78.03,-73.34,-75.72,-72.85,-73.19,-72.42,-70.58,-71.91,-68.03,-71.2,-65.69,-70.17,-63.65,-68.76,-61.96,-66.92,-60.64,-64.7,-59.64,-62.17,-58.88,-59.42,-58.23,-56.62,-57.57,-53.89,-56.74,-51.38,-55.65,-49.19,-54.21,-47.38,-52.39,-45.96,-50.2,-44.91,-47.71,-44.14,-45.02,-43.53,-42.28,-42.95,-39.62,-42.27,-37.18,-41.35,-35.07,-40.11,-33.37,-38.52,-32.08,-36.57,-31.18,-34.33,-30.59,-31.9,-30.21,-29.41,-29.89,-26.99,-29.5,-24.79,-28.9,-22.91,-28.01,-21.44,-26.78,-20.4,-25.2,-19.76,-23.32,-19.47,-21.24</v>
+        <v>-1.62,24.63,-2.14,14.05,13.15,-2.69,23.07,-4.1,13.74,11.07,-2.99,22.18,-5.24,14.18,9.76,-2.43,22.04,-5.51,15.4,9.26,-1.02,22.62,-4.93,17.35,9.48,1.13,23.8,-3.66,19.85,10.26,3.84,25.38,-1.9,22.67,11.35,6.84,27.1,0.06,25.53,12.47,9.82,28.64,1.91,28.1,13.31,12.48,29.7,3.38,30.03,13.5,14.4,29.93,3.98,31.06,12.82,15.53,29.05,3.81,30.97,10.99,15.3,26.81,1.46,28.78,7.61,13.41,22.54,-1.45,24.71,0.59,9.28,15.57,-6.74,18.99,-7.24,1.29,7.92,-18.45,9.92,-20.01,-9.79,-2.19,-27.08,-2.33,-28.3,-19.23,-24.67,-41.67,-19.57,-38.64,-36.09,-35.07,-57.68,-36.34,-56.67,-40.23,-34.66,-61,-41.67,-70.93,-37.17,-48.81,-68.18,-42.2,-54.93,-47.63,-54.98,-57.63,-35.88,-62.17,-35.01,-42.71,-40.47,-6.63,-33.72,-5.59,-16.61,-29.48,8.04,-11.1,16.94,17.09,15.99,44.17,13.07,55.31,56.7,39.51,93.3,48.26,98.91,88.07,85.99,117.57,98.26,128.26,130.44,126.03,154.59,154.84,157.33,185.27,191.02,203.19,188.8,231.99,231.11,200.71,251.6,216.54,277.94,235.22,286.11,297.42,242.37,312.61,296.49,296.49,292.31,266.44,335.97,290.91,330.88,321.9,313.45,315.03,307.6,360.87,386.65,367.04,336.43,369.26,323,379.71,377.37,360.16,354.98,369.71,361.39,306.83,396.36,317.37,372.08,372.63,325.98,341.06,295.62,298.4,326.41,335.72,315.3,281.43,270.83,309.02,277.33,286.28,234.51,251.55,261.87,258.28,240.73,208.32,250.55,201.16,225.35,246.86,213.01,211.28,189.35,185.26,191.79,136.3,187.97,153.41,154.27,168.27,109.62,154.7,124.99,115.32,129.8,84.06,105.14,95.39,95.81,100.27,76.18,90.29,68.62,66.35,81.97,55.48,76.92,52.6,56.22,67.51,38.17,59.21,37.46,41.47,45.93,23,47.98,26.68,26.86,36.28,9.99,36.27,13.43,18.79,28.16,3.84,29.1,5.46,14.43,20.15,-3.49,23.13,-1.19,7.82,13.62,-8.54,18.21,-5.98,5.25,7.89,-12.09,15.56,-11.33,1.96,4.83,-15.16,12.87,-14.37,0.33,1.05,-15.79,9.46,-16.3,-0.04,-2.63,-15.51,8.8,-18.92,0.22,-2.68,-14.76,8.53,-17.63,-0.3,-6.08,-16.11,8.04,-18.92,4.05,-7,-12.7,9.55,-17.81,1.51,-4.22,-12.72,9.43,-18.96,7.43,-8.78,-8.59,5.37,-19.94,8.81,-4.31,-7.62,11.55,-19.8,9.58,-13.06,-9.87,6.93,-22.6,2.03,-17.09,-7.58,-1.19,-21.12,7.69,-20.21,-9.98,-2.17,-31.2,-4.09,-22.22,-10.72,-2.82,-33.33,-5.68,-24.37,-14.96,-8.77,-30.95,-12.63,-36.38,-19.67,-11.59,-45.85,-14.1,-45.82,-31.15,-25.02,-51.72,-13.04,-53,-37.38,-25.9,-51.55,-28.35,-40.58,-48.79,-32.6,-64.08,-19.43,-63.37,-45.37,-30.63,-49.92,-30.23,-68.67,-53.98,-43.83,-67.15,-36.12,-72.78,-52.6,-61.68,-59.43,-44.61,-69.95,-42.88,-57,-63.61,-36.85,-80.21,-42.27,-47.95,-52.83,-29.63,-57.38,-53.48,-40.78,-52.45,-38.98,-80.88,-58.37,-53.47,-64.51,-26.86,-72.56,-38.13,-64.09,-64.56,-43.87,-81.69,-51.52,-56.55,-51.71,-47.82,-79.53,-44.83,-49.78,-50.82,-26.45,-63.77,-23.38,-43.59,-65.09,-45.54,-79.89,-41.43,-43.59,-63.35,-49.04,-60.91,-40.84,-68.54,-53.33,-51.99,-68.07,-32.36,-70.34,-63.7,-26.69,-68.88,-39.48,-53.95,-60.21,-28.57,-78.4,-40.09,-66,-61.69,-30.7,-70.52,-28.81,-55.72,-52.23,-52.96,-58.03,-42.19,-61.94,-50,-50.79,-70.8,-33.35,-62.09,-44.15,-32.5,-61.56,-34.24,-56.77,-42.55,-42.33,-52.5,-36.15,-51.78,-43.12,-43.42,-57.66,-14.92,-41.98,-33.8,-33.21,-44.5,-21.61,-42.56,-23.77,-29.54,-41.73,-11.8,-46.59,-13.23,-26.34,-29.5,-12.69,-37.13,-13.98,-18.91,-23.57,-3.42,-28.21,-5.65,-21.94,-22.01,4.29,-28.04,3.04,-11.1,-13.79,0.24,-27.62,1.11,-13.97</v>
       </c>
     </row>
     <row r="44">
@@ -880,7 +880,7 @@
         <v>[L_02_标记]</v>
       </c>
       <c r="C44" t="str">
-        <v>a: 17.4ms -171.0uv b: 38.4ms 764.4uv</v>
+        <v>a: 16.4ms -36.1uv b: 38.2ms 203.8uv</v>
       </c>
     </row>
     <row r="45">
@@ -891,7 +891,7 @@
         <v>[R_03_名字]</v>
       </c>
       <c r="C45" t="str">
-        <v>FERG(3)_dOps</v>
+        <v>FERG(3)_dRod</v>
       </c>
     </row>
     <row r="46">
@@ -913,7 +913,7 @@
         <v>[R_03_闪光]</v>
       </c>
       <c r="C47" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.10cd.m-2,5ms</v>
       </c>
     </row>
     <row r="48">
@@ -924,7 +924,7 @@
         <v>[R_03_闪光背景]</v>
       </c>
       <c r="C48" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="49">
@@ -935,7 +935,7 @@
         <v>[R_03_采样]</v>
       </c>
       <c r="C49" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="50">
@@ -946,7 +946,7 @@
         <v>[R_03_分析时间]</v>
       </c>
       <c r="C50" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="51">
@@ -968,7 +968,7 @@
         <v>[R_03_详细数据(uv)]</v>
       </c>
       <c r="C52" t="str">
-        <v>-10.16,-11.59,-8.78,-12.13,-7.59,-12.45,-6.8,-12.56,-6.58,-12.54,-7.03,-12.45,-8.17,-12.34,-9.85,-12.23,-11.82,-12.05,-13.73,-11.7,-15.17,-11.07,-15.79,-10.08,-15.36,-8.75,-13.88,-7.21,-11.57,-5.78,-8.88,-4.86,-6.45,-4.87,-4.9,-6.13,-4.75,-8.75,-6.2,-12.48,-9.09,-16.74,-12.81,-20.65,-16.45,-23.18,-18.96,-23.41,-19.46,-20.8,-17.44,-15.39,-13.04,-7.94,-7.08,0.13,-0.96,7.01,3.64,10.83,5.15,10.2,2.58,4.57,-4.1,-5.41,-13.84,-17.94,-24.56,-30.33,-33.59,-39.56,-38.31,-42.99,-36.78,-39.1,-28.45,-28.01,-14.43,-11.64,2.55,6.59,18.64,22.41,29.72,31.73,32.44,31.67,25.14,21.41,8.5,2.59,-14.42,-20.89,-38.72,-43.67,-58.69,-60.16,-69.17,-65.9,-66.89,-58.79,-51.45,-39.74,-25.57,-12.66,5.33,16.36,34.28,40.41,54.41,53.48,60.61,51.94,50.84,35.56,26.8,7.71,-6.41,-25.36,-41.35,-55.95,-70,-76.76,-85.67,-82.67,-84.63,-72.02,-67,-47.1,-36.81,-13.6,-1,20.73,32.2,47.92,55.25,61.69,63.08,58.97,54.25,40.57,31.22,10.95,-0.35,-22.9,-32.95,-53.18,-59.16,-73.14,-73.28,-78.6,-72.71,-68.88,-58.33,-46.81,-34.19,-17.89,-6.36,11.08,18.6,33.67,35.21,45.26,40.28,44.02,33.52,31.11,17.38,10.25,-3.7,-13.38,-24.52,-34.38,-40.35,-48.44,-48.04,-53.15,-46.58,-48.44,-37.16,-36.32,-22.71,-20.23,-6.99,-4.07,6.29,8.66,14.38,15.68,16,16.25,11.48,11.13,2.5,2.27,-8.43,-7.88,-18.66,-16.91,-26.02,-23.07,-29.21,-25.5,-28.06,-24.34,-23.33,-20.5,-16.5,-15.36,-9.28,-10.33,-3.24,-6.53,0.52,-4.61,1.55,-4.62,0.04,-6.14,-3.35,-8.47,-7.65,-10.81,-11.89,-12.55,-15.28,-13.3,-17.34,-13.01,-17.92,-11.93,-17.19,-10.47,-15.54,-9.09,-13.41,-8.17,-11.26,-7.95,-9.42,-8.47,-8.09,-9.57,-7.34,-10.99,-7.12,-12.4,-7.34,-13.49,-7.86,-14.07,-8.58,-14.03,-9.4,-13.39,-10.26,-12.31,-11.11,-10.97,-11.89,-9.62,-12.57,-8.47,-13.06,-7.68,-13.33,-7.36,-13.32,-7.53,-13,-8.14,-12.4,-9.09,-11.57,-10.23,-10.6,-11.4,-9.62,-12.45,-8.75,-13.25,-8.11,-13.7,-7.8,-13.76,-7.87,-13.42,-8.32,-12.73,-9.08,-11.79,-10.07,-10.72,-11.15,-9.65,-12.17,-8.72,-13.01,-8.05,-13.54,-7.72,-13.7,-7.78,-13.46,-8.22,-12.86,-8.97,-11.98,-9.95,-10.93,-11.03,-9.85,-12.07,-8.88,-12.92,-8.15,-13.49,-7.75,-13.7,-7.74,-13.51,-8.12,-12.96,-8.83,-12.11,-9.79,-11.08,-10.86,-10,-11.92,-9.01,-12.81,-8.24,-13.43,-7.79,-13.69,-7.72,-13.57,-8.04,-13.07,-8.71,-12.26,-9.63,-11.24,-10.7,-10.16,-11.76,-9.15,-12.69,-8.34,-13.36,-7.83,-13.68,-7.71,-13.61,-7.97,-13.16,-8.59,-12.39,-9.48,-11.4,-10.53,-10.32,-11.61,-9.29,-12.57,-8.44,-13.28,-7.89,-13.66,-7.7,-13.65,-7.9,-13.25,-8.47,-12.53,-9.33,-11.56,-10.37,-10.48,-11.45,-9.44,-12.43,-8.55,-13.19,-7.95,-13.62,-7.7,-13.67,-7.85,-13.33,-8.37,-12.65,-9.19,-11.72,-10.21,-10.65,-11.29,-9.59,-12.3,-8.67,-13.1,-8.02,-13.58,-7.72,-13.69,-7.8,-13.41,-8.27,-12.77,-9.05,-11.87,-10.05,-10.81,-11.13,-9.74,-12.16,-8.79,-12.99,-8.09,-13.53,-7.74,-13.7,-7.76,-13.48,-8.18,-12.89,-8.92,-12.02,-9.89,-10.97,-10.97,-9.9,-12.01,-8.92,-12.89,-8.18,-13.47,-7.77,-13.7,-7.74,-13.53,-8.09,-13,-8.79,-12.16,-9.73,-11.14,-10.81,-10.05,-11.86,-9.06,-12.77,-8.27,-13.41,-7.8,-13.69,-7.71,-13.58,-8.01,-13.1,-8.66,-12.3,-9.58,-11.3,-10.64,-10.22,-11.71,-9.19,-12.65,-8.37,-13.33,-7.85,-13.67,-7.7,-13.62,-7.95,-13.19,-8.55,-12.44,-9.43,-11.46,-10.48,-10.38,-11.56,-9.34,-12.52,-8.48,-13.25,-7.91,-13.64,-7.7,-13.66,-7.88,-13.28,-8.44,-12.57,-9.28,-11.61</v>
+        <v>-18.9,-24.4,-17.9,-24.86,-17.04,-25.1,-16.35,-25.11,-15.84,-24.87,-15.55,-24.39,-15.46,-23.67,-15.58,-22.75,-15.88,-21.65,-16.34,-20.44,-16.94,-19.13,-17.6,-17.81,-18.32,-16.5,-19.05,-15.27,-19.74,-14.24,-20.38,-13.32,-20.84,-12.8,-21.3,-12.41,-21.41,-12.28,-21.59,-12.53,-21.35,-13.16,-21.52,-14.29,-21.15,-15.52,-20.98,-16.54,-21.17,-18.11,-20.53,-19.99,-20.62,-22.13,-19.76,-25.36,-20.63,-27.79,-21.41,-29.58,-21.26,-32.2,-22.94,-32.82,-25.51,-35.86,-25.28,-38.57,-33.19,-36.84,-30.2,-41.44,-33.44,-42.14,-43.94,-43.74,-37.93,-50.66,-39.95,-51.54,-55.76,-48.45,-47.9,-54.71,-52.07,-55.63,-57.13,-55.03,-57.75,-38.56,-48.65,-40.53,-54.07,-52.54,-66.09,-49.52,-50.01,-41.53,-58.28,-50.07,-29.23,-17.52,-31.55,-23.29,-30.11,-23.01,-14.58,-12.66,-6.67,-4.96,3.45,3.3,22.74,10.44,29.56,31.12,33.52,50.38,43.09,58.14,59.76,47.54,69.9,85.92,102.49,82,99.12,107.45,126.68,123.27,127.63,138.7,148.56,167.73,177.64,160.89,180.72,185.93,202.5,189.05,181.41,203.49,202.58,235.1,227,262.7,223.85,268.2,225.94,258.87,284.23,264.48,251.95,305.83,292.66,302.66,305.42,265.09,285.33,299.56,317.77,328.75,346.91,325.26,313.24,341.95,306.72,358.97,302.62,302.81,331.53,289.22,350.08,280.22,358.99,316.06,357.66,320.59,301.26,303.36,321.69,343.26,309.49,272.36,281.66,330.78,320.05,324.32,323.88,292.19,299.81,287.98,296.16,241.06,242.74,247.65,228.82,227.63,215.59,238.21,254.36,211.62,242.44,196.07,185.7,209.2,176.82,197.3,196.43,181.76,178.53,188.87,161.33,165.1,161,143.4,157.29,140.06,138.16,137.55,122.3,119.75,111.24,111.55,97.78,98.9,86.58,76.12,97.74,86.26,85.42,57.51,64.37,52.46,62.06,58.49,53.32,46.43,53.71,32.21,49.66,33.5,33.02,27.34,26.29,28.76,26.08,18.27,16.44,15.62,13.11,12.03,10.62,9.39,7.32,11.03,2.56,5.97,-1.39,5.05,-6.24,3.42,-6.4,1.49,-8.81,0.35,-10.21,-3.5,-12.08,-4.27,-13,-7.2,-11.71,-8.86,-13.7,-9.61,-12.19,-12.33,-11.34,-12.28,-11.33,-15.07,-10.21,-17.88,-11.09,-19.12,-11.92,-19.58,-9.05,-20.96,-10.32,-21.83,-12.14,-19.76,-10.69,-23.55,-12.77,-21.03,-11.91,-19.16,-13.15,-19.78,-16.26,-18.01,-17.14,-16.6,-23.78,-22.97,-21.72,-21.13,-27.72,-21.9,-27.49,-25.12,-33.03,-25.86,-29.51,-21.76,-35.63,-19.32,-33.12,-30.02,-30.3,-21.1,-40.01,-22.94,-41.71,-24.33,-35.28,-28.58,-29.41,-36.26,-34.85,-30.13,-41.95,-35.02,-37.72,-49.11,-29.79,-40.56,-34.12,-50.81,-32.83,-38.39,-37.17,-44.82,-31.29,-48.93,-37.1,-58.92,-44.06,-48.13,-46.93,-45.98,-38.89,-41.2,-48.86,-61.74,-43.53,-50.29,-50,-53.17,-65.28,-40.5,-62.12,-63.15,-43.73,-41.12,-45.49,-56.18,-62.2,-44.98,-67.83,-42.57,-50.55,-53.52,-69.71,-64.06,-57.02,-48.32,-52.75,-51.42,-56.02,-51.31,-53.92,-44.6,-70.52,-54.28,-72.7,-63.33,-61.37,-64.59,-58.72,-58.72,-52.96,-68.18,-61.06,-59.55,-69.8,-55.38,-64.97,-67.14,-40.34,-53.76,-67.67,-66.63,-52.22,-59.57,-72.19,-56.71,-57.78,-49.78,-43.2,-77.5,-52.01,-56.94,-54.94,-54.71,-56.51,-50.94,-62.65,-55.86,-66.2,-62.09,-65.08,-62.35,-61.91,-50.38,-60.16,-64.46,-68.37,-40.64,-47.85,-49.58,-52.63,-62.12,-59.1,-49.81,-52.01,-55.62,-47.97,-38.65,-42.92,-51.18,-54.97,-57.22,-53.44,-51.72,-50.77,-54.38,-39.95,-35.93,-31.36,-50.28,-27.99,-51.93,-27.26,-49.07,-33.59,-39.88,-25.43,-45.07,-38.73,-30.23,-21.74,-43.95,-35.1,-26.5,-22.41,-29.71,-21.48,-23.24,-31.53,-29.33,-18.99,-21.28,-26.83,-17.44,-20.01,-20.86,-24.33,-18.88,-25.02,-15.29,-20.33,-10.76,-18.83,-9.86,-20.71,-11.49,-26.85,-15.21,-23.5,-13.35,-21.58,-10.62,-19,-14.61,-22.96,-19.83</v>
       </c>
     </row>
     <row r="53">
@@ -979,7 +979,7 @@
         <v>[R_03_标记]</v>
       </c>
       <c r="C53" t="str">
-        <v>105.7uv</v>
+        <v>a: 18.0ms -36.8uv b: 41.2ms 237.0uv</v>
       </c>
     </row>
     <row r="54">
@@ -990,7 +990,7 @@
         <v>[L_03_名字]</v>
       </c>
       <c r="C54" t="str">
-        <v>FERG(3)_dOps</v>
+        <v>FERG(3)_dRod</v>
       </c>
     </row>
     <row r="55">
@@ -1012,7 +1012,7 @@
         <v>[L_03_闪光]</v>
       </c>
       <c r="C56" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.10cd.m-2,5ms</v>
       </c>
     </row>
     <row r="57">
@@ -1023,7 +1023,7 @@
         <v>[L_03_闪光背景]</v>
       </c>
       <c r="C57" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="58">
@@ -1034,7 +1034,7 @@
         <v>[L_03_采样]</v>
       </c>
       <c r="C58" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="59">
@@ -1045,7 +1045,7 @@
         <v>[L_03_分析时间]</v>
       </c>
       <c r="C59" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="60">
@@ -1067,7 +1067,7 @@
         <v>[L_03_详细数据(uv)]</v>
       </c>
       <c r="C61" t="str">
-        <v>-10.62,-8.79,-11.32,-7.48,-11.78,-6.49,-11.99,-6.02,-11.97,-6.2,-11.81,-7.07,-11.58,-8.56,-11.34,-10.45,-11.08,-12.42,-10.77,-14.09,-10.32,-15.07,-9.63,-15.07,-8.66,-13.99,-7.49,-11.94,-6.28,-9.3,-5.35,-6.61,-5.05,-4.52,-5.73,-3.62,-7.56,-4.29,-10.48,-6.54,-14.11,-10,-17.77,-13.9,-20.58,-17.25,-21.64,-19.05,-20.28,-18.58,-16.3,-15.61,-10.1,-10.56,-2.73,-4.5,4.26,1.07,9.11,4.52,10.29,4.54,6.9,0.55,-0.97,-7.02,-12.08,-16.74,-24.24,-26.35,-34.66,-33.29,-40.58,-35.31,-40.03,-31.14,-32.33,-20.97,-18.52,-6.55,-1.27,9.02,15.64,21.95,28.08,28.66,32.64,26.71,27.49,15.61,13.02,-2.93,-8.04,-25.12,-31.14,-45.91,-50.88,-60.13,-62.27,-63.77,-62.04,-55.09,-49.54,-35.22,-27.05,-8.1,0.56,20.31,26.96,43.39,45.78,55.41,52.23,53,44.31,36.09,23.44,8.04,-5.82,-25.02,-36.75,-55.57,-62.07,-76.51,-75.7,-82.85,-74.28,-72.93,-57.98,-48.89,-30.55,-16.15,1.62,17.81,31,45.27,50.76,60.07,56.38,59.08,46.75,42.85,24.34,15.42,-5.4,-16.67,-35.44,-46.07,-58.85,-66.28,-70.49,-73.19,-68.1,-65.91,-52.79,-46.85,-28.59,-20.95,-1.41,5.57,22.44,26.74,37.77,38.25,41.63,38.26,33.86,27.72,16.97,9.89,-4.63,-10.58,-25.82,-28.88,-41.93,-41.12,-49.83,-45.18,-48.5,-41.04,-39.05,-30.54,-24.32,-16.77,-8.01,-3.24,6.19,7.01,15.46,12.06,18.36,11.42,15.03,5.97,6.93,-2.39,-3.63,-11.34,-14.11,-18.72,-22.34,-23.03,-26.93,-23.67,-27.49,-21,-24.52,-16.08,-19.2,-10.38,-13.01,-5.34,-7.34,-2.06,-3.24,-1.09,-1.2,-2.35,-1.22,-5.3,-2.84,-9.04,-5.38,-12.64,-8.13,-15.31,-10.51,-16.57,-12.16,-16.3,-12.99,-14.73,-13.1,-12.34,-12.75,-9.7,-12.19,-7.36,-11.64,-5.74,-11.21,-5.07,-10.94,-5.35,-10.74,-6.43,-10.51,-8.04,-10.18,-9.83,-9.71,-11.51,-9.12,-12.82,-8.51,-13.6,-8,-13.8,-7.71,-13.44,-7.76,-12.63,-8.17,-11.52,-8.92,-10.27,-9.89,-9.06,-10.94,-8.04,-11.91,-7.32,-12.62,-6.98,-12.97,-7.06,-12.88,-7.53,-12.37,-8.33,-11.51,-9.35,-10.43,-10.46,-9.29,-11.5,-8.25,-12.35,-7.48,-12.89,-7.08,-13.03,-7.1,-12.77,-7.55,-12.13,-8.35,-11.21,-9.4,-10.12,-10.53,-9.02,-11.6,-8.07,-12.44,-7.39,-12.95,-7.08,-13.05,-7.19,-12.73,-7.7,-12.04,-8.54,-11.07,-9.6,-9.95,-10.72,-8.86,-11.75,-7.93,-12.54,-7.3,-12.99,-7.06,-13.02,-7.24,-12.64,-7.81,-11.89,-8.7,-10.89,-9.78,-9.77,-10.9,-8.69,-11.9,-7.8,-12.64,-7.23,-13.02,-7.06,-12.98,-7.31,-12.54,-7.94,-11.74,-8.87,-10.71,-9.97,-9.59,-11.08,-8.53,-12.04,-7.69,-12.73,-7.18,-13.04,-7.07,-12.94,-7.38,-12.43,-8.07,-11.59,-9.04,-10.53,-10.15,-9.41,-11.25,-8.37,-12.18,-7.58,-12.81,-7.13,-13.06,-7.09,-12.88,-7.47,-12.31,-8.21,-11.43,-9.21,-10.35,-10.33,-9.23,-11.41,-8.23,-12.3,-7.48,-12.88,-7.1,-13.06,-7.13,-12.82,-7.57,-12.19,-8.36,-11.26,-9.39,-10.16,-10.52,-9.05,-11.57,-8.08,-12.42,-7.39,-12.94,-7.07,-13.05,-7.17,-12.74,-7.68,-12.05,-8.52,-11.09,-9.57,-9.98,-10.7,-8.88,-11.73,-7.95,-12.53,-7.31,-12.98,-7.06,-13.02,-7.23,-12.65,-7.79,-11.91,-8.68,-10.91,-9.76,-9.8,-10.87,-8.71,-11.88,-7.82,-12.63,-7.24,-13.02,-7.06,-12.99,-7.3,-12.55,-7.92,-11.76,-8.84,-10.74,-9.94,-9.61,-11.05,-8.55,-12.02,-7.7,-12.72,-7.18,-13.04,-7.07,-12.95,-7.37,-12.45,-8.05,-11.61,-9.01,-10.56,-10.12,-9.43,-11.22,-8.4,-12.16,-7.59,-12.8,-7.14,-13.06,-7.09,-12.89,-7.46,-12.33,-8.19,-11.45,-9.19,-10.37,-10.31,-9.25,-11.39,-8.25,-12.29,-7.49,-12.87,-7.1,-13.06,-7.12,-12.83,-7.56,-12.21,-8.34,-11.28,-9.37,-10.19</v>
+        <v>17.86,2.8,14.07,7.46,9.3,12.7,4.71,17.35,1.43,20.38,0.3,21.15,1.66,19.59,5.3,16.15,10.48,11.76,16.1,7.58,20.97,4.71,24.08,3.96,24.83,5.62,23.17,9.45,19.62,14.65,15.12,20.12,10.82,24.67,7.84,27.32,6.93,27.51,8.35,25.24,11.82,21.1,16.56,16.02,21.42,11.17,25.23,7.54,27.05,6.18,26.35,6.88,22.9,9.84,17.78,13.49,11.79,17.39,5.88,20.07,1.81,20.34,-0.6,19.15,-0.38,13.5,0.88,6.87,3.37,0.91,5.63,-6.88,6.17,-11.04,5.81,-16.18,2.01,-15.61,-5.98,-15.06,-11.24,-15.78,-17.4,-17.27,-26.55,-20.85,-40.5,-18.73,-35.52,-20.54,-45.69,-29.08,-41.17,-41.69,-37.39,-44.01,-39.73,-55.97,-37.33,-43.6,-20.96,-58.79,-31.77,-49.28,-32.14,-39.95,-32.91,-24.58,-33.01,-11.88,-19.29,-13.17,-30.92,-3.66,-10.67,2.74,-12.78,22.18,-2.5,23.62,22.18,21.9,32.85,37.31,61.26,50.52,72.15,63.32,84.04,77.52,94.23,94.25,98.12,126.36,119.56,151.02,126.55,146.92,138.1,157.89,162.02,204.18,177.46,203.17,207.63,212.74,211.15,232.56,256.39,241.9,249.48,224.53,270.24,255.88,262.31,260.66,265.49,307.2,326.72,299.53,295.62,318.05,343.01,315.38,310.8,363.27,337.86,327.96,355.35,339.94,364.99,349.66,359.07,311.34,339.63,367.52,369.24,316.51,336.53,365.32,394.8,331.56,314.14,363.16,362.35,352.51,334.72,357.05,288.6,341.43,294.59,327.8,330.26,335.61,275.95,303.62,299.73,265.4,305.86,254.35,280.26,230.05,284.2,234.96,243.04,213.41,250.83,239.36,244.76,229.33,188.44,181.04,190.42,179.82,184.06,180.77,170.26,164.03,141.97,169.91,133.76,140.99,130.63,130.35,125.61,117.53,108.56,101.89,112.59,88.45,101.36,79.83,81.01,67.5,71.87,65.82,56.15,61.41,45.23,62.03,38.4,57.33,28.88,51.38,27.42,40.63,26.5,34.3,25.75,22.87,30.02,15.16,30.41,10.49,29.29,5.1,25.22,4.13,18.88,6.24,11.89,8.82,6.1,13.57,-1.55,14.9,-3.95,15.22,-5.45,13.18,-3.89,9.94,-2.42,3.68,2.82,-2.28,7.76,-5.28,11.58,-8.89,10.94,-8.42,12.09,-7.12,8.24,-1.52,1.46,3.25,-2.15,7.75,-7.74,11.46,-10.4,9.95,-9.57,11.65,-4.8,5.42,-1.36,3.36,1.45,-0.5,4.02,-5.57,8.42,-10.16,11.06,-12.92,6.56,-11.1,5.73,-8.84,-0.18,-0.91,-9.06,-0.14,-14.89,-0.67,-14.06,-1.18,-15.34,1.81,-19.06,-4.45,-11.99,-13.07,-13.74,-18.7,-7.25,-25.42,-5.62,-32.6,-14.89,-27.5,-16.27,-32.58,-17.69,-29.25,-20.16,-26.05,-32.37,-14.36,-40.54,-21.93,-42.33,-20.4,-36.89,-17.9,-41.9,-23.75,-28.13,-42.85,-33.26,-44.22,-25.25,-48.86,-32.57,-41.17,-34.69,-47.68,-37.53,-43.94,-27.12,-36.13,-51.29,-47.82,-43.59,-39.2,-63.05,-25.81,-61.19,-39.57,-50.31,-26.53,-38.21,-26.78,-48.14,-48.71,-49.9,-51.92,-39.14,-39.83,-24.13,-60.6,-49.21,-44.19,-31.1,-49.19,-49.82,-42.45,-42,-46.48,-42.2,-36.59,-54.77,-46.06,-45.92,-44.65,-64.53,-32.61,-60.69,-58.27,-36.52,-53.86,-50.78,-65.23,-30.86,-60.57,-48.39,-48.54,-55.48,-71.28,-44.74,-54.39,-45.97,-64.25,-44.27,-60.38,-72.45,-41.99,-65.18,-50.53,-75.25,-46.63,-73.39,-49.99,-49.63,-64.52,-51.03,-56.1,-60.45,-52.38,-48.24,-54.31,-55.02,-49.87,-29.55,-70.6,-43.06,-67.19,-42.49,-34.34,-61.51,-52.27,-54.28,-49.4,-47.82,-43.79,-53.15,-27.6,-39.02,-44.36,-34.81,-48.12,-35.31,-47.42,-37.01,-44.13,-27.41,-45.52,-31.07,-44.77,-28.45,-44.03,-32.67,-39.34,-19.74,-20.62,-36.59,-25.4,-31.38,-22.6,-30.5,-7.49,-37.32,-9.93,-21.72,-10.47,-16.93,-18.73,-12.96,-22.05,-6.17,-30.46,-2.34,-20.2,-1.17,-27.62,-9.99,-23.32,-11.5,-18.54,-11.87,-5.78,-17.16,-1.06,-16.77,-5.73,-24.5,2.62</v>
       </c>
     </row>
     <row r="62">
@@ -1078,7 +1078,7 @@
         <v>[L_03_标记]</v>
       </c>
       <c r="C62" t="str">
-        <v>99.6uv</v>
+        <v>a: 18.2ms -39.6uv b: 41.2ms 226.1uv</v>
       </c>
     </row>
     <row r="63">
@@ -1089,7 +1089,7 @@
         <v>[R_04_名字]</v>
       </c>
       <c r="C63" t="str">
-        <v>FERG(4)_lCone</v>
+        <v>FERG(4)_dRod</v>
       </c>
     </row>
     <row r="64">
@@ -1111,7 +1111,7 @@
         <v>[R_04_闪光]</v>
       </c>
       <c r="C65" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:0.30cd.m-2,5ms</v>
       </c>
     </row>
     <row r="66">
@@ -1122,7 +1122,7 @@
         <v>[R_04_闪光背景]</v>
       </c>
       <c r="C66" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="67">
@@ -1133,7 +1133,7 @@
         <v>[R_04_采样]</v>
       </c>
       <c r="C67" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="68">
@@ -1144,7 +1144,7 @@
         <v>[R_04_分析时间]</v>
       </c>
       <c r="C68" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="69">
@@ -1166,7 +1166,7 @@
         <v>[R_04_详细数据(uv)]</v>
       </c>
       <c r="C70" t="str">
-        <v>-0.56,1.1,-1.61,2.05,-2.43,2.71,-2.91,2.99,-2.98,2.85,-2.63,2.31,-1.91,1.45,-0.93,0.38,0.18,-0.74,1.27,-1.76,2.18,-2.53,2.79,-2.95,3,-2.95,2.79,-2.54,2.19,-1.77,1.28,-0.76,0.19,0.36,-0.93,1.42,-1.92,2.28,-2.65,2.81,-3.02,2.94,-2.98,2.62,-2.55,1.91,-1.81,0.88,-0.86,-0.34,0.11,-1.62,0.95,-2.82,1.48,-3.83,1.56,-4.59,1.08,-5.09,0.01,-5.4,-1.66,-5.62,-3.86,-5.92,-6.5,-6.5,-9.48,-7.55,-12.66,-9.25,-15.95,-11.72,-19.26,-15,-22.54,-19.08,-25.79,-23.84,-29.01,-29.08,-32.22,-34.54,-35.44,-39.91,-38.67,-44.86,-41.85,-49.1,-44.9,-52.33,-47.67,-54.34,-49.95,-54.99,-51.52,-54.21,-52.11,-52.02,-51.49,-48.5,-49.44,-43.76,-45.81,-37.96,-40.51,-31.26,-33.57,-23.78,-25.06,-15.62,-15.19,-6.86,-4.18,2.48,7.68,12.4,20.09,22.94,32.78,34.12,45.5,45.94,58.1,58.4,70.46,71.44,82.57,84.96,94.47,98.81,106.25,112.82,118.05,126.82,129.98,140.6,142.15,154.02,154.6,166.92,167.33,179.23,180.25,190.9,193.21,201.92,206,212.33,218.36,222.16,230.02,231.45,240.71,240.23,250.21,248.46,258.32,256.09,264.94,263,270.02,269.01,273.57,273.95,275.66,277.61,276.42,279.78,275.95,280.32,274.39,279.11,271.84,276.13,268.36,271.4,263.98,265.06,258.7,257.29,252.46,248.32,245.24,238.43,236.97,227.89,227.66,216.94,217.33,205.81,206.05,194.64,193.99,183.53,181.33,172.54,168.31,161.65,155.21,150.83,142.3,140.02,129.83,129.21,118.01,118.37,106.99,107.55,96.85,96.81,87.6,86.28,79.18,76.11,71.48,66.49,64.38,57.57,57.72,49.51,51.36,42.4,45.22,36.3,39.24,31.18,33.42,26.96,27.81,23.51,22.52,20.65,17.64,18.18,13.31,15.93,9.63,13.72,6.66,11.44,4.41,9.03,2.85,6.5,1.87,3.89,1.34,1.31,1.07,-1.11,0.88,-3.24,0.61,-4.98,0.11,-6.24,-0.72,-7.01,-1.89,-7.31,-3.38,-7.24,-5.11,-6.92,-6.96,-6.52,-8.76,-6.2,-10.39,-6.11,-11.71,-6.37,-12.65,-7.04,-13.18,-8.15,-13.32,-9.62,-13.16,-11.37,-12.83,-13.25,-12.49,-15.11,-12.28,-16.8,-12.36,-18.19,-12.82,-19.2,-13.71,-19.82,-15.04,-20.07,-16.74,-20.05,-18.69,-19.88,-20.75,-19.72,-22.76,-19.72,-24.58,-20.01,-26.07,-20.69,-27.17,-21.81,-27.86,-23.34,-28.19,-25.21,-28.25,-27.3,-28.17,-29.46,-28.11,-31.52,-28.22,-33.35,-28.62,-34.82,-29.4,-35.87,-30.6,-36.5,-32.18,-36.75,-34.06,-36.74,-36.11,-36.58,-38.19,-36.45,-40.12,-36.48,-41.76,-36.8,-43.02,-37.48,-43.83,-38.56,-44.19,-39.98,-44.17,-41.67,-43.87,-43.47,-43.44,-45.25,-43.02,-46.84,-42.78,-48.1,-42.82,-48.94,-43.21,-49.31,-43.97,-49.21,-45.04,-48.73,-46.34,-47.98,-47.73,-47.1,-49.04,-46.26,-50.13,-45.59,-50.86,-45.21,-51.15,-45.18,-50.95,-45.51,-50.3,-46.14,-49.27,-46.96,-47.99,-47.85,-46.61,-48.64,-45.29,-49.18,-44.17,-49.35,-43.35,-49.08,-42.9,-48.32,-42.8,-47.13,-43.01,-45.6,-43.41,-43.84,-43.85,-42.03,-44.19,-40.32,-44.27,-38.85,-43.98,-37.71,-43.26,-36.96,-42.08,-36.58,-40.5,-36.5,-38.61,-36.62,-36.55,-36.79,-34.48,-36.84,-32.56,-36.65,-30.92,-36.09,-29.66,-35.11,-28.8,-33.71,-28.34,-31.94,-28.19,-29.91,-28.23,-27.76,-28.32,-25.64,-28.3,-23.73,-28.02,-22.13,-27.4,-20.94,-26.37,-20.18,-24.94,-19.82,-23.18,-19.78,-21.19,-19.92,-19.13,-20.1,-17.15,-20.16,-15.4,-19.97,-14,-19.43,-13.03,-18.49,-12.51,-17.17,-12.38,-15.55,-12.56,-13.73,-12.92,-11.86,-13.29,-10.11,-13.53,-8.62,-13.5,-7.51,-13.11,-6.83,-12.32,-6.59,-11.17,-6.75,-9.72,-7.19,-8.11,-7.78,-6.47,-8.36,-4.98,-8.78,-3.76,-8.91,-2.93,-8.67,-2.53,-8.04,-2.58,-7.04,-2.99,-5.76,-3.67,-4.32</v>
+        <v>-7.45,2.61,-3.48,-0.75,1.08,-4.18,5.16,-6.66,7.8,-7.41,8.44,-6.14,7.01,-3.06,3.98,1.1,0.25,5.34,-3.16,8.61,-5.28,10.1,-5.53,9.47,-3.8,6.88,-0.57,3,3.35,-1.17,6.84,-4.57,9,-6.37,9.15,-6.14,7.19,-4.15,3.53,-0.89,-1.07,2.64,-5.38,5.17,-8.47,6.19,-9.84,5.35,-8.96,1.83,-6.58,-2.37,-3.26,-7.36,-0.36,-11.8,1.63,-14.64,0.29,-15.38,-1.37,-14.27,-6.13,-12.3,-10.23,-8.25,-16.57,-6.57,-21.22,-4.23,-21.94,-7.73,-22.81,-11.89,-23.2,-16.88,-23.12,-23.81,-14.77,-25.9,-13.39,-35.73,-15.68,-30.41,-22.07,-38.25,-23.77,-29.91,-25.15,-36.09,-40.65,-25.22,-32.58,-34.38,-48.37,-23.84,-42.72,-33.16,-44.64,-24.39,-30.92,-43.91,-21.35,-45.8,-24.25,-31.92,-22.49,-29.33,-25.37,-22.07,-1.07,-6.01,-5.97,-2,-0.21,4.82,12.76,6.89,17.85,30.68,27.68,43.36,41.98,36.77,36.76,43.75,82.98,63.82,86.21,83.02,102.39,72.24,107.02,107.95,136.28,124.88,153.6,129.86,126.39,164.58,163.97,184.49,185.28,188.39,179.06,196.34,220.19,247.96,237.87,247.88,240.67,230.64,281.49,250.37,283.01,253.67,300.5,257.11,313.52,294.23,303.8,300.2,341.2,304.51,291.88,296.94,335.68,341.38,318.56,377.13,355.7,312.1,372.39,331.77,360.27,393.28,396.88,370.13,406.7,363.45,386.29,394.09,373.74,353.7,327.66,377.03,376.54,396.21,351.67,324.51,361.77,325.92,328.01,353.7,363.04,357.64,346.68,344.5,359.43,328.73,282.52,295.82,328.34,292.95,275.68,284.18,289.4,284.72,247.13,275.56,249.04,255.99,242,243.81,218.87,251.11,196.93,219.3,204.12,198.48,197.18,174.55,179.61,157.94,165.33,162.1,147.6,145.12,144.46,121.38,138.23,129.11,139.03,107.27,119.87,124.89,100.35,103.25,83.92,104.04,70.2,93.24,77.88,77.73,75.82,61.44,69,58.49,63.22,49.26,57.5,40.52,49.02,30.36,50.23,31.12,38.12,34.77,32.44,30.79,27.3,29.87,20.33,33.29,12.14,27.77,13.25,22.48,13.98,17.65,14.65,10.15,15.66,4.93,18.48,1.34,16.72,0.88,15.5,0.45,10.53,5.06,6.91,6.65,1.23,8,-4.59,8.43,-5.17,8.28,-4.46,9.04,-2.88,4.03,-2.12,-4.38,-1.45,-5.47,4.6,-10.3,4.8,-11.38,-0.63,-12.7,-2.35,-11.94,-3.84,-6.27,-12.42,-3,-14.53,-4.69,-19.77,-5.41,-19.25,-11.62,-20.97,-11.74,-14.33,-15.65,-14.29,-21.81,-10.57,-29.19,-12.03,-26.31,-16.21,-24,-22.83,-30.51,-25.41,-30.53,-21.92,-26.06,-25.64,-18.62,-34.84,-20.92,-38.16,-22.63,-34.24,-34.33,-28.7,-30.72,-22.69,-44.31,-24.47,-41.12,-24.06,-38.31,-25.46,-42.85,-36.48,-43.4,-24.06,-35.21,-31.16,-42.98,-33.51,-36.7,-39.95,-33.78,-43.32,-39.66,-37.44,-28.36,-35.06,-34.27,-31.94,-56.12,-45.28,-56.36,-38.62,-59.8,-37.63,-47.63,-52.09,-48.67,-29.22,-39.87,-47.85,-56.94,-66.71,-27.95,-55.3,-36.74,-56.58,-48.43,-66.57,-53.28,-70.42,-57.18,-62.78,-54.33,-60.71,-72.97,-55.05,-59.07,-33.88,-64.18,-40.78,-66.37,-48.34,-67.78,-61.37,-45.93,-80.1,-37.52,-74.91,-68.33,-63.68,-42.31,-51.01,-46.36,-66.29,-69.99,-76.36,-48.82,-61.14,-58.34,-55.34,-72.72,-52.25,-77.6,-55.86,-70.85,-63.63,-69.43,-63.85,-57.7,-51.2,-52.79,-53.86,-45.37,-50.85,-31.5,-65.37,-41.24,-57.15,-53.95,-50.99,-61.87,-48.85,-61.92,-49.61,-41.73,-48.52,-42.43,-42.52,-60.4,-34.89,-43.58,-49.48,-35.11,-46.86,-41.17,-50.75,-19.71,-38.8,-26.61,-32.98,-17.89,-35.28,-27.03,-34.34,-35.79,-22.74,-36.44,-20.77,-44.59,-13.89,-37.54,-23.87,-25.26,-12.74,-26.99,-25.79,-23.97,-22.97,-15.89,-28.26,-15.38,-32.77,-10.49,-23.55,-12.19,-32.13,-23.4,-26.79,-23.74,-16.4,-26.52,-15.73,-24.33,-9.78,-25.51,-5.72,-24.87,-12,-19.34</v>
       </c>
     </row>
     <row r="71">
@@ -1177,7 +1177,7 @@
         <v>[R_04_标记]</v>
       </c>
       <c r="C71" t="str">
-        <v>a: 21.4ms -64.2uv b: 46.4ms 278.2uv</v>
+        <v>a: 20.5ms -38.9uv b: 45.8ms 274.5uv</v>
       </c>
     </row>
     <row r="72">
@@ -1188,7 +1188,7 @@
         <v>[L_04_名字]</v>
       </c>
       <c r="C72" t="str">
-        <v>FERG(4)_lCone</v>
+        <v>FERG(4)_dRod</v>
       </c>
     </row>
     <row r="73">
@@ -1210,7 +1210,7 @@
         <v>[L_04_闪光]</v>
       </c>
       <c r="C74" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:0.30cd.m-2,5ms</v>
       </c>
     </row>
     <row r="75">
@@ -1221,7 +1221,7 @@
         <v>[L_04_闪光背景]</v>
       </c>
       <c r="C75" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="76">
@@ -1232,7 +1232,7 @@
         <v>[L_04_采样]</v>
       </c>
       <c r="C76" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="77">
@@ -1243,7 +1243,7 @@
         <v>[L_04_分析时间]</v>
       </c>
       <c r="C77" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="78">
@@ -1265,7 +1265,7 @@
         <v>[L_04_详细数据(uv)]</v>
       </c>
       <c r="C79" t="str">
-        <v>-1.59,2.7,-2.98,2.36,-1.03,-0.62,2.08,-2.91,2.85,-1.93,0.42,1.22,-2.48,3,-2.6,1.41,0.2,-1.76,2.78,-2.96,2.23,-0.83,-0.82,2.22,-2.95,2.78,-1.77,0.22,1.4,-2.6,3,-2.5,1.22,0.4,-1.93,2.84,-2.93,2.07,-0.66,-1.05,2.31,-3.04,2.63,-1.69,-0.1,1.44,-2.87,2.77,-2.64,0.71,0.2,-2.57,2.3,-3.59,1.06,-1.49,-2.47,0.97,-4.78,0.5,-3.89,-3.08,-1.62,-6.68,-1.56,-7.44,-5.11,-5.99,-9.94,-5.79,-12.65,-9.29,-12.6,-15.17,-12.69,-19.87,-16.06,-21.57,-22.57,-22.17,-28.89,-25.14,-32.19,-31.48,-33.16,-38.52,-35.15,-42.72,-40.19,-43.5,-46.57,-43.69,-50.53,-46.13,-50.3,-50.33,-47.89,-52.8,-46.68,-50.82,-47.45,-45.41,-47.45,-40.05,-43.41,-36.79,-35.18,-33.93,-25.98,-28,-18.82,-17.73,-13.25,-5.63,-5.98,4.74,5.28,12.57,19.09,20.62,31.77,31.93,41.41,46.33,49.89,60.52,60.68,71.66,74.87,80.55,89.91,90.63,102.38,104.11,111.84,119.44,121.27,133,133.68,143.17,148.7,152.04,162.93,163.05,173.7,177.03,181.98,191.2,191.2,202.17,203.32,209.66,216.46,216.7,226.97,226.09,233.34,237.15,237.82,246.37,243.76,251.22,251.73,252.9,258.82,254.91,261.77,259.02,260.62,263.26,258.58,264.06,258.41,260.28,259.33,254.45,257.88,249.99,251.87,247.41,242.87,243.78,234.55,236.13,228.62,224.87,223.04,213.46,214.42,204.62,201.97,197.44,188.49,188.53,177.41,175.95,169.05,161.56,160.39,149.04,148.65,139.9,134.46,131.92,121.35,121.73,111.83,108.73,104.73,95.83,96.53,86.27,85.46,80.05,73.47,73.97,64.15,65.28,58.68,54.76,54.56,45.91,48.4,40.97,39.75,38.43,31.58,34.71,26.91,28.14,25.45,20.82,23.82,16.24,19.38,15.3,13.11,15.28,8.5,12.86,7.58,7.8,8.6,3.16,7.96,1.85,4.22,3.32,-0.33,4.11,-2.27,1.76,-0.91,-2.5,0.89,-5.15,-0.09,-4.35,-3.82,-2.02,-7.11,-1.73,-7.17,-4.69,-4.79,-8.4,-3.45,-9.49,-5.44,-7.51,-9.28,-5.42,-11.4,-6.33,-10.17,-9.95,-7.71,-12.97,-7.54,-12.75,-10.61,-10.32,-14.25,-9.18,-15.18,-11.43,-13.16,-15.36,-11.3,-17.41,-12.55,-16.14,-16.38,-13.88,-19.4,-14.07,-19.14,-17.44,-16.84,-21.16,-16.05,-22.04,-18.65,-20.08,-22.72,-18.5,-24.72,-20.11,-23.45,-24.15,-21.38,-27.14,-21.91,-26.79,-25.52,-24.58,-29.23,-24.07,-29.97,-26.92,-27.99,-31.02,-26.61,-32.86,-28.46,-31.45,-32.54,-29.46,-35.35,-30.18,-34.78,-33.86,-32.52,-37.4,-32.13,-37.84,-35.06,-35.68,-38.99,-34.31,-40.47,-36.21,-38.76,-40.15,-36.66,-42.58,-37.39,-41.6,-40.94,-39.1,-44.09,-38.65,-44.04,-41.44,-41.51,-45,-39.99,-45.94,-41.75,-43.75,-45.34,-41.38,-47.2,-41.94,-45.65,-45.18,-42.78,-47.77,-42.1,-47.08,-44.61,-44.07,-47.65,-42.26,-47.91,-43.75,-45.14,-46.88,-42.42,-48.07,-42.72,-45.87,-45.55,-42.57,-47.52,-41.63,-46.15,-43.8,-42.63,-46.28,-40.53,-45.86,-41.75,-42.53,-44.41,-39.49,-44.96,-39.56,-42.17,-42.03,-38.5,-43.42,-37.36,-41.45,-39.27,-37.53,-41.28,-35.26,-40.29,-36.31,-36.53,-38.61,-33.31,-38.65,-33.3,-35.42,-35.54,-31.56,-36.51,-30.4,-34.11,-32.21,-29.99,-33.91,-27.72,-32.53,-28.79,-28.55,-30.91,-25.35,-30.62,-25.44,-27.16,-27.63,-23.32,-28.37,-22.33,-25.74,-24.21,-21.62,-25.78,-19.56,-24.2,-20.81,-20.2,-22.92,-17.22,-22.48,-17.58,-18.97,-19.87,-15.33,-20.53,-14.66,-17.84,-16.77,-13.88,-18.33,-12.17,-16.7,-13.73,-12.8,-15.93,-10.16,-15.46,-10.91,-12.01,-13.39,-8.67,-14.04,-8.42,-11.38,-10.8,-7.67,-12.43,-6.38,-10.79,-8.29,-7.08,-10.62,-4.83,-10.14,-5.98,-6.8,-8.66,-3.8,-9.32,-3.98,-6.71,-6.63,-3.26,-8.3,-2.38,-6.67,-4.63,-3.13,-7.05,-1.26,-6.55,-2.78</v>
+        <v>18.16,8.78,22.18,6.62,25.78,5.03,28.78,4.15,31.02,4.08,32.4,4.85,32.86,6.46,32.42,8.83,31.14,11.86,29.12,15.37,26.53,19.17,23.53,23.05,20.35,26.78,17.19,30.13,14.26,32.91,11.75,34.93,9.81,36.06,8.55,36.23,8.04,35.4,8.29,33.62,9.28,30.96,10.89,27.54,12.99,23.58,15.42,19.25,17.99,14.78,20.54,10.44,22.78,6.4,24.53,3.02,25.75,0.25,26.22,-1.8,25.8,-2.7,24.31,-3.1,21.98,-2.58,19.65,-0.6,15.56,1.31,11.81,4.14,7.47,5.47,3.21,8.91,-0.55,10.2,-5.86,12.22,-9.17,12.07,-11.44,12.93,-15.04,12.14,-18.63,13.06,-17.49,10.41,-13.15,0.85,-20.87,-1.72,-16.48,-8.89,-9.81,-12.38,-17.73,-15.42,-7.38,-12.2,-14.28,-23.27,-15.2,-27.05,-8.79,-34.43,-6.82,-22.9,-4.09,-27.75,-0.18,-36.55,-4.41,-27.4,-12.93,-26.19,5.64,-3.24,11.38,-5.12,5.45,10.88,-9.23,2.26,0.39,40.59,1.39,21.77,22.29,36.13,34.82,42.17,30.92,70.03,59.83,82.53,60.9,90.03,85.54,101.64,74.09,108.09,114.4,124.74,118.27,155.71,136.64,159.75,185.36,182.49,160.24,193.77,186.35,165.66,196.36,182.89,251,196.51,264.95,210.25,280.43,267.18,263.83,265.31,263.64,290.97,328.77,271.07,326.86,343.91,334.77,312.26,357.78,357.53,366.84,364.74,361.99,394.02,364.19,333.22,320.54,407.8,393.44,374.1,324.24,385.91,342.9,410.2,355.18,380.28,410.6,416.97,356.88,406.22,366.37,403.88,339.18,364.77,392.67,383.06,367.98,342.23,384.27,347.41,346.81,329.67,331.56,359.21,325.87,350.57,353.9,303.51,357.84,307.7,281.97,303.99,278.85,303.59,271.78,296.56,241.19,276.04,270.1,254.26,241.87,240.13,217.24,221.59,196.62,199.19,169.46,213.72,179.95,187.83,172.55,185.11,154.75,179.73,138.29,138.68,117.48,133.88,128.22,113.94,99.15,117.81,99.47,89.6,91.66,91.66,86.38,79.92,86.39,67.18,90.27,60.68,83.06,52.31,71.23,49.86,66.85,38.46,61.78,40.68,58.85,33.65,54.54,37.39,46.96,36.58,38.57,33.83,32.18,37.83,28.4,36.98,22.41,39.84,18.73,40.53,17.22,42.02,12.7,39.68,11.95,39.24,12.26,36.58,9.95,32.56,12.8,29.7,14,23.87,14.29,21.8,19.47,15.45,19.87,9.51,23.79,6.81,23.84,1.69,23.11,1.41,24.14,-0.98,23.7,-3.91,23.77,-7.6,21.44,-7.44,16.95,-3.64,8.71,-6.9,7.92,-2.73,3.77,-3.51,-2.58,4.06,-11.39,1.15,-16.28,5.34,-20.06,3,-20.55,7.45,-27.74,-1.46,-30.12,4.01,-23.2,-1.46,-22.89,1.51,-19.91,-10.92,-27.09,-9.94,-24.96,-15.1,-17.94,-11.13,-19.9,-20.28,-9.83,-18.15,-15.39,-31.18,-4.37,-27.64,-13.29,-24.44,-10.62,-24.33,-15.61,-32.24,-1.57,-26.17,-7.73,-38.77,-7.1,-22.77,-12.17,-35.48,-18.78,-14.61,-26.16,-12.11,-16.36,-20.26,-44.16,-12.96,-31.83,-17.06,-28.86,-4.24,-39,-16.28,-30.71,-10.51,-47.63,-10.2,-35.93,-26.06,-33.05,-28.38,-45.97,-20.68,-41.22,-28.31,-41.83,-30.73,-28.93,-49.51,-37.33,-33.82,-22.33,-59.22,-39.68,-49.14,-42.43,-48.87,-27.65,-67.98,-31.97,-57.98,-28.58,-68.43,-30.32,-59.7,-45.69,-41.07,-31.66,-67.2,-51.36,-43.15,-37.19,-41.96,-50.47,-42.33,-75.55,-52.75,-62.45,-27.71,-60.25,-32.7,-73.7,-31.44,-68.32,-22.89,-57.05,-30.23,-68.68,-48.52,-53.56,-22.09,-40.69,-37.51,-32.48,-41.96,-44.48,-35.9,-50.05,-44.54,-25.47,-32.45,-26.48,-39.04,-18.94,-43.25,-27.38,-37.72,-10.05,-46.81,-18.9,-42.21,-22.68,-27.81,-11.79,-34.36,-16.88,-37.06,-23.7,-13.53,-19.8,-23.16,-17.41,-6.64,-17.96,-6.56,-21.87,-7.28,-26.22,1.86,-24.96,-10.53,-26.95,5.19,-34.04,-1.62,-33.71,6.88,-29.08,1.63,-15.96,-12.19,-18.43,-6.92,-19.11,-16.54,-8.36,-14.07</v>
       </c>
     </row>
     <row r="80">
@@ -1276,7 +1276,7 @@
         <v>[L_04_标记]</v>
       </c>
       <c r="C80" t="str">
-        <v>a: 21.4ms -60.3uv b: 46.4ms 261.5uv</v>
+        <v>a: 20.3ms -38.4uv b: 45.7ms 274.8uv</v>
       </c>
     </row>
     <row r="81">
@@ -1287,7 +1287,7 @@
         <v>[R_05_名字]</v>
       </c>
       <c r="C81" t="str">
-        <v>FERG(5)_Flicker</v>
+        <v>FERG(5)_dRod</v>
       </c>
     </row>
     <row r="82">
@@ -1298,7 +1298,7 @@
         <v>[R_05_放大器]</v>
       </c>
       <c r="C82" t="str">
-        <v>1-300 Hz</v>
+        <v>1-75 Hz</v>
       </c>
     </row>
     <row r="83">
@@ -1309,7 +1309,7 @@
         <v>[R_05_闪光]</v>
       </c>
       <c r="C83" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:1.0cd.m-2,5ms</v>
       </c>
     </row>
     <row r="84">
@@ -1320,7 +1320,7 @@
         <v>[R_05_闪光背景]</v>
       </c>
       <c r="C84" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="85">
@@ -1331,7 +1331,7 @@
         <v>[R_05_采样]</v>
       </c>
       <c r="C85" t="str">
-        <v>刺激间隔: 50.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="86">
@@ -1342,7 +1342,7 @@
         <v>[R_05_分析时间]</v>
       </c>
       <c r="C86" t="str">
-        <v>500 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="87">
@@ -1364,7 +1364,7 @@
         <v>[R_05_详细数据(uv)]</v>
       </c>
       <c r="C88" t="str">
-        <v>61.68,68.37,64.91,72.28,70.69,72.66,76.67,72.72,79.23,74.89,77.38,77.99,73.79,78.43,71.66,74.17,71.13,67.01,69.07,60.54,62.64,56.2,52.57,51.72,42.42,43.81,34.73,32.02,28.36,19.42,19.97,9.38,7.97,2.01,-5.43,-5.73,-16.48,-16.36,-23.85,-28.83,-29.9,-39.47,-37.81,-45.9,-47.83,-49.54,-56.82,-53.87,-61.66,-60.38,-62.65,-66.87,-63.13,-69.84,-65.7,-68.45,-69.33,-65.49,-70.56,-64.32,-67.5,-65.21,-62.03,-65.14,-57.85,-61.36,-56.47,-54.62,-55.67,-48.48,-52.15,-45.5,-45.41,-44.48,-38.43,-41.97,-34.48,-36.27,-33.53,-29.39,-32.38,-24.93,-28.32,-24.01,-22.16,-24.08,-17.37,-21.74,-16.13,-16.52,-16.83,-11.36,-15.82,-9.23,-11.42,-9.68,-5.7,-9.29,-2.08,-5.38,-1.37,1.07,-0.8,6.57,2.98,9.15,10.13,10.57,17.54,14.39,22.28,21.94,24.86,30.79,28.63,37.42,35.91,41.04,45.27,44.39,53.01,50.48,57.14,59.06,59.45,66.72,63.33,70.53,69.73,71.15,75.98,71.9,78.55,74.89,76.92,78.5,74,79.08,72.78,74.98,72.92,68.36,71.08,62.75,64.72,59.13,54.97,54.9,45.49,46.92,38.46,35.17,32.33,22.97,23.72,13.44,11.46,6.24,-1.88,-1.84,-12.63,-13,-19.91,-25.74,-26.37,-36.33,-35,-42.75,-45.58,-46.8,-54.74,-51.91,-59.61,-59.17,-60.93,-66,-62.16,-69.02,-65.54,-67.81,-69.61,-65.44,-70.88,-65.03,-67.81,-66.4,-62.68,-66.34,-59.12,-62.37,-58.21,-55.68,-57.39,-49.96,-53.54,-47.39,-46.6,-46.37,-39.81,-43.47,-36.2,-37.37,-35.32,-30.48,-33.8,-26.3,-29.24,-25.55,-22.92,-25.37,-18.38,-22.54,-17.43,-17.07,-18.06,-12.13,-16.67,-10.4,-11.99,-11.01,-6.44,-10.4,-3.31,-6.22,-2.97,0.13,-2.35,5.13,1.66,7.2,8.82,8.5,15.81,12.53,19.99,20.22,22.35,28.83,26.33,34.97,33.92,38.34,43.28,41.91,50.7,48.48,54.62,57.35,57.18,64.94,61.68,68.63,68.65,69.51,75.09,70.97,77.67,74.75,76.29,78.8,74.08,79.49,73.75,75.59,74.51,69.57,72.86,64.84,66.59,61.91,57.24,57.91,48.48,49.87,42.12,38.24,36.19,26.51,27.38,17.51,14.93,10.45,1.73,2.03,-8.69,-9.6,-15.9,-22.54,-22.79,-33.03,-32.11,-39.44,-43.18,-43.93,-52.45,-49.85,-57.36,-57.81,-59.06,-64.93,-61.06,-67.99,-65.25,-67.02,-69.72,-65.28,-71.01,-65.65,-67.99,-67.47,-63.26,-67.39,-60.36,-63.27,-59.89,-56.72,-59.04,-51.46,-54.87,-49.29,-47.79,-48.24,-41.25,-44.93,-37.99,-38.48,-37.13,-31.64,-35.2,-27.77,-30.18,-27.13,-23.74,-26.65,-19.47,-23.33,-18.76,-17.65,-19.28,-12.94,-17.47,-11.6,-12.53,-12.31,-7.18,-11.43,-4.54,-6.99,-4.51,-0.79,-3.8,3.7,0.45,5.29,7.57,6.52,14.09,10.79,17.73,18.57,19.9,26.86,24.12,32.5,31.97,35.64,41.26,39.47,48.32,46.49,52.03,55.57,54.87,63.03,59.99,66.59,67.46,67.76,74.03,69.95,76.59,74.46,75.5,78.89,74.02,79.68,74.57,76,75.89,70.63,74.42,66.79,68.26,64.53,59.37,60.72,51.39,52.66,45.68,41.22,39.94,30.02,30.93,21.57,18.36,14.64,5.38,5.88,-4.67,-6.18,-11.82,-19.24,-19.16,-29.57,-29.14,-35.99,-40.63,-40.96,-49.97,-47.67,-54.92,-56.28,-57.04,-63.65,-59.85,-66.75,-64.81,-66.07,-69.65,-65.02,-70.95,-66.17,-68.03,-68.41,-63.78,-68.3,-61.55,-64.07,-61.5,-57.72,-60.59,-52.97,-56.13,-51.19,-48.98,-50.08,-42.74,-46.36,-39.83,-39.61,-38.95,-32.87,-36.6,-29.31,-31.12,-28.75,-24.63,-27.92,-20.64,-24.11,-20.14,-18.26,-20.47,-13.81,-18.23,-12.82,-13.06,-13.57,-7.95,-12.38,-5.78,-7.7,-6,-1.68,-5.16,2.27,-0.66,3.44,6.36,4.65,12.38,9.15,15.5,16.97,17.53,24.9,21.99,30.03,30.06,32.97,39.2,37.06,45.88,44.5,49.4,53.71,52.54,60.99,58.25,64.43</v>
+        <v>0.57,-2.51,6.83,-4.82,5.02,1.05,-2.12,7.18,-4.54,5.22,1.2,-2.06,7.18,-4.6,5.07,1.01,-2.34,6.84,-5.01,4.59,0.49,-2.93,6.21,-5.69,3.85,-0.28,-3.77,5.36,-6.58,2.92,-1.21,-4.74,4.39,-7.56,1.92,-2.18,-5.75,3.39,-8.54,0.93,-3.15,-6.68,2.49,-9.45,0.04,-4.02,-7.6,1.7,-10.26,-0.88,-4.88,-8.3,0.73,-11.4,-1.98,-5.9,-9.65,-0.26,-12.34,-2.94,-7.24,-11.29,-1.6,-14.36,-6.06,-10.66,-15.34,-5.75,-18.45,-9.86,-14.58,-19.38,-12.79,-23.74,-15.41,-24.48,-28.04,-20.4,-32.07,-23.2,-25.77,-39.98,-23.97,-45.59,-32.33,-41.38,-49,-45.58,-45.5,-48.29,-56.04,-60.46,-40.69,-63.37,-45.85,-47.12,-68.18,-45.54,-70.44,-42.06,-63.69,-70.05,-40.55,-49.29,-56.34,-61.11,-50.39,-38.71,-53.41,-40.77,-46.26,-28.99,-21.43,-26.71,-18.73,0.79,-7.21,5.51,4.47,14.76,19.64,31.24,38.05,41.73,65.85,50.56,64.32,86.9,78.05,81.45,92.79,104.08,117.57,106.57,140.34,128.45,158.99,142.3,171.17,169.98,203.26,192.02,198.89,218.84,232.44,232.1,204.54,229.25,232.11,238.71,256.88,290.6,298.67,264.81,267.28,335.94,322.31,341.02,295.27,357.66,353.37,344.13,355.25,303.44,347.8,390.46,359.71,346.82,349.4,362.3,388.11,362.61,335.51,350.82,387.96,384.16,384.17,381.4,378.7,405.65,352.11,352.01,368.01,370.37,338.87,356.07,324.75,296.83,282.11,293.69,314.08,268.09,309.61,263.36,286.05,296.23,251.55,272.3,273.58,220.26,217.57,232.77,236.89,214.58,211.87,180.37,165.74,172.03,187.27,151.82,165.65,160.12,165.84,128.52,145.98,134.32,113.16,109.52,87.68,100.31,86.36,92.67,80.73,72.95,79.88,67.27,57.1,64.93,42.28,58.59,45.01,42.03,48.18,33.55,38.74,31.04,21.62,29.87,21.04,27.39,17.61,16.37,21,9.29,15.27,12.15,5.5,16.23,2.78,10.91,8.35,2.2,11.14,-1.7,8.85,3.74,-0.12,9.31,-3.75,5.21,1.48,-1.95,7.34,-3.92,3.83,0.17,-3.28,6.65,-6.2,3.33,-1.38,-5.81,3.68,-8.37,1.86,-2.05,-6.62,3.23,-8.85,1.17,-2.24,-6.99,0.11,-9.8,-0.66,-5.77,-8.72,1.78,-14.73,-3.25,-5.02,-13.69,-2.41,-16.81,-5.53,-10.34,-14.99,-8.02,-18.87,-11.94,-9.79,-19.47,-10.13,-23.07,-15.35,-14.17,-22.65,-12.94,-27.51,-16.51,-15.92,-22.66,-9.98,-30.64,-22.68,-23.62,-24.16,-16.24,-24.69,-25.68,-20.68,-33.05,-22.89,-34.13,-27.87,-24.12,-31.74,-15.57,-34.92,-18.76,-34.35,-30.36,-19.55,-38.79,-30.18,-30.48,-27.59,-19.37,-45.06,-29.24,-25.96,-43.97,-34.59,-41.72,-37.66,-24.91,-44.79,-35.8,-52.84,-33.32,-27.33,-47.93,-25.39,-34.05,-47.54,-39.63,-47.75,-24.98,-37.99,-51.14,-44.1,-46.52,-25.54,-57.52,-31.51,-40.45,-52.73,-33.25,-40.58,-43.58,-37.49,-39.71,-56.77,-54.27,-51.9,-63.57,-60.97,-37.56,-74.81,-49.71,-43.84,-54.72,-55.28,-76.47,-48.53,-53.94,-71.53,-36.3,-80.56,-52.54,-74.3,-73.32,-51.32,-72.27,-68.1,-69.9,-70.65,-40.73,-60.25,-52.26,-66.48,-66.93,-65.74,-82.33,-71.41,-55.36,-60.28,-56.26,-52.2,-42.78,-54.83,-69.55,-59.16,-59.02,-51.17,-65.12,-59.06,-53.17,-72.44,-63.5,-67.56,-67.12,-49.2,-78.61,-70.09,-61.98,-71.96,-62.82,-72.71,-38.02,-65.34,-66.27,-47.13,-68.85,-41.9,-46.3,-50.03,-53.89,-49.82,-38.63,-35.97,-44.82,-43.13,-45.87,-38.64,-31.87,-43.35,-40.76,-51.19,-29.02,-33.27,-51.31,-20.62,-54.44,-29.02,-29.85,-49.22,-24.95,-43.85,-24.98,-32.73,-34.29,-31.92,-32.15,-23.43,-38.72,-40.37,-30.47,-41.38,-27.74,-29.27,-34.12,-18.02,-40.1,-22.14,-23.86,-28.1,-15.72,-29,-20.69,-18.86,-25.42,-20.77,-28.57,-22.81,-24.43,-24.23,-20.17,-28.17,-18.48,-18.44,-27.04,-9.51,-20.94,-12.97,-15.18,-25.83,-13.48,-20.95,-19.01</v>
       </c>
     </row>
     <row r="89">
@@ -1375,7 +1375,7 @@
         <v>[R_05_标记]</v>
       </c>
       <c r="C89" t="str">
-        <v>幅值: 62.1uv 相位: 35°</v>
+        <v>a: 22.9ms -44.2uv b: 49.2ms 327.3uv</v>
       </c>
     </row>
     <row r="90">
@@ -1386,7 +1386,7 @@
         <v>[L_05_名字]</v>
       </c>
       <c r="C90" t="str">
-        <v>FERG(5)_Flicker</v>
+        <v>FERG(5)_dRod</v>
       </c>
     </row>
     <row r="91">
@@ -1397,7 +1397,7 @@
         <v>[L_05_放大器]</v>
       </c>
       <c r="C91" t="str">
-        <v>1-300 Hz</v>
+        <v>1-75 Hz</v>
       </c>
     </row>
     <row r="92">
@@ -1408,7 +1408,7 @@
         <v>[L_05_闪光]</v>
       </c>
       <c r="C92" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:1.0cd.m-2,5ms</v>
       </c>
     </row>
     <row r="93">
@@ -1419,7 +1419,7 @@
         <v>[L_05_闪光背景]</v>
       </c>
       <c r="C93" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="94">
@@ -1430,7 +1430,7 @@
         <v>[L_05_采样]</v>
       </c>
       <c r="C94" t="str">
-        <v>刺激间隔: 50.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="95">
@@ -1441,7 +1441,7 @@
         <v>[L_05_分析时间]</v>
       </c>
       <c r="C95" t="str">
-        <v>500 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="96">
@@ -1463,7 +1463,7 @@
         <v>[L_05_详细数据(uv)]</v>
       </c>
       <c r="C97" t="str">
-        <v>57.92,64.86,62.42,63.13,68.84,64.76,66.71,70.47,65.23,68.13,69.41,63.6,67,65.52,59.73,63.04,58.82,53.59,56.18,49.52,45.27,46.56,38.03,35,34.52,24.87,23.11,20.6,10.69,10.07,5.46,-3.82,-3.6,-10.09,-17.97,-17.31,-25.24,-31.08,-30.43,-39.18,-42.61,-42.4,-51.19,-52.1,-52.67,-60.7,-59.27,-60.81,-67.32,-63.96,-66.5,-70.88,-66.19,-69.58,-71.43,-66.13,-70.05,-69.21,-64.03,-68.03,-64.64,-60.25,-63.83,-58.29,-55.2,-57.83,-50.77,-49.27,-50.53,-42.71,-42.86,-42.45,-34.7,-36.31,-34.1,-27.21,-29.89,-25.96,-20.58,-23.77,-18.39,-14.98,-18.06,-11.67,-10.42,-12.76,-5.92,-6.74,-7.8,-1.13,-3.67,-3.07,2.85,-0.84,1.6,6.26,2.13,6.35,9.43,5.62,11.34,12.69,9.93,16.66,16.36,15.24,22.38,20.69,21.58,28.47,25.84,28.85,34.83,31.8,36.75,41.28,38.43,44.89,47.58,45.42,52.75,53.41,52.37,59.76,58.42,58.73,65.35,62.25,63.93,68.99,64.55,67.39,70.24,65,68.6,68.83,63.35,67.17,64.62,59.46,62.85,57.66,53.28,55.6,48.2,44.89,45.6,36.64,34.53,33.22,23.51,22.53,19.02,9.43,9.35,3.73,-4.91,-4.45,-11.86,-18.84,-18.28,-26.91,-31.72,-31.5,-40.63,-43.02,-43.5,-52.33,-52.32,-53.75,-61.45,-59.33,-61.8,-67.65,-63.91,-67.33,-70.8,-66.09,-70.18,-70.98,-66.01,-70.36,-68.46,-63.92,-68.03,-63.7,-60.17,-63.51,-57.26,-55.13,-57.22,-49.76,-49.21,-49.67,-41.82,-42.78,-41.42,-33.99,-36.18,-32.97,-26.73,-29.67,-24.83,-20.34,-23.44,-17.35,-14.95,-17.59,-10.78,-10.54,-12.16,-5.24,-6.94,-7.08,-0.68,-3.86,-2.26,3.07,-0.93,2.46,6.3,2.21,7.22,9.33,5.92,12.16,12.53,10.47,17.4,16.22,16.02,23,20.65,22.56,28.95,25.95,29.95,35.16,32.11,37.9,41.48,38.94,45.98,47.65,46.12,53.68,53.39,53.19,60.45,58.33,59.6,65.73,62.13,64.75,69.02,64.41,68.06,69.92,64.85,69.02,68.17,63.19,67.25,63.67,59.26,62.55,56.5,53.02,54.9,46.92,44.55,44.51,35.31,34.06,31.81,22.23,21.91,17.38,8.27,8.58,1.97,-5.9,-5.39,-13.61,-19.62,-19.35,-28.53,-32.3,-32.65,-42,-43.41,-44.69,-53.36,-52.54,-54.89,-62.08,-59.42,-62.82,-67.87,-63.93,-68.14,-70.62,-66.06,-70.73,-70.45,-65.97,-70.6,-67.67,-63.89,-67.93,-62.76,-60.15,-63.08,-56.27,-55.11,-56.5,-48.82,-49.17,-48.72,-41.02,-42.68,-40.31,-33.39,-35.99,-31.82,-26.36,-29.37,-23.7,-20.18,-23.01,-16.34,-14.97,-17.03,-9.97,-10.68,-11.47,-4.66,-7.12,-6.29,-0.34,-3.99,-1.41,3.2,-0.95,3.32,6.24,2.39,8.05,9.17,6.33,12.92,12.34,11.12,18.06,16.09,16.88,23.52,20.66,23.59,29.33,26.14,31.07,35.41,32.51,39.02,41.6,39.56,47.01,47.69,46.91,54.52,53.36,54.09,61.03,58.28,60.51,65.99,62.07,65.57,68.94,64.35,68.69,69.5,64.78,69.36,67.44,63.1,67.24,62.7,59.13,62.13,55.36,52.81,54.07,45.68,44.21,43.31,34.07,33.57,30.31,21.05,21.24,15.68,7.21,7.72,0.19,-6.79,-6.41,-15.34,-20.33,-20.51,-30.08,-32.83,-33.9,-43.28,-43.78,-45.95,-54.27,-52.78,-56.07,-62.59,-59.57,-63.83,-67.97,-64.02,-68.92,-70.34,-66.13,-71.21,-69.86,-66.03,-70.73,-66.86,-63.94,-67.72,-61.83,-60.19,-62.54,-55.33,-55.11,-55.67,-47.97,-49.11,-47.69,-40.32,-42.53,-39.16,-32.9,-35.73,-30.64,-26.08,-28.97,-22.61,-20.1,-22.47,-15.41,-15.04,-16.37,-9.24,-10.83,-10.7,-4.18,-7.27,-5.45,-0.1,-4.06,-0.54,3.22,-0.86,4.18,6.12,2.67,8.84,8.97,6.84,13.61,12.15,11.86,18.62,16,17.81,23.95,20.73,24.65,29.62,26.43,32.19,35.58,33.03,40.1,41.68,40.28,47.96,47.71,47.79,55.26,53.36,55.05,61.5,58.27</v>
+        <v>-2.85,-8.52,4.78,-12.21,5.07,-7.71,-1.93,1.19,-9.63,6.68,-10.87,3.94,-4.4,-4.44,3.99,-10.86,6.7,-9.56,1.2,-1.84,-7.69,5.13,-12.17,4.79,-8.47,-2.89,-0.3,-11.34,4.53,-13.38,1.2,-7.63,-7.8,0.16,-14.88,2.4,-14.19,-3.53,-6.97,-12.86,-0.35,-17.75,-0.91,-14.39,-8.76,-6.4,-17.36,-1.62,-19.68,-4.89,-13.95,-13.97,-6.25,-21.11,-3.63,-20.36,-9.64,-13.02,-18.8,-6.91,-24.4,-7.87,-21.71,-15.76,-13.66,-24.13,-9.3,-27.84,-12.8,-23.88,-21.81,-14.95,-32.86,-12.84,-33.87,-22.58,-30.22,-32.4,-21.96,-38.9,-26.26,-43.69,-32.65,-38.81,-45.91,-36.08,-46.06,-32.49,-44.34,-47.74,-39.76,-54.64,-49,-53.29,-48.89,-62.85,-56.88,-51.24,-76.23,-56.51,-61.22,-51.47,-53.67,-69.42,-47.48,-52.56,-33.38,-45.66,-43.03,-48.48,-52.83,-27.44,-45.62,-34.11,-19.31,-20.61,-16.92,-8.66,-8.96,-8.06,-1.97,17.55,14.35,40.41,25.67,51,52.12,42.01,66.88,42.17,78.58,76.48,97.92,108.88,86.06,115.24,122.83,121.26,131.4,131.46,154.25,146.31,177.71,191.45,180.55,182.73,216.87,228.64,191.36,243.89,228.27,215.48,274.01,261.26,273.58,236.82,255.46,246.99,263.81,287.53,303.05,325.18,300.17,340.31,358.23,350.83,363.66,300.18,372.23,311.16,357.78,342.32,315.39,402.56,330.44,398.76,326.15,343.17,380.42,388.91,406.73,358.66,339.71,324.02,342.34,380.01,324.75,360.68,356.14,343.23,347.26,327.38,332.22,279.84,298.53,302.87,319.46,254.63,240.65,281.9,269.96,240.16,245.78,228.61,258.14,231.35,219.85,186.24,188.59,210.07,178.71,206.78,146.88,162.96,152.49,138.84,143.96,123.84,151.37,103.71,115.1,117.38,111.67,91.87,74.13,89.75,77.8,82.39,67.14,53.66,58.18,39.58,55.4,45.41,44.48,46.14,29.71,42.41,19.92,29.24,17.67,21.22,25.18,8.37,21.69,3.85,10.24,6.23,0.58,10,-9.96,8.4,-6.69,0.8,-0.06,-9.98,1.93,-14.73,-0.47,-11.26,-8.75,-2.47,-17.3,0.01,-17.12,-5.85,-11.08,-14.57,-4.42,-20.89,-4.58,-19.02,-11.59,-10.22,-19.33,-4.88,-23.48,-8.19,-17.63,-14.93,-9.63,-23.58,-6.14,-24.9,-12.53,-18.56,-21.4,-11.01,-27.58,-9.18,-25.23,-18.02,-16.93,-28.86,-12.53,-30.19,-16.97,-25.69,-26.7,-18,-34.55,-15.66,-34.77,-21.51,-26.61,-33.68,-25.26,-37.88,-23,-41.82,-30.86,-31.71,-44.11,-29.45,-44.49,-27.4,-44.64,-41.37,-28.77,-45.32,-26.72,-51.73,-31.99,-44.11,-40.04,-38.49,-47.43,-37.93,-49.12,-38.68,-43.64,-57.58,-35.74,-51.3,-38.25,-54.57,-50.49,-49.42,-56.54,-45.58,-50.18,-51.71,-47.43,-46.61,-46.27,-61.76,-34.36,-62.17,-52.19,-50.62,-51.98,-55.39,-72.27,-56.55,-49.2,-45.33,-39.91,-61.61,-41.72,-64.96,-47.93,-57.42,-66.38,-64.84,-64.22,-50.47,-62.63,-63.11,-63.03,-69.08,-54.85,-63.58,-65.29,-56.23,-78.11,-48.04,-75.66,-44.42,-81.85,-78.71,-85.21,-68.39,-71.07,-78.82,-78.33,-89.65,-61.31,-61.83,-81.34,-60.63,-74.54,-67.98,-74.91,-82.97,-88.58,-78.38,-55.65,-75.81,-67.75,-67.37,-86.98,-76.64,-88.44,-72.62,-90.96,-79.98,-69.26,-89.98,-84.45,-97.8,-81.24,-103.28,-97,-64.75,-108.16,-58.52,-95.4,-90.8,-82.89,-82,-69.23,-85.2,-81.18,-98.56,-63.22,-65.22,-81.76,-85.87,-102.56,-77.96,-95.8,-63.46,-84.18,-91.87,-77.08,-96.5,-61.2,-80.49,-62.87,-53.06,-74.32,-55.37,-77.3,-72.01,-76.95,-58.32,-44.66,-66.21,-45.61,-57.71,-59.26,-67.49,-63.83,-53.11,-79,-56.82,-63.68,-52.59,-52.16,-64.71,-48.56,-68.66,-45.21,-42.59,-68.92,-47.9,-63.22,-43.51,-48.7,-59.03,-38.12,-60.84,-48.55,-58.93,-42.53,-42.59,-45.29,-39.47,-61.86,-42.74,-49.89,-48.65,-41.76,-46.49,-40.46,-50.85,-39.98,-45.48,-41.84,-37.25,-52.82,-35.25,-54.85,-34.29,-49.01,-45.27,-32.4,-54.41,-32.9,-47.32</v>
       </c>
     </row>
     <row r="98">
@@ -1474,12 +1474,3774 @@
         <v>[L_05_标记]</v>
       </c>
       <c r="C98" t="str">
-        <v>幅值: 58.3uv 相位: 35°</v>
+        <v>a: 22.9ms -40.8uv b: 49.0ms 336.4uv</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B99" t="str">
+        <v>[R_06_名字]</v>
+      </c>
+      <c r="C99" t="str">
+        <v>FERG(6)_dRod</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B100" t="str">
+        <v>[R_06_放大器]</v>
+      </c>
+      <c r="C100" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B101" t="str">
+        <v>[R_06_闪光]</v>
+      </c>
+      <c r="C101" t="str">
+        <v>b白色光:3.0cd.m-2,4ms</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B102" t="str">
+        <v>[R_06_闪光背景]</v>
+      </c>
+      <c r="C102" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B103" t="str">
+        <v>[R_06_采样]</v>
+      </c>
+      <c r="C103" t="str">
+        <v>刺激间隔:2.0S</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B104" t="str">
+        <v>[R_06_分析时间]</v>
+      </c>
+      <c r="C104" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B105" t="str">
+        <v>[R_06_数据长度]</v>
+      </c>
+      <c r="C105" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B106" t="str">
+        <v>[R_06_详细数据(uv)]</v>
+      </c>
+      <c r="C106" t="str">
+        <v>7.5,-6.42,2.36,6.5,-7.08,3.12,5.24,-7.71,3.7,3.77,-8.29,4.1,2.11,-8.77,4.33,0.34,-9.14,4.4,-1.49,-9.37,4.34,-3.34,-9.43,4.16,-5.13,-9.31,3.89,-6.81,-8.98,3.54,-8.34,-8.45,3.15,-9.65,-7.7,2.73,-10.73,-6.74,2.29,-11.52,-5.59,1.86,-12.03,-4.28,1.44,-12.23,-2.83,1.02,-12.13,-1.28,0.61,-11.78,0.32,0.22,-11.12,1.9,-0.19,-10.33,3.34,-0.71,-9.41,4.61,-1.3,-8.2,5.81,-2.07,-7.54,6.49,-3.1,-6.16,7.01,-4.29,-5.76,6.54,-6.56,-6.04,4.92,-8.73,-6.07,4.1,-10.88,-6.09,-0.87,-13.28,-9.32,-4.27,-16.24,-12.44,-5.34,-20.22,-12.74,-13.68,-26.68,-16.83,-22.3,-35.33,-26.6,-25.77,-45.17,-27.97,-27.44,-43.42,-33.35,-32.51,-48.68,-33.71,-49.9,-52.1,-38.29,-46.68,-55.35,-43.41,-51.53,-63.33,-45.09,-50.41,-59.12,-39.66,-42.73,-48.57,-41.55,-44.29,-50.1,-29.85,-31.34,-20.95,-25.2,-29.23,-24.09,-1.21,-17.42,3.74,12.92,12.27,21.5,35.37,28.79,38.68,57.32,49.89,70.6,79.56,63.68,102.79,84.95,90.95,99.01,103.83,103.81,150.54,126.64,153.74,166.08,148.21,147.7,194.33,199.94,189.55,201.44,213.21,217.72,210.42,241.67,263.85,246.06,264.66,289.91,271.18,280.25,272.08,328.87,307.28,268.45,281.31,293.25,309.27,357.92,349.94,300.01,326.53,309.01,304.2,367.47,365.61,375.48,313.84,357.39,349.18,356.12,358.64,327.78,366.27,311.13,360.77,340.67,351.79,334.23,347.49,287.99,327.33,323.14,265.77,287.52,285.7,313.74,323.56,254.54,301.85,274.35,272.57,230.71,269.18,256.48,252,254.85,239.1,212.62,214.53,185.21,180.23,183.9,166.16,189.33,161.28,166.43,151.64,143.08,141.93,140.54,137.41,112.72,114.94,121.25,107.22,105.57,110.48,98.13,104.78,90.25,72.13,83.04,77.31,61.58,81.91,56.28,57.64,66.89,48.8,46.48,56.2,38.47,36.27,50.55,34.83,35.16,42.94,28.02,31.82,33.4,20.16,26.19,28.73,15.92,21.71,25.43,11.58,19.47,20.97,5.25,16.61,17.08,3.37,16.3,11.44,1.3,13.96,8.57,-1.57,11.68,5.25,-1.26,10.47,1.61,-2.51,10.3,-1.26,-4.36,8.42,-4.15,-5.8,7.02,-7.56,-6.61,4.51,-8.44,-5.47,2.35,-9.51,-5.99,0.62,-12.5,-7.37,2.26,-12.61,-7.41,-2.75,-13.41,-7.12,-0.48,-14.38,-3.23,-5.1,-18.67,-4.53,-5.07,-19.04,-1.47,-4.74,-15.77,-6.66,-6.76,-18.07,0.37,-13.87,-13.32,-1.18,-14.53,-13.52,0.34,-16.94,-13.85,-5.14,-18.12,-17,-8.12,-17.64,-10.39,-0.99,-19.06,-13.69,-2.11,-17.78,-11.47,-6.05,-20.71,-14.19,-14.94,-26.91,-19,-4.81,-24.56,-17.17,-21.26,-35.71,-12.65,-19.26,-31.45,-11.01,-16.15,-28,-20.45,-27.11,-24.49,-15.8,-18.19,-32.24,-26.96,-26.2,-30.62,-30.08,-44.37,-36.23,-20.03,-41.03,-44.83,-34.57,-35.01,-45.23,-27.02,-49.28,-55.66,-41.86,-50.6,-41.36,-24.77,-58.57,-57.7,-51.82,-61.2,-34.53,-51.97,-49.55,-35.34,-47.17,-60.64,-41.89,-41.42,-62.74,-58.2,-55.37,-43.84,-48.16,-36.4,-50.42,-58.46,-56.26,-71.23,-54.4,-62.42,-66.54,-57.63,-43.33,-65.16,-42,-48.61,-51.23,-50.69,-39.06,-44.53,-39.7,-58.41,-44.51,-34.41,-64.91,-61.63,-53.89,-41.02,-39.73,-37.64,-59,-53.53,-43.27,-59.65,-54.86,-37.96,-52.15,-49.29,-32.54,-34.29,-25.19,-29.46,-45.11,-48.36,-44.17,-51.23,-19.91,-47.82,-38.22,-33.77,-34.53,-45.79,-31.1,-50.04,-40.92,-16.41,-37.63,-30.15,-26.65,-41.55,-38.16,-15.06,-27.22,-45.37,-29.93,-29.62,-36.5,-29.77,-38.08,-33.37,-21.77,-44.42,-39.89,-22.85,-41.89,-32.02,-18.87,-28.35,-34.78,-19.87,-27.81,-25.6,-17.19,-27.31,-20.65,-14.2,-33.72,-12.27,-15.6,-24.08,-8.52,-14.97,-24.51,-5.92,-21.92,-20.55,-8.23,-18.81,-20.06,-4.28,-14.44</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B107" t="str">
+        <v>[R_06_标记]</v>
+      </c>
+      <c r="C107" t="str">
+        <v>a: 24.0ms -47.9uv b: 52.3ms 374.2uv</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B108" t="str">
+        <v>[L_06_名字]</v>
+      </c>
+      <c r="C108" t="str">
+        <v>FERG(6)_dRod</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B109" t="str">
+        <v>[L_06_放大器]</v>
+      </c>
+      <c r="C109" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B110" t="str">
+        <v>[L_06_闪光]</v>
+      </c>
+      <c r="C110" t="str">
+        <v>b白色光:3.0cd.m-2,4ms</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B111" t="str">
+        <v>[L_06_闪光背景]</v>
+      </c>
+      <c r="C111" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B112" t="str">
+        <v>[L_06_采样]</v>
+      </c>
+      <c r="C112" t="str">
+        <v>刺激间隔:2.0S</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B113" t="str">
+        <v>[L_06_分析时间]</v>
+      </c>
+      <c r="C113" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B114" t="str">
+        <v>[L_06_数据长度]</v>
+      </c>
+      <c r="C114" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B115" t="str">
+        <v>[L_06_详细数据(uv)]</v>
+      </c>
+      <c r="C115" t="str">
+        <v>-7.84,-0.82,-13.29,-4.14,-3.57,-13.55,-1.33,-7.39,-11.99,-0.25,-11.21,-9.12,-1.29,-13.98,-5.84,-4.22,-15.01,-3.22,-8.32,-14.12,-2.13,-12.52,-11.69,-3.03,-15.75,-8.59,-5.81,-17.22,-5.84,-9.8,-16.64,-4.39,-13.99,-14.32,-4.79,-17.28,-11.04,-7.02,-18.83,-7.85,-10.54,-18.25,-5.75,-14.39,-15.78,-5.4,-17.46,-12.21,-6.92,-18.99,-8.47,-9.97,-18.33,-5.91,-13.37,-15.97,-4.77,-16.45,-12.63,-6.11,-18.55,-8.74,-9.34,-18.45,-5.78,-12.51,-17.47,-4.53,-17.17,-13.51,-7.89,-19.2,-10.77,-9.82,-23.05,-11.12,-17.39,-20.89,-12.14,-22.96,-20.59,-14.14,-27.04,-22.48,-22.09,-31.54,-17.08,-21.98,-30.26,-20.68,-30.9,-30.42,-29.82,-43.46,-31.84,-25.96,-45.25,-30.24,-35.42,-52.34,-30.73,-44.9,-51.67,-31.51,-55.97,-54.5,-37.92,-50.46,-43.74,-51.95,-44.15,-26.54,-43.11,-51.11,-26.64,-31.22,-34.09,-26.87,-26.04,-28.48,-24.54,-20.8,-7.24,-0.63,-13.41,8.86,-7.9,19.35,13.81,27.72,40.89,36.96,31.51,43.81,67.95,45.49,71,81.86,78.89,83.53,97.83,111.09,134.34,115.56,134.76,145.16,154.26,153.3,133.31,160.2,163.59,166.3,170.43,215.8,204.36,211.4,209.51,227.81,233.42,226.34,220.14,233.72,282.15,248.89,258.54,281.19,288.52,297.71,287.08,290.9,308.38,336.56,288.17,341.45,281.25,361.5,303.18,331.13,294.47,349.06,358.59,352.66,335.38,309.01,354.88,370.44,379.85,317.96,298.38,320.53,314.73,365.39,346.03,338.8,301.53,289.52,314.37,326.83,337.25,314.69,331.27,319.41,264.91,277.59,263.61,302.38,289.83,260.34,288.12,281.59,229.88,222.21,229.39,237.67,244.52,197.2,215.32,209.16,224.31,194.93,203.1,178.46,175.94,164.45,164.78,161.78,168.81,146.39,155.8,133.38,153.68,138.56,140.71,127.75,116.84,127.2,109.62,86.33,99.72,97.83,95.3,95.94,74.01,83.59,75.17,56.25,67.63,71.63,57.01,61.36,55.5,40.42,58.47,39.87,43.31,45.61,28.81,40.36,36.19,22.87,33.23,28.65,21.5,28.38,19.4,20.11,24.11,7.37,18.14,14.96,4.17,16.21,8.9,3.42,14.3,2.24,4.23,9.79,-2.62,4.74,5.36,-7.54,4.2,-1.64,-7.49,4.34,-6.02,-5.52,2.49,-10.66,-5.7,-2.61,-13.55,-2.75,-7.67,-14.63,-4.56,-11.96,-15.7,-3.22,-16.82,-13.25,-8.58,-19.36,-10.36,-11.63,-20.3,-11.11,-17.44,-18.34,-11.61,-21.73,-19.06,-14.19,-27.47,-14.9,-18.35,-23.17,-15.98,-21.17,-20.74,-10.15,-27.25,-23.77,-10.69,-27.4,-14.8,-18.14,-27.14,-17.75,-25.33,-25.42,-14.34,-30.63,-24.46,-16.66,-28.43,-21.38,-19.8,-31.64,-16.69,-28.28,-26.1,-21.01,-32.41,-24.74,-26.22,-30.81,-19.3,-19.4,-38.68,-23.62,-25.9,-35.09,-28.87,-33.58,-27.94,-32.9,-47.72,-37.1,-30.29,-51.89,-27.17,-41.19,-38.5,-30.44,-44.02,-53.69,-38.81,-36.66,-41.36,-32.71,-48.61,-41.5,-30.77,-50.54,-28.86,-43.17,-53.89,-50.97,-45.42,-53.88,-38.92,-57.53,-49.98,-39.06,-68.8,-35.04,-61.01,-69.14,-36.34,-65.93,-46.42,-45.44,-66.38,-50.87,-48.79,-52.21,-48.86,-66.03,-61.42,-41.06,-48.6,-61.98,-63.22,-71.66,-58.25,-48.99,-64.71,-54.5,-71.15,-49.28,-68.01,-53.85,-62.46,-52.92,-73.98,-42.25,-66.67,-76.76,-36.25,-68.15,-65.11,-64.14,-56.81,-52.77,-36.36,-58,-53.66,-41.92,-45.57,-54.41,-57.21,-53.52,-55.56,-38.13,-60.66,-29.77,-66.48,-34.47,-43.2,-58.87,-35.23,-39.32,-49.43,-31.01,-51.79,-35.68,-49.78,-43.51,-56.93,-25.26,-58.36,-40.62,-31.82,-55.22,-42.96,-49.42,-36.93,-30.49,-49.61,-51.17,-37.89,-46.24,-29.89,-34.42,-40.11,-24.88,-38.71,-47.14,-32.88,-41.36,-36.22,-28.77,-42.39,-37.45,-34.57,-48.45,-22.62,-38.32,-37.08,-19.07,-34.85,-37.44,-26.14,-41.06,-30.88,-28.85,-36.91,-26.69,-27.56,-36.9,-22.38,-24.81,-27.05,-16.8,-24.33,-20.8,-20.28,-22.14</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B116" t="str">
+        <v>[L_06_标记]</v>
+      </c>
+      <c r="C116" t="str">
+        <v>a: 24.0ms -50.7uv b: 52.3ms 353.7uv</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B117" t="str">
+        <v>[R_07_名字]</v>
+      </c>
+      <c r="C117" t="str">
+        <v>FERG(7)_dMax</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B118" t="str">
+        <v>[R_07_放大器]</v>
+      </c>
+      <c r="C118" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B119" t="str">
+        <v>[R_07_闪光]</v>
+      </c>
+      <c r="C119" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B120" t="str">
+        <v>[R_07_闪光背景]</v>
+      </c>
+      <c r="C120" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B121" t="str">
+        <v>[R_07_采样]</v>
+      </c>
+      <c r="C121" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B122" t="str">
+        <v>[R_07_分析时间]</v>
+      </c>
+      <c r="C122" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B123" t="str">
+        <v>[R_07_数据长度]</v>
+      </c>
+      <c r="C123" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B124" t="str">
+        <v>[R_07_详细数据(uv)]</v>
+      </c>
+      <c r="C124" t="str">
+        <v>-5.11,-2.18,7.97,0.38,-7.31,2.77,5.83,-6.07,-4.93,5.95,-0.12,-9.09,0.05,4.86,-6.7,-7.32,4.06,-0.29,-10.29,-2.27,4.2,-6.69,-9.05,2.55,0.06,-10.71,-4.07,3.88,-6.04,-10.14,1.31,0.58,-10.71,-5.61,3.42,-5.72,-11.36,-1,-0.16,-12.03,-8.7,0.8,-6.96,-16.92,-6.65,-5.77,-18.29,-17.14,-7.43,-19.45,-30.17,-19.45,-18.65,-32.28,-37.02,-31.09,-31.57,-45.51,-47.74,-40.74,-65.18,-64.74,-51.46,-82.34,-80.13,-88.71,-70.87,-88.67,-101,-96.18,-118.23,-109.7,-125.25,-94,-130.27,-117.32,-108.45,-128.5,-143.18,-112.86,-87.63,-90.33,-120.99,-109.01,-98.04,-78.29,-71.28,-52.13,-72.95,-30.42,-13.29,-2.66,-3.24,4.44,21.17,25.28,51.91,82.39,106.46,117.77,118.48,128.17,188.09,157.07,190.43,247.81,241.35,232.97,293.96,263.5,300.71,318.53,376.17,334.09,403.45,447.75,472.04,448.87,460.16,503.77,473.84,528.92,607.18,617.65,527.28,584.51,580.33,676.38,675.39,688.26,674.2,735.55,646.02,654.07,664.09,693,675.5,711.62,745.29,790.29,718.38,800.53,702.23,787.41,765.58,738.21,766.25,632.46,773.49,613.08,723.55,685.56,596.55,646.54,627.26,619.5,617.29,583.27,595.02,594.19,522.84,502.97,497.68,449.32,520.52,476.68,474.47,439.73,469.2,394.56,390.07,377.95,322.11,322.54,348.32,340.01,279.85,289.94,249.61,308.44,265.2,292.82,256.46,231.61,208.06,212.1,225.26,200.5,200.75,205.04,224.28,175.27,205.81,187.37,171.71,157.74,184.8,180.22,176.72,168.73,157.75,154.45,146.36,165.34,170.1,174.03,136.66,146.89,154.06,129.08,128.85,158.49,110.68,124.42,123.33,103.43,117.39,82.74,103.71,123.14,112.47,77.04,96.52,90.01,87.71,95.08,95.37,51.56,61.27,93.66,72.45,69.59,81.73,50.58,60.16,65.02,50.42,46.71,38.06,47.44,48.21,35.48,23.9,46,27.53,16.05,30.11,28.1,10.96,18.63,26.76,19.21,4.87,17.08,16.98,4.93,-3.8,7.75,-0.38,-0.6,-3.33,3.67,-9.6,-8.36,-2.63,-1.35,-18.76,-9.97,-6.35,-13.62,-20.33,-13.03,-9.95,-24.93,-25.47,-14.51,-24.14,-32.44,-20.8,-22.36,-28.81,-27.65,-18.9,-24.07,-38.25,-27.17,-30.87,-44.94,-40.55,-21.41,-33.96,-46.48,-33.16,-23.47,-36.67,-43.69,-29.78,-35.2,-50.49,-40.13,-29.5,-50.58,-48.42,-32.44,-45.88,-54.06,-39.44,-42.49,-45.42,-61.89,-53.15,-37.11,-53,-51.5,-38.3,-62.76,-55.84,-59.31,-51.22,-50.9,-64.23,-59.28,-48.4,-56.72,-49.78,-37.68,-74.54,-66.07,-64.96,-59.54,-74.22,-49.93,-45.55,-63.68,-78.28,-41.99,-57.74,-70.18,-78.76,-54.66,-58.54,-59.61,-69.36,-55.82,-75.13,-65.08,-62.51,-72.26,-71.73,-64.11,-74.66,-73.93,-79.57,-69.98,-87.11,-94.48,-55.02,-73.65,-89.08,-92.07,-64.3,-76.19,-78.68,-85.53,-93.83,-94.36,-75.07,-93.99,-82.58,-91.34,-88.67,-95.18,-91.47,-76.68,-98.42,-77.12,-93.86,-67.74,-77.31,-85.37,-85.49,-69.93,-74.33,-108.31,-86.3,-88.89,-92.56,-82.17,-73.15,-97.78,-107.72,-82.47,-71.59,-93.87,-75.5,-86.36,-84.03,-92.12,-75.32,-81.04,-76.36,-67.26,-65.72,-89.52,-94.82,-72.29,-63.44,-60.13,-89.24,-85.64,-67.29,-90.25,-77.9,-67.53,-80.81,-71.31,-54.09,-67.87,-63.19,-77.42,-58.47,-77.29,-59.63,-61.76,-67.37,-80.73,-63.01,-58.85,-64.16,-57.85,-61.99,-59.76,-60.48,-63.24,-44.94,-58.02,-55.49,-62.23,-39.03,-65.98,-53.76,-35.5,-55.54,-60.13,-47.88,-36.73,-42.93,-58.88,-52.13,-38.61,-49.53,-57.36,-31.9,-48.45,-56.93,-43.31,-44.09,-45.51,-40.29,-28.61,-44,-54.9,-43.13,-33.42,-45.97,-45.71,-38.72,-38.05,-40.81,-40.15,-27.57,-32.42,-45.15,-32.08,-22.76,-38.77,-38.56,-22.73,-28.26,-40.21,-28.16,-21.85,-29.15,-23.18,-22.46,-24.56,-27.86,-18.98,-18,-25.96,-29.12,-9.7,-17.8,-24.12,-14.56,-9.34,-27.12,-24.56,-10.1,-12.22</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B125" t="str">
+        <v>[R_07_标记]</v>
+      </c>
+      <c r="C125" t="str">
+        <v>a: 26.1ms -131.8uv b: 55.4ms 566.7uv</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B126" t="str">
+        <v>[L_07_名字]</v>
+      </c>
+      <c r="C126" t="str">
+        <v>FERG(7)_dMax</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B127" t="str">
+        <v>[L_07_放大器]</v>
+      </c>
+      <c r="C127" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B128" t="str">
+        <v>[L_07_闪光]</v>
+      </c>
+      <c r="C128" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B129" t="str">
+        <v>[L_07_闪光背景]</v>
+      </c>
+      <c r="C129" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B130" t="str">
+        <v>[L_07_采样]</v>
+      </c>
+      <c r="C130" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B131" t="str">
+        <v>[L_07_分析时间]</v>
+      </c>
+      <c r="C131" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B132" t="str">
+        <v>[L_07_数据长度]</v>
+      </c>
+      <c r="C132" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B133" t="str">
+        <v>[L_07_详细数据(uv)]</v>
+      </c>
+      <c r="C133" t="str">
+        <v>-8.64,-19.34,-9.18,-5.72,-18.73,-14.22,-4.78,-16.12,-18.72,-6.3,-12.51,-21.47,-9.99,-9.2,-21.8,-14.89,-7.4,-19.79,-19.65,-7.85,-16.23,-22.95,-10.55,-12.36,-23.9,-14.79,-9.5,-22.31,-19.35,-8.63,-18.76,-22.87,-10.09,-14.37,-24.36,-13.43,-10.6,-23.24,-17.75,-8.58,-20.07,-21.8,-9.42,-15.99,-23.97,-12.28,-12.37,-25.43,-18.06,-11.1,-24.24,-23.9,-13.08,-23.02,-29.51,-20.44,-23.26,-34.96,-27.94,-22.62,-38.77,-35.93,-34.18,-44.74,-47.93,-42.71,-52.56,-65.79,-67.99,-62.72,-81.81,-73.69,-64.24,-92.38,-100.15,-103.89,-110.08,-98.94,-90.83,-102.52,-144.72,-122.57,-118.5,-142.6,-140.42,-138.6,-124.24,-150.76,-108.17,-139.22,-149.77,-117.83,-109.69,-124.93,-75.6,-83.44,-95.49,-93.37,-67.98,-33.45,-33.1,-22.83,-4.26,-16.27,40.16,32.65,33.21,62.12,114.54,97.9,146.61,137.75,140.95,199.21,202.37,247.06,229.72,261.55,282.31,282.06,295.62,354.16,373,373.38,372.75,468.1,478.33,511.86,481.73,442.77,509.33,500.94,530.66,600.63,529.74,567.24,567.97,604.6,578.19,587.75,654.25,607.8,713.25,631.66,625.7,753.12,743.99,681.03,758.33,769.5,680.55,645.79,704.48,737.88,680.51,642.93,636.73,624.85,681.19,746.82,625.08,622.29,716.58,579.57,672.82,668.47,645.93,576.64,623.63,599,558.8,574.47,510.44,473.66,442.94,505.44,486.47,465.57,374.73,434.27,384.86,353.36,329.25,394.09,335.97,344.33,339.9,337.1,323.52,277.55,296.32,270.68,253.43,237.99,221.46,214.97,225.68,234.88,193.33,229.92,185.4,222.51,193.22,168.83,176.83,198.85,195.46,154.86,181.86,137.07,141.65,132.03,155.49,165.64,153.09,140.36,132.18,147.53,125.52,91.26,114.22,102.81,84.81,128.49,135.22,116.96,112.67,107.84,79.89,100.99,109.68,75.08,69.93,111.14,105.01,68.35,61.2,63.79,77.76,46.08,57.65,57.01,36.3,64.34,40.2,47.49,51.36,40.06,30.64,45.32,36.49,24.3,14.84,27.46,17.93,19.73,24.14,16.24,6.91,7.81,10.69,8.64,-1.51,11.22,-3.76,-10.72,4.04,-1.2,-15.92,-9.74,-3.38,-18.49,-16.87,-9.22,-24.36,-24.59,-14.69,-21.98,-26.06,-15.4,-16.04,-31.95,-32.07,-19.65,-38.42,-29.69,-19.91,-28.62,-38.18,-33.95,-32.43,-48.47,-39.68,-33.36,-40.35,-46.1,-25.7,-44.53,-45.99,-37.74,-33.36,-46.78,-48.99,-39.57,-44.86,-53.56,-36.52,-51.32,-50.96,-43.72,-48.34,-54.98,-50.57,-54.37,-48.87,-56.15,-39.25,-68.07,-63.48,-50.39,-66.68,-63.3,-51.11,-51.57,-62.46,-46.87,-41.16,-75.47,-53.04,-47.59,-75.92,-75.49,-43.88,-47.22,-75.17,-46.33,-68.96,-65.35,-68.47,-53.84,-77.79,-60.13,-61.61,-59.69,-62.99,-67.01,-73.94,-80.43,-86.35,-63.89,-86.28,-75.5,-65.97,-67.98,-74.75,-63.65,-67.04,-88.71,-71.88,-92.99,-92.37,-98.7,-69.65,-87.56,-83.65,-75.03,-78.24,-114.3,-88.09,-83.99,-85.3,-95.11,-69.6,-88.47,-95.04,-92.82,-100.46,-107.82,-96.92,-85.58,-96.12,-88.87,-78.37,-110.49,-100.38,-96.45,-83.01,-113.95,-106.28,-111.51,-90.11,-79.64,-105.91,-85.45,-115.32,-87.23,-82.23,-100.39,-87.68,-103.03,-85.08,-71.66,-103.6,-86.19,-95.6,-76.65,-80.58,-81.76,-61.63,-93.03,-77.18,-61.29,-75.46,-94.83,-92.82,-58.57,-79.77,-101.18,-65.78,-71.86,-84.88,-72.08,-85.06,-88.62,-73.87,-59.16,-93.71,-59.65,-61.88,-71.59,-87.97,-60.79,-77.9,-81.08,-50.34,-52.09,-63.92,-63.11,-45.57,-73.43,-54.32,-68.54,-64.22,-62.5,-59.88,-54.25,-76.2,-60.32,-52.8,-77.1,-52.79,-61.71,-56.41,-54.66,-40.64,-47.64,-68.84,-56.27,-47.96,-50.3,-53.68,-53.67,-62.15,-59.91,-50,-55.74,-48.53,-52.86,-52.21,-64.25,-48.37,-45.59,-57.91,-43.35,-42.68,-52.34,-55.56,-29.18,-46.24,-45.89,-40.11,-32.59,-39.81,-39.75,-26.31,-34.1,-45.37,-27.32,-27.68,-36.1,-26.24,-28.18,-32.84,-23.7,-21.51,-27.65,-29.35,-22.36,-26.67,-29.68</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B134" t="str">
+        <v>[L_07_标记]</v>
+      </c>
+      <c r="C134" t="str">
+        <v>a: 26.2ms -131.3uv b: 55.1ms 618.2uv</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B135" t="str">
+        <v>[R_08_名字]</v>
+      </c>
+      <c r="C135" t="str">
+        <v>FERG(8)_dOps</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B136" t="str">
+        <v>[R_08_放大器]</v>
+      </c>
+      <c r="C136" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B137" t="str">
+        <v>[R_08_闪光]</v>
+      </c>
+      <c r="C137" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B138" t="str">
+        <v>[R_08_闪光背景]</v>
+      </c>
+      <c r="C138" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B139" t="str">
+        <v>[R_08_采样]</v>
+      </c>
+      <c r="C139" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B140" t="str">
+        <v>[R_08_分析时间]</v>
+      </c>
+      <c r="C140" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B141" t="str">
+        <v>[R_08_数据长度]</v>
+      </c>
+      <c r="C141" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B142" t="str">
+        <v>[R_08_详细数据(uv)]</v>
+      </c>
+      <c r="C142" t="str">
+        <v>-28.32,-38.03,-37.43,-27.2,-24.83,-34.18,-40.09,-33.13,-25.33,-30.49,-40.81,-40.01,-29.89,-28.75,-38.24,-43.99,-36.2,-28.53,-32.67,-41.57,-38.99,-27.61,-25.23,-33.93,-37.15,-27.11,-18.66,-24,-32.71,-28.94,-19.04,-17.5,-28.28,-33.33,-26.28,-20.68,-28.52,-39.18,-37.26,-30.29,-29.02,-40.25,-43.3,-35.72,-29.24,-32.44,-40.35,-33.42,-19.69,-16.72,-23.1,-24.02,-9.9,-0.29,-6.65,-12.78,-8.72,-3.63,-6.06,-19.13,-25.66,-21.1,-21.5,-32.89,-45.58,-49.32,-41.59,-48.16,-52.89,-61.55,-46.32,-41.32,-41.27,-45.79,-32.32,-14.83,-11.54,-11.05,-5.79,2.52,14.33,1.84,0.24,1.61,10.06,-0.33,-18.88,-30.58,-30.22,-35.6,-54.27,-71.37,-75.14,-71.11,-73.79,-89.05,-77.35,-60.17,-49.77,-52.67,-47.64,-26.96,-7.37,-2.74,-1,8.21,22.59,35.67,16.13,15.89,7.91,16.51,-3.63,-25.23,-36.35,-39.82,-45.63,-79.1,-84.35,-82.58,-86.42,-92.46,-96.42,-85.29,-54.43,-50.64,-43.79,-31.5,-7.67,10.31,25.97,14.01,39.65,35.73,51.95,20.53,12.18,17.36,18.94,-5,-28.54,-37.49,-40.77,-48.9,-75.12,-82.72,-82.43,-65.83,-70.79,-76.43,-58.87,-41.99,-28.72,-28.78,-19.05,4.12,12.98,12.29,18.77,19.07,28.7,19.64,3.97,3.4,2.63,-4.79,-21.25,-39.2,-43.87,-45.03,-49.41,-69.7,-68.54,-57.05,-59.19,-62.18,-62.27,-50.76,-32.11,-25.07,-28.64,-22.47,-6.26,4.83,1.12,-11.41,-2.04,7.53,0.73,-14.59,-20.86,-15.38,-17.04,-30.01,-42.15,-38.06,-32.06,-39.18,-52.54,-51.79,-39.1,-34.7,-41.08,-40.76,-32.41,-19.71,-19.69,-26.19,-22.41,-10.49,-5.2,-16.38,-18.84,-14.62,-4.27,-11.9,-23.21,-23.83,-14.82,-13.98,-25.21,-31.31,-24.34,-17.56,-23.58,-33.2,-31.03,-18.88,-16.88,-24.52,-29.01,-19.74,-10.95,-15.63,-23.89,-21.14,-10.35,-9.07,-19.14,-23.45,-15.84,-8.75,-15.54,-25.5,-23.29,-13.83,-13.91,-24.57,-28.84,-20.5,-13.89,-20.62,-29.96,-26.29,-16.26,-16.48,-26.66,-29.82,-20.79,-14.48,-21.39,-30.16,-26.17,-16.38,-17.13,-27.7,-30.47,-21.47,-15.88,-23.45,-31.9,-27.47,-17.82,-19.26,-29.56,-31.76,-22.17,-16.9,-24.61,-32.43,-27.16,-17.41,-19.16,-29.26,-30.56,-20.61,-15.65,-23.59,-30.86,-24.98,-15.37,-17.63,-27.61,-28.25,-18.08,-13.61,-21.87,-28.65,-22.22,-12.83,-15.66,-25.53,-25.53,-15.2,-11.28,-19.85,-26.18,-19.29,-10.23,-13.68,-23.51,-22.97,-12.61,-9.36,-18.33,-24.3,-17.08,-8.48,-12.63,-22.47,-21.47,-11.2,-8.69,-18.08,-23.72,-16.23,-8.14,-13,-22.82,-21.37,-11.22,-9.46,-19.22,-24.47,-16.71,-9.14,-14.65,-24.38,-22.43,-12.39,-11.32,-21.36,-26.14,-18.06,-10.95,-17.01,-26.51,-23.99,-13.99,-13.53,-23.7,-27.89,-19.43,-12.7,-19.2,-28.35,-25.16,-15.15,-15.19,-25.38,-28.88,-19.98,-13.59,-20.41,-29.11,-25.2,-15.15,-15.65,-25.77,-28.53,-19.19,-13.12,-20.23,-28.44,-23.81,-13.77,-14.73,-24.76,-26.79,-17.07,-11.39,-18.8,-26.53,-21.26,-11.32,-12.8,-22.78,-24.15,-14.16,-8.97,-16.75,-24.07,-18.27,-8.55,-10.65,-20.63,-21.44,-11.32,-6.74,-14.95,-21.92,-15.71,-6.35,-9.15,-19.19,-19.51,-9.38,-5.49,-14.18,-20.85,-14.31,-5.39,-8.92,-19.02,-18.9,-8.81,-5.66,-14.8,-21.16,-14.31,-5.85,-10.1,-20.21,-19.6,-9.57,-7.12,-16.64,-22.61,-15.41,-7.39,-12.26,-22.27,-21.11,-11.08,-9.25,-19.03,-24.49,-16.88,-9.22,-14.6,-24.37,-22.56,-12.47,-11.18,-21.08,-25.91,-17.83,-10.47,-16.25,-25.67,-23.13,-12.94,-12.11,-22.04,-26.17,-17.58,-10.5,-16.62,-25.61,-22.33,-12.05,-11.67,-21.58,-24.99,-15.93,-9.16,-15.62,-24.18,-20.19,-9.9,-10.03,-19.93,-22.66,-13.22,-6.86,-13.71,-21.88,-17.29,-7.1,-7.82,-17.77,-19.92,-10.23,-4.4,-11.7,-19.56,-14.48,-4.54,-5.93,-16,-17.64,-7.83,-2.64,-10.46,-18.06,-12.58,-2.99,-5.13,-15.33,-16.53</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B143" t="str">
+        <v>[R_08_标记]</v>
+      </c>
+      <c r="C143" t="str">
+        <v>97.1uv</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B144" t="str">
+        <v>[L_08_名字]</v>
+      </c>
+      <c r="C144" t="str">
+        <v>FERG(8)_dOps</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B145" t="str">
+        <v>[L_08_放大器]</v>
+      </c>
+      <c r="C145" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B146" t="str">
+        <v>[L_08_闪光]</v>
+      </c>
+      <c r="C146" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B147" t="str">
+        <v>[L_08_闪光背景]</v>
+      </c>
+      <c r="C147" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B148" t="str">
+        <v>[L_08_采样]</v>
+      </c>
+      <c r="C148" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B149" t="str">
+        <v>[L_08_分析时间]</v>
+      </c>
+      <c r="C149" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B150" t="str">
+        <v>[L_08_数据长度]</v>
+      </c>
+      <c r="C150" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B151" t="str">
+        <v>[L_08_详细数据(uv)]</v>
+      </c>
+      <c r="C151" t="str">
+        <v>-0.13,-12.6,-5.43,7.04,0.06,-13.37,-7.86,5.5,0.63,-13.4,-9.54,4.7,1.81,-12.33,-10.64,3.99,2.88,-11.99,-12.46,1.78,2.64,-12.24,-14.86,-1.1,1.77,-12.26,-15.91,-2.31,3.46,-10.18,-15.21,-1.21,6.64,-4.67,-11.36,1.94,11.6,2.31,-6.98,5.62,16.27,6.61,-4.72,3.21,13.69,4.52,-9.22,-3.41,8.02,-1.51,-15.48,-10.51,3.92,-3.31,-15.48,-11.58,4.91,4.03,-7.22,-2.29,15.49,16.78,5.56,7.75,26.23,25.15,11.67,9.74,24.6,26.05,5.63,-1.95,6.72,7.1,-13.95,-25.05,-16.4,-12.37,-22.91,-37.18,-25.53,-14.83,-24.38,-23.94,-9.41,7.77,4.31,-1.02,18.18,39.15,36.87,18.01,26.48,43.02,30.76,16.81,8.71,15.97,1.71,-21.44,-31.85,-27.65,-32.2,-57.11,-63.47,-52.18,-47.69,-57.92,-52.03,-28.91,-16.66,-17.74,-4.57,18.4,41.05,25.99,41.38,50.02,68.37,53.33,41.25,44,43.2,18.69,-5.11,-6.76,-16.5,-34.25,-62.95,-53.47,-55.78,-67.17,-81.54,-64.43,-31.31,-37.34,-31.07,-9.72,17.5,26.12,25.61,40.49,72.4,76.23,53.84,57.76,66.59,61.39,27.75,22.57,21.79,6.86,-20.87,-31.52,-37.65,-47.87,-64.9,-72.75,-44.29,-47.27,-51.04,-41.77,-20.28,0.91,-2.36,2.5,25.46,49.16,32.36,35.35,53.46,58.26,42.53,28.25,23.43,31.29,7.12,-13.66,-14.67,-11.5,-32.53,-43.29,-40.42,-27.6,-36.66,-45.11,-37.09,-17.85,-20.69,-25.11,-12.87,8.7,10.15,6.13,11.23,23.19,25.49,13.66,10.9,19.07,15.95,0.07,-7.69,1.75,-0.32,-17.23,-24.05,-15.81,-11.81,-24.99,-32.84,-13.62,-7.88,-18.36,-19.19,-4.18,7.16,-1.28,-7.83,6.92,17.82,10.15,-1.13,8.56,19.24,10.44,-2.64,4.16,14.18,5.81,-8.68,-3.91,8.89,1.44,-12.72,-8,6.64,3.44,-11.04,-6.82,7.65,7.52,-6.16,-4.88,10.37,11.46,-2.47,-4.4,10.13,12.54,-2.65,-6.61,6.87,10.63,-3.8,-10.09,2.46,8.18,-5.44,-13.18,-1.49,6.24,-5.74,-14.94,-4.15,5.48,-5.05,-15.5,-5.89,5.18,-3.91,-15.8,-7.76,4.48,-2.94,-16.06,-9.92,3.32,-2.37,-16.23,-11.86,2.02,-1.64,-15.95,-13.37,1.04,-0.46,-14.89,-14.25,0.48,1.14,-13.21,-14.42,0.27,2.99,-10.98,-14.14,0.19,4.92,-8.48,-13.55,0.12,6.72,-5.84,-12.72,-0.01,8.36,-3.17,-11.74,-0.21,9.75,-0.53,-10.63,-0.53,10.8,1.97,-9.51,-1.04,11.43,4.19,-8.45,-1.81,11.54,6.02,-7.55,-2.87,11.1,7.4,-6.85,-4.22,10.09,8.29,-6.36,-5.82,8.57,8.69,-6.06,-7.62,6.58,8.64,-5.92,-9.54,4.22,8.2,-5.88,-11.46,1.6,7.44,-5.86,-13.29,-1.16,6.45,-5.8,-14.9,-3.91,5.34,-5.6,-16.19,-6.53,4.2,-5.21,-17.06,-8.9,3.12,-4.56,-17.43,-10.92,2.17,-3.62,-17.25,-12.51,1.4,-2.39,-16.52,-13.63,0.83,-0.88,-15.25,-14.28,0.46,0.85,-13.49,-14.46,0.25,2.72,-11.32,-14.23,0.16,4.64,-8.84,-13.66,0.11,6.51,-6.19,-12.83,0.03,8.19,-3.49,-11.85,-0.16,9.59,-0.87,-10.82,-0.54,10.59,1.54,-9.81,-1.17,11.12,3.63,-8.92,-2.09,11.12,5.33,-8.19,-3.3,10.55,6.57,-7.66,-4.81,9.43,7.34,-7.32,-6.56,7.8,7.64,-7.15,-8.48,5.72,7.52,-7.12,-10.5,3.3,7.03,-7.14,-12.49,0.66,6.27,-7.15,-14.35,-2.08,5.32,-7.07,-15.95,-4.79,4.29,-6.81,-17.19,-7.32,3.26,-6.32,-17.98,-9.59,2.33,-5.54,-18.25,-11.48,1.54,-4.46,-17.96,-12.94,0.93,-3.07,-17.11,-13.94,0.52,-1.41,-15.73,-14.47,0.29,0.45,-13.87,-14.56,0.2,2.43,-11.63,-14.28,0.19,4.43,-9.12,-13.69,0.18,6.34,-6.47,-12.89,0.09,8.03,-3.81,-11.98,-0.15,9.39,-1.26,-11.05,-0.62,10.32,1.04,-10.18,-1.36,10.76,3.02</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B152" t="str">
+        <v>[L_08_标记]</v>
+      </c>
+      <c r="C152" t="str">
+        <v>97uv</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B153" t="str">
+        <v>[R_09_名字]</v>
+      </c>
+      <c r="C153" t="str">
+        <v>FERG(9)_dMax</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B154" t="str">
+        <v>[R_09_放大器]</v>
+      </c>
+      <c r="C154" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B155" t="str">
+        <v>[R_09_闪光]</v>
+      </c>
+      <c r="C155" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B156" t="str">
+        <v>[R_09_闪光背景]</v>
+      </c>
+      <c r="C156" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B157" t="str">
+        <v>[R_09_采样]</v>
+      </c>
+      <c r="C157" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B158" t="str">
+        <v>[R_09_分析时间]</v>
+      </c>
+      <c r="C158" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B159" t="str">
+        <v>[R_09_数据长度]</v>
+      </c>
+      <c r="C159" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B160" t="str">
+        <v>[R_09_详细数据(uv)]</v>
+      </c>
+      <c r="C160" t="str">
+        <v>-13.25,-23.41,-21.85,-9.97,0.78,0.1,-11.15,-21.78,-21.17,-9.65,1.84,2.4,-8.19,-19.26,-19.65,-8.62,3.46,5.19,-4.72,-16.2,-17.66,-7.26,5.25,8.07,-1.15,-13.04,-15.63,-6.03,6.75,10.57,2.02,-10.27,-14.03,-5.35,7.51,12.23,4.35,-8.3,-13.32,-5.69,7.13,12.53,5.28,-7.87,-14.04,-7.5,4.98,11.2,3.98,-8.88,-16.87,-12.52,-0.83,6.57,-0.55,-14.41,-24.33,-19.8,-10.85,-4.91,-10.72,-25.68,-35.73,-31.27,-26.34,-17.68,-25.02,-41.11,-49.16,-52.84,-46.22,-36.55,-40.83,-70.24,-76.68,-79.38,-67.44,-81.31,-64.2,-82.27,-106.54,-120.31,-94.9,-108.48,-91.37,-97.88,-140.78,-119.05,-118.93,-91.44,-116.86,-103.79,-136.56,-143.44,-121.37,-76.98,-89.65,-88.17,-86.63,-91.91,-68.36,-34.91,-19.71,-31.79,-53.42,-46.81,-37.83,32.13,25.47,27,67.7,55.77,67.22,142.7,139.72,141.43,154.81,179.13,206.27,225.94,245.6,289.57,292,304.62,340.39,320,385.44,354.3,382.15,394.1,414.34,484.04,445.56,485.71,460.13,510.86,548.46,576.89,537.45,529.73,604.58,624.9,679.07,642.19,730.21,707.07,679.76,718.48,752.52,762.31,749.18,780.25,646.44,698.28,628.79,790.04,728.1,658.35,735.55,623.34,620.86,695.51,739.23,679.26,758.68,744.45,647.87,722.39,673.05,740.41,679.24,641.61,659.51,603.05,623.57,613.09,615.65,522.94,490.49,562.79,463.35,486.73,453.51,457.18,406.27,431.65,480.64,402.76,426.74,388.6,360.31,374.08,353.82,402.02,315.92,317.51,307.13,319.9,281.15,306.32,269.51,267.37,265.25,234.79,270.76,274.92,213.52,245.15,206.36,223.56,194.59,250.85,188.98,188.2,205.01,176.29,159.02,204.18,185.29,172.6,149.43,155.86,188.26,155.1,177.78,155.05,144.89,154.19,113.79,148.92,122.95,101.52,126.51,106.14,110.74,118.1,116.95,106.86,70.86,72.51,89.6,113.5,90.11,67.05,72.83,39.01,64.47,55.34,62.19,52.62,35.38,38.06,40.99,38.39,40.45,32.01,13.25,8.72,24.74,20.72,30.47,28.08,8.34,-8.16,3.29,18.11,13.41,7.93,-4.37,-13.53,-5.46,-1.3,8.49,1.85,-10.48,-15.58,-17.26,-2.27,-3.43,-1.8,-19.16,-23.56,-22.62,-11.52,-4.56,-6.66,-17.33,-33.39,-25.17,-13.16,-5.92,-9.05,-27.12,-30.48,-28.72,-24.33,-16.22,-9.52,-28.68,-32.48,-30.91,-32.64,-22.92,-11.19,-28.72,-44.77,-40.5,-26.42,-16.93,-23.38,-39.46,-40.96,-52.8,-29.24,-31.48,-29.55,-37.63,-46.3,-48.72,-53.71,-31.34,-35.58,-40.8,-57.7,-66.94,-61.13,-37.97,-28.25,-40.42,-57.9,-65.48,-67.95,-58.91,-34.86,-45.52,-75.46,-73.21,-67.16,-52.7,-45.6,-71.46,-87.71,-70.78,-76.74,-52.08,-66.38,-51.25,-93.56,-100.42,-85.84,-86.05,-51.71,-59.9,-80.3,-99.78,-72.07,-62.93,-75.67,-80.01,-87.23,-88,-81.96,-64.45,-74.84,-60.33,-100.6,-85.1,-95.03,-88.61,-72.84,-86.13,-83.05,-111.13,-90.26,-101.29,-73.75,-86.92,-68.3,-82.46,-85.67,-71.13,-63.58,-70.12,-65,-97.77,-101.24,-83.95,-62.73,-90.76,-80.53,-112.31,-101.36,-87.61,-66.17,-87.91,-87.31,-91.09,-103.41,-73.22,-60.47,-69.98,-59.03,-94.27,-86.02,-96.06,-59.07,-72.41,-93.22,-72.72,-94.05,-77.99,-58.16,-61.17,-57.05,-94.43,-111.47,-78.44,-72.32,-56.45,-72.47,-76.67,-96.38,-88.26,-78.21,-86.48,-74.62,-70.85,-78.18,-101.07,-94.65,-72.18,-87.81,-74.04,-107.7,-79.77,-70.95,-50.89,-79.6,-73.71,-97.31,-79.46,-61.45,-70.67,-48.01,-58.39,-75.97,-80.67,-58.85,-49.08,-47.82,-54.43,-77.5,-63.51,-64.29,-63.95,-41.4,-48.98,-70.78,-64.87,-65.4,-49.26,-47.41,-48.04,-63.69,-56.11,-54.33,-35.49,-42.47,-32.06,-60.12,-48.76,-42.01,-26.72,-31.33,-35.57,-54.84,-44.43,-40.6,-22.78,-29.29,-27.17,-44.6,-42.32,-37.82,-22.15,-21.84,-25.54,-37.77,-35.95,-32.92,-17.06,-8.7,-23.52,-27.77,-37.45,-35.47,-25.99,-12.24,-17.71,-29.07</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B161" t="str">
+        <v>[R_09_标记]</v>
+      </c>
+      <c r="C161" t="str">
+        <v>a: 29.5ms -141.9uv b: 63.0ms 590.2uv</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B162" t="str">
+        <v>[L_09_名字]</v>
+      </c>
+      <c r="C162" t="str">
+        <v>FERG(9)_dMax</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B163" t="str">
+        <v>[L_09_放大器]</v>
+      </c>
+      <c r="C163" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B164" t="str">
+        <v>[L_09_闪光]</v>
+      </c>
+      <c r="C164" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B165" t="str">
+        <v>[L_09_闪光背景]</v>
+      </c>
+      <c r="C165" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B166" t="str">
+        <v>[L_09_采样]</v>
+      </c>
+      <c r="C166" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B167" t="str">
+        <v>[L_09_分析时间]</v>
+      </c>
+      <c r="C167" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B168" t="str">
+        <v>[L_09_数据长度]</v>
+      </c>
+      <c r="C168" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B169" t="str">
+        <v>[L_09_详细数据(uv)]</v>
+      </c>
+      <c r="C169" t="str">
+        <v>11.31,0.89,-6.2,-1.43,9.37,13.08,5.21,-4.66,-4.51,5.57,13.46,9.74,-0.94,-5.44,1.88,12.37,13.53,4.22,-4.03,-0.93,10.05,15.88,9.79,-0.51,-2.28,6.96,16.31,14.64,4.34,-1.95,3.82,14.69,17.87,9.54,-0.18,0.77,11.08,18.18,13.61,2.44,-1.65,6.06,15.26,14.75,4.31,-4.36,-1.85,9.35,12.11,6.2,-5.12,-10.93,-1.4,6.18,1,-12.36,-17.89,-16.24,-10.86,-8.84,-18.11,-37,-31.07,-25.49,-18.99,-33.34,-48.37,-54.82,-43.91,-43.45,-55.71,-60.51,-67.96,-78.56,-67.5,-65.53,-75.36,-91.23,-90.32,-86.53,-60.24,-91.82,-91.47,-92.02,-106.02,-78,-84.22,-70.28,-77.17,-104.26,-57.16,-50.29,-63.69,-65.25,-48.92,-27.92,-0.3,-18.57,-35.66,17.34,15.11,16.25,44.54,43.2,73.22,90.74,112.36,137.49,132.11,133.42,154.59,173.32,219.21,229.86,206.38,262.65,280.75,326.38,316.22,298.89,366.38,318.49,379.58,420.84,478.7,491,494.43,484.86,504.99,583.86,564.02,605.79,548.63,643.67,583.9,577.24,556.44,575.55,670.94,720.5,681.77,714.82,645.13,677.44,634.58,750.48,715.67,693.89,677.37,686.52,759.92,673.04,721.36,730.01,650.62,686.39,686.33,660.89,761.07,665.58,670.63,752.15,786.32,710.02,745.01,748.74,732.46,677.64,713.11,652.33,634.77,571.79,658.71,661.3,635.07,509.43,525.16,632.01,568,497.95,514.52,519.45,465.97,532.31,442.56,470.43,413.67,432.49,442.9,455.16,406.87,400.26,386.87,399.71,344.77,402.15,362.23,301.9,356.85,337.75,310.45,298.67,319.2,283.55,300.13,295.4,236.7,273.98,242.62,237.94,242.6,234.72,242.4,217.58,214.99,230.61,206.28,178.05,197.73,205.14,172.56,194.9,202.89,178.25,191.46,175.99,138.55,167.99,144.2,137.15,144.61,136.17,135.47,125.52,90.39,120.1,96.77,93.76,75.94,72.68,94.55,86.95,92.57,75.59,70.25,62.4,73.76,83.2,48.73,60.06,40.13,51.29,39.73,45.88,23.34,18.97,28.19,34.96,27.37,25.53,7.51,9.61,4.67,10.49,19.35,3.31,-14.37,-3.61,2.6,5.1,-2.3,-14.76,-15.41,-10.71,2.98,-9.91,-15.73,-22.34,-14.73,-10.56,-8.94,-14.54,-24.56,-26.63,-12.43,-15.03,-13.67,-26.57,-30.78,-20.69,-13.06,-13.24,-23.32,-30.92,-33.12,-21.09,-13.02,-23.87,-42.95,-43.41,-35.13,-18.78,-21.76,-33.65,-49.33,-38.38,-24.32,-34.81,-45.07,-54.17,-45.9,-35.77,-24.25,-37.32,-47.64,-55.8,-42.9,-37.26,-44.06,-57.11,-50.52,-42.99,-31.3,-32.56,-59.97,-54.38,-50.81,-46.71,-51.71,-60.45,-66.1,-61.15,-63.03,-56.05,-43.37,-78.53,-76.25,-70.23,-59.14,-57.48,-56.79,-68.37,-90.28,-67.93,-58.44,-63.03,-72.78,-101.23,-91.27,-78.05,-56.03,-92.18,-74.24,-80.95,-71.59,-88.33,-74.62,-83.45,-82.46,-70.34,-68.52,-89.87,-72.64,-98.65,-93.1,-82.05,-88.58,-72.62,-81.6,-92.12,-74.49,-68.35,-67.79,-77.59,-105.54,-75.98,-80.19,-60.81,-93.05,-107.61,-104.79,-74.7,-70.63,-71.66,-110.87,-118.24,-72.31,-61.13,-91.26,-86.37,-106.07,-91.49,-73.48,-98.09,-87.09,-116.18,-77.75,-103.71,-92.78,-68.72,-88.66,-101.63,-97.35,-69.93,-60.34,-85.96,-97,-109.45,-76.7,-56.26,-94.81,-88.5,-81.49,-96.96,-61.73,-65.84,-92.57,-95.04,-104.14,-64.53,-87.36,-96.04,-98.39,-82.09,-70.82,-89.01,-90.56,-90.81,-88.71,-66.64,-65.4,-69.84,-76.61,-85.5,-82.63,-73.88,-64.16,-63.04,-92.52,-85.89,-75.61,-77.95,-60.59,-74.46,-74.28,-89.22,-74.46,-53.07,-79.76,-66.32,-64.09,-56.84,-64.99,-67.03,-84.94,-62.36,-72.56,-52.57,-52.96,-59.16,-68.54,-66.01,-57.97,-39.63,-47.69,-62.08,-61.38,-56.71,-47.07,-44.74,-45.48,-52.93,-47.16,-37.88,-31.62,-42.09,-50.45,-51.37,-41.91,-34.56,-29.6,-43.95,-50.17,-33.99,-30.14,-32.96,-39.55,-45.97,-32.74,-23.89,-21.25,-33.09,-43.29,-37.29,-32.71,-19.44,-24.3,-35.51,-38.48,-35.13</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B170" t="str">
+        <v>[L_09_标记]</v>
+      </c>
+      <c r="C170" t="str">
+        <v>a: 29.5ms -141.7uv b: 62.8ms 622.4uv</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B171" t="str">
+        <v>[R_10_名字]</v>
+      </c>
+      <c r="C171" t="str">
+        <v>FERG(10)_dOps</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B172" t="str">
+        <v>[R_10_放大器]</v>
+      </c>
+      <c r="C172" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B173" t="str">
+        <v>[R_10_闪光]</v>
+      </c>
+      <c r="C173" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B174" t="str">
+        <v>[R_10_闪光背景]</v>
+      </c>
+      <c r="C174" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B175" t="str">
+        <v>[R_10_采样]</v>
+      </c>
+      <c r="C175" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B176" t="str">
+        <v>[R_10_分析时间]</v>
+      </c>
+      <c r="C176" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B177" t="str">
+        <v>[R_10_数据长度]</v>
+      </c>
+      <c r="C177" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B178" t="str">
+        <v>[R_10_详细数据(uv)]</v>
+      </c>
+      <c r="C178" t="str">
+        <v>-21.7,-21.43,-19.11,-14.56,-10.65,-8.62,-9.01,-12.05,-15.78,-18.92,-19.64,-18.05,-14.25,-10.03,-7.02,-6.87,-9.17,-13.37,-17.78,-20.69,-20.98,-19.43,-16.34,-11.86,-10.17,-11.13,-14.83,-18.38,-21.01,-20.65,-18,-13.29,-7.47,-3.66,-2.59,-3.03,-6.98,-9.37,-10.71,-12.41,-9.34,-8.17,-6.08,-6.19,-9.61,-15.29,-22.94,-26.48,-32.08,-30.56,-27.21,-26.21,-20.63,-21.4,-20.99,-21.86,-22.13,-21.15,-16.17,-11.37,-1.76,5.67,9.31,9.49,7.74,3.16,-5.49,-8.39,-11.44,-12.91,-14.91,-18.25,-22.51,-30.47,-41.16,-42.83,-51.11,-48.84,-43.58,-43.9,-28.68,-24.73,-18.6,-13.61,-8.33,-1.8,-0.88,8.94,20.36,22.76,30.54,32.42,17.51,13.75,-0.16,-7.7,-17.49,-26.1,-28.88,-32.26,-40.06,-45.59,-55.14,-66.31,-58.63,-56.91,-45.27,-38.27,-22.14,-6.78,4.7,13.1,27.03,32.67,41.07,43.76,38.5,55.27,42.66,33.3,28.44,13.6,-6.45,-26.2,-38.29,-47.1,-66.08,-54.83,-74.33,-59.77,-63.78,-75.91,-64.94,-59.79,-37.79,-21.86,-1.12,14.44,32.85,33.09,42.93,58.29,47.51,42.6,47.47,39.8,34.09,14.9,3.13,-16.12,-38.32,-55.79,-57.58,-73.36,-74.96,-83.06,-78.91,-70.14,-57.87,-48.23,-44.15,-31.36,-17.07,-1.56,13.62,27.87,31.38,45.57,49.84,46.99,39.41,25.77,18.09,8.77,-1.31,-8.13,-16.23,-30.93,-46.7,-50.89,-52.9,-61.56,-61.18,-46.3,-39.57,-26.88,-20.37,-14.9,-10.41,-5.45,4.11,7.53,17.96,27.45,37.03,33.69,24.47,22.89,7.89,4.2,-5.39,-9.76,-12.7,-12.62,-14.51,-19.5,-28.04,-35.2,-33.29,-36.66,-33.24,-25.85,-14.48,-8.34,-2.4,0.04,-0.69,1.85,-2.29,0,3.23,8.67,9.51,11.01,8.94,1.9,-5.32,-12.71,-17.1,-17.98,-18.52,-15.52,-11.75,-11.64,-15.7,-17.61,-22.23,-21.68,-20.59,-16.23,-10.81,-5.56,-2.5,-1.56,-4.5,-7.9,-10.65,-12.41,-10.97,-8.14,-4.62,-2.92,-2.9,-6.08,-10.7,-15.39,-18.38,-18.72,-15.83,-12.37,-7.53,-5.5,-6.26,-9.1,-12.29,-14.73,-15.07,-12.79,-8.5,-3.77,-0.53,-0.09,-1.62,-5.5,-9.25,-11.38,-11.06,-8.27,-4.26,-0.68,0.92,-0.12,-3.34,-7.41,-10.57,-11.45,-9.66,-5.73,-1.61,1.38,1.83,-0.33,-4.08,-7.76,-9.76,-9.23,-6.31,-2.21,1.3,2.68,1.54,-1.9,-6.12,-9.35,-10.34,-8.72,-5.2,-1.38,1.06,1.04,-1.55,-5.63,-9.57,-11.78,-11.34,-8.57,-4.65,-1.33,-0.08,-1.48,-5,-9.21,-12.39,-13.25,-11.47,-7.86,-4.02,-1.6,-1.68,-4.26,-8.3,-12.1,-14.09,-13.44,-10.45,-6.38,-2.97,-1.66,-2.99,-6.37,-10.37,-13.25,-13.76,-11.64,-7.75,-3.67,-1.09,-1.03,-3.45,-7.26,-10.76,-12.4,-11.39,-8.09,-3.79,-0.23,1.17,-0.07,-3.35,-7.17,-9.81,-10.07,-7.73,-3.69,0.44,3.01,3.01,0.54,-3.27,-6.72,-8.26,-7.18,-3.84,0.39,3.8,5,3.53,0.07,-3.88,-6.6,-6.92,-4.66,-0.77,3.11,5.36,5.02,2.23,-1.83,-5.47,-7.16,-6.21,-3.05,0.93,4.02,4.86,3.05,-0.71,-4.87,-7.73,-8.14,-6,-2.27,1.4,3.38,2.77,-0.25,-4.46,-8.15,-9.82,-8.84,-5.68,-1.74,1.25,1.96,0.05,-3.73,-7.82,-10.54,-10.75,-8.42,-4.54,-0.79,1.23,0.66,-2.27,-6.31,-9.75,-11.11,-9.81,-6.35,-2.19,0.96,1.8,0.03,-3.55,-7.37,-9.74,-9.59,-6.92,-2.77,1.18,3.33,2.87,0.08,-3.77,-6.94,-8.01,-6.42,-2.74,1.56,4.76,5.6,3.83,0.29,-3.44,-5.67,-5.37,-2.59,1.58,5.45,7.47,6.83,3.89,-0.05,-3.27,-4.35,-2.79,0.8,4.92,7.86,8.4,6.32,2.52,-1.39,-3.75,-3.58,-0.95,3,6.58,8.24,7.24,3.97,-0.22,-3.62,-4.83,-3.39,0.03,3.91,6.56,6.78,4.42,0.41,-3.63,-6.05,-5.9,-3.3,0.57,4,5.48,4.32</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B179" t="str">
+        <v>[R_10_标记]</v>
+      </c>
+      <c r="C179" t="str">
+        <v>97uv</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B180" t="str">
+        <v>[L_10_名字]</v>
+      </c>
+      <c r="C180" t="str">
+        <v>FERG(10)_dOps</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B181" t="str">
+        <v>[L_10_放大器]</v>
+      </c>
+      <c r="C181" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B182" t="str">
+        <v>[L_10_闪光]</v>
+      </c>
+      <c r="C182" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B183" t="str">
+        <v>[L_10_闪光背景]</v>
+      </c>
+      <c r="C183" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B184" t="str">
+        <v>[L_10_采样]</v>
+      </c>
+      <c r="C184" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B185" t="str">
+        <v>[L_10_分析时间]</v>
+      </c>
+      <c r="C185" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B186" t="str">
+        <v>[L_10_数据长度]</v>
+      </c>
+      <c r="C186" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B187" t="str">
+        <v>[L_10_详细数据(uv)]</v>
+      </c>
+      <c r="C187" t="str">
+        <v>1.71,4.42,1.67,-5.32,-12.79,-16.38,-13.25,-5.29,1.6,4.51,2.54,-3.34,-9.11,-9.94,-5.21,3.7,12.24,15.09,11.39,4.56,-1.74,-2.87,1.19,8.44,12.39,12.52,6.35,-3.5,-11.34,-15.04,-12.99,-5.68,1.39,2.01,-5.39,-10.98,-15.74,-12.98,-4.61,6.36,14.55,17.29,17.69,10.19,6.74,11.35,15.75,19.92,22.01,19.23,9.93,-1.17,-12.3,-16.5,-18.35,-13.65,-15.64,-22.89,-27.94,-33.04,-38.09,-40.57,-26.84,-10.87,-2.66,2.67,4.67,2.54,6.4,13.48,31.11,42.87,47.55,31.08,25.07,11.27,-0.49,-4.78,-6.82,-12.03,-17.03,-34.11,-46.35,-53.5,-61.18,-67.11,-56.79,-45.56,-37.68,-25.22,-23.36,-16.22,-5.92,10.58,33.66,40.47,62.8,49.22,61.04,40.92,34.25,30.85,37.34,24.44,11.69,-7.63,-26.3,-45.64,-60,-60.74,-64.89,-48.32,-55.05,-60.46,-56.79,-41.66,-33.48,-10.47,14.04,33.2,40.54,49.25,51.28,46.7,54.66,57.43,68.84,49.14,39.74,29.28,4.43,-15.92,-28.37,-35.48,-43.37,-53.27,-59.28,-58.79,-58.91,-57.34,-50.6,-41.15,-17.97,-4.05,6.11,11.73,15.52,25.27,36.82,51.13,57.97,50.22,37.19,34.88,14,2.81,-5.14,-9.32,-12.72,-22.61,-26.8,-43.41,-59.37,-54.26,-56.23,-40.19,-35.75,-21,-21.73,-18.79,-16.9,-11.38,3.59,17.86,27.84,26.64,24.97,14.8,7.61,6.54,3.12,9.51,8.72,3.56,-6.06,-18.32,-30.81,-31.06,-27.27,-23.32,-11.43,-15.29,-14.5,-22.03,-21.75,-16.3,-6.67,4.63,13.2,13.72,9.38,5.73,-0.4,3.92,6.89,14.26,14.88,12.1,4.04,-5.78,-11.98,-12.36,-7.44,-2.02,2.03,-1.16,-7.89,-14.8,-16.74,-13.82,-6.52,2.19,6.17,4.35,-1.95,-8.47,-10.93,-7.97,-1.02,6.37,7.58,3.95,-4.06,-12.35,-15.32,-12.78,-6.46,-0.69,0.32,-4,-11.75,-18.54,-20.34,-16.31,-8.83,-2.65,-1.46,-5.53,-12.91,-18.8,-19.62,-14.87,-7.18,-1.41,-0.57,-5.46,-13.27,-18.97,-19.29,-14.23,-6.69,-1.24,-1.18,-6.51,-14.01,-19.05,-18.68,-12.81,-5,0.29,-0.02,-5.53,-12.78,-17.17,-15.87,-9.51,-1.68,3.12,2.2,-3.73,-10.86,-14.8,-12.98,-6.34,1.27,5.43,3.73,-2.64,-9.77,-13.26,-10.92,-4.07,3.24,6.7,4.27,-2.53,-9.58,-12.63,-9.82,-2.85,4.09,6.78,3.59,-3.64,-10.62,-13.24,-10.02,-3,3.49,5.41,1.47,-6.1,-12.92,-15.05,-11.39,-4.31,1.75,2.95,-1.61,-9.4,-15.92,-17.46,-13.28,-6.1,-0.43,0.14,-4.92,-12.77,-18.85,-19.69,-14.95,-7.63,-2.29,-2.26,-7.71,-15.47,-20.99,-21.05,-15.7,-8.22,-3.18,-3.65,-9.37,-16.95,-21.82,-21.06,-15.1,-7.5,-2.78,-3.71,-9.68,-17.01,-21.2,-19.64,-13.15,-5.51,-1.18,-2.62,-8.82,-15.91,-19.46,-17.17,-10.26,-2.7,1.13,-0.89,-7.38,-14.26,-17.22,-14.32,-7.13,0.19,3.39,0.71,-6.1,-12.81,-15.26,-11.86,-4.54,2.4,4.88,1.48,-5.69,-12.26,-14.26,-10.44,-3.09,3.37,5.05,0.91,-6.59,-13,-14.54,-10.34,-3.04,2.9,3.78,-1.05,-8.81,-14.99,-16.02,-11.45,-4.19,1.23,1.36,-4.06,-11.96,-17.78,-18.23,-13.23,-5.98,-1.04,-1.57,-7.45,-15.33,-20.67,-20.44,-14.95,-7.67,-3.14,-4.24,-10.44,-18.16,-22.88,-21.88,-15.86,-8.54,-4.38,-5.96,-12.39,-19.83,-23.85,-22.04,-15.5,-8.14,-4.36,-6.39,-12.97,-20.08,-23.36,-20.77,-13.76,-6.44,-3.08,-5.59,-12.32,-19.07,-21.65,-18.35,-10.98,-3.82,-0.99,-4.03,-10.93,-17.38,-19.32,-15.41,-7.84,-0.98,1.21,-2.43,-9.56,-15.74,-17.12,-12.74,-5.11,1.31,2.75,-1.55,-8.93,-14.87,-15.76,-11.01,-3.44,2.42,3.06,-1.92,-9.54,-15.25,-15.66,-10.59,-3.15,2.1,1.92,-3.7,-11.49,-16.9,-16.82,-11.44,-4.16,0.5,-0.45,-6.61,-14.46,-19.47,-18.83,-13.1,-5.94,-1.84,-3.46</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B188" t="str">
+        <v>[L_10_标记]</v>
+      </c>
+      <c r="C188" t="str">
+        <v>97.5uv</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B189" t="str">
+        <v>[R_11_名字]</v>
+      </c>
+      <c r="C189" t="str">
+        <v>FERG(11)_dMax</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B190" t="str">
+        <v>[R_11_放大器]</v>
+      </c>
+      <c r="C190" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B191" t="str">
+        <v>[R_11_闪光]</v>
+      </c>
+      <c r="C191" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B192" t="str">
+        <v>[R_11_闪光背景]</v>
+      </c>
+      <c r="C192" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B193" t="str">
+        <v>[R_11_采样]</v>
+      </c>
+      <c r="C193" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B194" t="str">
+        <v>[R_11_分析时间]</v>
+      </c>
+      <c r="C194" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B195" t="str">
+        <v>[R_11_数据长度]</v>
+      </c>
+      <c r="C195" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B196" t="str">
+        <v>[R_11_详细数据(uv)]</v>
+      </c>
+      <c r="C196" t="str">
+        <v>-7.48,-5.6,-3.67,-1.84,-0.27,0.93,1.65,1.85,1.52,0.68,-0.58,-2.17,-3.93,-5.74,-7.42,-8.81,-9.85,-10.43,-10.55,-10.1,-9.24,-8.04,-6.64,-5.09,-3.63,-2.32,-1.21,-1.01,-0.88,-1.46,-2.87,-4.02,-6.33,-8.73,-11.98,-14.01,-16.53,-17.95,-20.82,-21.37,-23.48,-22.87,-24.22,-22.41,-22.4,-25.47,-29.44,-30.7,-27.83,-35.68,-38.09,-38.73,-44.13,-40.31,-47.1,-62.61,-64.42,-73.88,-74.05,-72.65,-80.97,-92.98,-96.49,-108.35,-98.2,-111.16,-108.24,-88.76,-86.81,-88.6,-100.54,-93.61,-96.53,-123.75,-122.73,-104.68,-111.81,-89.73,-109.64,-81.33,-108.81,-93.28,-87.51,-50.13,-74.7,-39.94,-21.65,-31.09,12.28,0.37,-16.86,19.12,40.75,50.55,67,114.37,103.37,128.69,123.99,181.41,167.06,180.12,233.53,251.64,218.39,250.27,262.05,341.18,350.32,335.56,376.2,400.93,393.48,482.92,453.81,434.5,483.3,514.81,534.56,520.81,563.71,611.92,636.48,646,617.53,570.63,552.92,624.48,583.48,640.63,667.04,757.2,643,664.04,778.22,724.15,736.59,728.21,727.14,717.61,711.01,688.97,720.76,793.17,765.72,694.99,742.31,729.01,692.29,688.15,644.3,728.59,652.63,748.59,642.06,717.54,584.14,611.04,671.43,639.57,628.78,597.25,588.69,593.83,543.31,539.13,503.01,463.47,465.75,487.52,506.54,464.07,439.66,436.23,433.34,355.57,435.31,412.86,356.34,385.27,391.82,351.48,350.65,352.71,326.18,339.9,321.7,266.23,286.24,266.04,235.09,234.21,261.98,253.59,229.52,231.67,215.52,193.91,197.18,205.04,193.89,184.48,167.65,172.13,193.55,196.97,171.45,164.81,162.48,171.7,169.13,126.02,126.32,131.23,149.96,124.57,115.75,122.55,112.44,96.08,106.64,86.42,97.94,119.82,74.32,95.68,61.29,61.97,85.44,68.03,57.51,46.35,65.29,59.95,36.35,39.81,45.57,34.88,31.56,47.26,29.32,28.47,41.8,40.27,31.82,20.78,15.6,6.21,7.76,11.26,3.39,-4.58,-1.68,-6.76,-6.14,-6.14,-8.86,-6.71,-10.74,-7.73,-7.66,-3.23,-0.96,-5.05,-7.78,-10.59,-8.53,-12.84,-10.95,-17.61,-18.89,-25.21,-28.05,-27.23,-24.37,-26.53,-35.77,-29.16,-28.86,-35.78,-27.32,-28.71,-22.75,-32.66,-29.89,-26.73,-32.67,-32.69,-34.78,-38.61,-30.38,-41.31,-35.01,-39.04,-41.48,-43.41,-57.33,-59.18,-57,-55.32,-45.26,-58.69,-42.32,-47.61,-56.8,-54.01,-48.6,-44.79,-53.64,-48.47,-63.66,-51.22,-70.52,-56.92,-60.64,-61.23,-77.23,-65.33,-69.11,-71.58,-73.03,-67.64,-61.5,-80.22,-75.79,-77.59,-76.69,-58.64,-54.01,-64.77,-54.58,-80.95,-78.99,-59.63,-86.97,-95.62,-72.35,-70.35,-102.17,-91.48,-83.87,-96.25,-85.59,-94.4,-98.34,-96.36,-95.31,-85.97,-76.33,-94.27,-79.88,-77.22,-96.06,-89.49,-71.88,-92.28,-84.15,-83.12,-103.68,-86.06,-82.34,-102.47,-77.85,-103,-85.7,-90.89,-92.13,-95.61,-107.96,-85.42,-104.65,-73.73,-78.69,-95.55,-89.95,-91.86,-82.22,-97.99,-77,-93.48,-117.75,-80.82,-82.87,-118.38,-106.31,-79.3,-83.39,-113.64,-80.73,-92.99,-81.16,-71.59,-76.4,-69.48,-70.33,-73.64,-98.61,-72.53,-85.21,-110.12,-99.97,-115.4,-103.06,-89.53,-115.5,-100.53,-85.54,-79.82,-100.3,-79.09,-77.04,-95.26,-74.71,-81.98,-95.99,-77.65,-64.52,-65.7,-92.51,-84.69,-75.52,-94.04,-73.91,-99.33,-94.8,-76.21,-80.16,-77.39,-83.61,-73.67,-78.99,-81.69,-67.5,-58.28,-66.51,-73.62,-63.56,-49.11,-56.58,-60.15,-49.72,-53.77,-71.96,-60.09,-70.89,-71.55,-55.23,-72.72,-61.09,-62.93,-68.6,-45.78,-48.13,-54.08,-38.59,-37.3,-45.86,-33.76,-37.56,-38.34,-42.39,-50.6,-41.91,-45.71,-40.12,-39.01,-42.72,-53.17,-47.68,-49.6,-52.94,-41.52,-39.27,-35.66,-38.99,-31.21,-33.29,-32.28,-35.76,-36.13,-28.81,-26.17,-31.06,-36.18,-34.99,-39.27,-34.71,-35.28,-37.92,-41.83,-37.31,-42,-41.89,-37.36,-32.6,-34.5,-28.49,-27.85,-33.24,-24.19</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B197" t="str">
+        <v>[R_11_标记]</v>
+      </c>
+      <c r="C197" t="str">
+        <v>a: 33.2ms -179.6uv b: 69.8ms 786.1uv</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B198" t="str">
+        <v>[L_11_名字]</v>
+      </c>
+      <c r="C198" t="str">
+        <v>FERG(11)_dMax</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B199" t="str">
+        <v>[L_11_放大器]</v>
+      </c>
+      <c r="C199" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B200" t="str">
+        <v>[L_11_闪光]</v>
+      </c>
+      <c r="C200" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B201" t="str">
+        <v>[L_11_闪光背景]</v>
+      </c>
+      <c r="C201" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B202" t="str">
+        <v>[L_11_采样]</v>
+      </c>
+      <c r="C202" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B203" t="str">
+        <v>[L_11_分析时间]</v>
+      </c>
+      <c r="C203" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B204" t="str">
+        <v>[L_11_数据长度]</v>
+      </c>
+      <c r="C204" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B205" t="str">
+        <v>[L_11_详细数据(uv)]</v>
+      </c>
+      <c r="C205" t="str">
+        <v>2.58,6.5,11.01,15.34,18.77,20.73,20.91,19.31,16.26,12.34,8.27,4.82,2.62,2.08,3.33,6.15,10.05,14.33,18.23,21.05,22.28,21.7,19.38,15.73,11.37,7.07,3.55,1.42,1.01,2.37,5.2,8.94,12.89,16.26,18.43,18.91,17.56,14.58,10.39,5.73,1.29,-2.2,-4.14,-4.34,-2.95,-0.15,3.52,6.92,9.72,11.69,10.74,8.79,5.54,0.74,-4.52,-10.49,-13.95,-16.04,-16.53,-16.4,-14.95,-10.19,-9.34,-6.73,-8.94,-12.77,-17.23,-20.74,-23.62,-31.28,-46.35,-49.41,-46.98,-49.72,-59.06,-44.03,-61.8,-51.24,-59.37,-64.41,-64.61,-64.25,-67.8,-90.65,-77.37,-102.05,-104.75,-86.02,-90.27,-88.68,-95.47,-86.3,-93.67,-104.63,-86.2,-61.06,-64.61,-102.07,-58.7,-55.33,-48.89,-82.61,-28.31,-39.06,-19.48,-2.91,-13.45,14.47,6.3,42.75,47.95,54.78,66.35,102.75,91.84,125.18,130.89,137.59,166.11,222.58,251.24,227.71,268.02,285.42,281.95,348.16,329.31,361.17,401.37,340.02,387.06,384.53,429.64,422.3,458.04,563.27,460.86,564.22,543.39,526.31,615.61,592.61,648.48,583.85,566.9,620.77,710.26,659.53,662.82,628.07,644.94,755.23,691.38,693.68,703.61,708.5,704.93,797.76,784.6,761.92,696.55,713.56,714.53,719.52,651.43,770.49,785.7,803.96,746.85,699.8,711.58,712.01,689.61,642.78,627,631.28,669.11,655.77,635.94,663.71,554.45,611.61,565.33,557.69,524.56,590.42,562.33,466.57,501.14,466.69,517.61,446.42,410.98,450.47,448.59,436.08,442.67,425.4,369.98,383.63,363.35,380.87,285.13,363.22,311.14,299.13,279.43,263.87,307.8,293.97,316.29,238.86,223.41,253.26,216.39,203.7,189.75,241.58,191.78,183.48,222.67,155.01,166.18,191.02,199.8,159.04,195.42,190.52,146.4,159.09,135.36,121.59,137,100.22,147.09,137.18,100.28,118.04,126.63,100.11,110.56,103.78,99.42,109.64,87.5,91.53,93.27,82.79,64.01,68.51,71.81,60.49,43.2,64.02,74.77,62.7,48.16,61.22,45.33,37.22,34.29,28.38,18.22,22.15,25.24,15.33,25.04,23.24,19.14,19.8,28.48,28.86,28,20.92,10.53,4.68,1.51,-4.84,-6.37,-4.28,-3.43,-4.17,-6.22,3.52,1.94,-1.38,1.78,0.73,0.33,-9.53,-15.97,-18.46,-27.3,-21.57,-27.81,-28.5,-15.66,-21.48,-20.86,-8.58,-12.47,-18.44,-16.09,-24.89,-22.26,-32.16,-37.54,-37.59,-45.12,-37.98,-42.2,-39.24,-36.79,-34.49,-25.72,-29.88,-27.67,-30.35,-34.54,-40.67,-54.26,-48.79,-64.25,-61.4,-48.03,-45.82,-54.93,-39.64,-52.39,-42.8,-55.82,-55.67,-48.06,-48.35,-49.3,-63.12,-57.94,-68.68,-82.75,-78.19,-56.44,-72.28,-63.34,-67.99,-43.93,-50.99,-63.75,-55.7,-52.72,-68.4,-85.37,-78.75,-72.34,-77.84,-89.31,-77.56,-52.25,-63.99,-47.33,-52.25,-56.18,-59.28,-52.37,-74.87,-64.13,-69.6,-97.55,-94.11,-72.63,-80.82,-76.59,-71.36,-75.41,-59.53,-76.11,-56.99,-56.8,-61.73,-98.64,-104.64,-98.24,-91.38,-109.52,-99.07,-108.69,-67.22,-73.4,-90.64,-70.74,-55.98,-80.87,-94.12,-91.37,-81.27,-114.69,-110.81,-104.59,-99.76,-96.26,-89.53,-74.4,-77.88,-83.64,-85.63,-61.24,-67.29,-94.17,-109.09,-96.15,-110.41,-104,-95.78,-85.09,-104.38,-112.4,-92.28,-82.38,-77.65,-59.81,-61.4,-64.67,-76.3,-89.34,-105.75,-94.94,-84.27,-107.02,-103.8,-100.52,-98.72,-62.45,-75.2,-57.93,-58.02,-71.19,-53.38,-59.33,-87.95,-67.79,-94.66,-71.54,-97.97,-70.46,-75.88,-72.93,-66.71,-48.2,-52.86,-40.08,-60.06,-55.24,-60.06,-55.32,-73.2,-61.1,-59.41,-78.71,-76.55,-47.16,-62.79,-62.69,-43.35,-52.63,-36.36,-48.3,-33.44,-45.53,-53.95,-48.42,-52.31,-53.51,-65.14,-56.6,-47.77,-52.54,-44.51,-28.71,-40.93,-28.66,-44.15,-30.56,-39.36,-46.14,-43.09,-45.22,-55.99,-47.01,-45.06,-35.02,-37.4,-38.69,-32.19,-26.21,-25.01,-32.86,-37.25,-32.24,-37.81,-38.76,-45.59</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B206" t="str">
+        <v>[L_11_标记]</v>
+      </c>
+      <c r="C206" t="str">
+        <v>a: 33.0ms -187.0uv b: 69.6ms 850.2uv</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B207" t="str">
+        <v>[R_12_名字]</v>
+      </c>
+      <c r="C207" t="str">
+        <v>FERG(12)_dOps</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B208" t="str">
+        <v>[R_12_放大器]</v>
+      </c>
+      <c r="C208" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B209" t="str">
+        <v>[R_12_闪光]</v>
+      </c>
+      <c r="C209" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B210" t="str">
+        <v>[R_12_闪光背景]</v>
+      </c>
+      <c r="C210" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B211" t="str">
+        <v>[R_12_采样]</v>
+      </c>
+      <c r="C211" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B212" t="str">
+        <v>[R_12_分析时间]</v>
+      </c>
+      <c r="C212" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B213" t="str">
+        <v>[R_12_数据长度]</v>
+      </c>
+      <c r="C213" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B214" t="str">
+        <v>[R_12_详细数据(uv)]</v>
+      </c>
+      <c r="C214" t="str">
+        <v>-26.95,-26.68,-26.31,-26,-25.63,-25.22,-24.91,-24.57,-24.25,-23.94,-23.63,-23.36,-23.12,-22.75,-22.47,-22.17,-21.95,-21.67,-21.25,-21.02,-20.49,-20.07,-19.61,-19.07,-18.61,-18.2,-17.56,-17.08,-16.91,-16.64,-16.5,-16.33,-16.88,-16.98,-17.54,-18.32,-19.11,-20.08,-20.97,-21.84,-23.03,-24.34,-24.79,-25.2,-25.68,-24.73,-25.13,-24.36,-23.53,-22.47,-21.28,-19.9,-19.34,-17.97,-15.36,-17.4,-14.52,-17.58,-17,-19.39,-20.72,-24.13,-27.28,-30.18,-32.97,-38.89,-42.04,-43.99,-42.81,-44.32,-44.9,-44.1,-39.27,-35.31,-32.48,-27.36,-21.93,-17.68,-7.86,-3.5,1.39,3.3,0.75,4.87,4.53,0.28,-7.09,-12.97,-20.75,-27.9,-35.57,-40.18,-50.37,-52.33,-57.37,-55.12,-51.68,-50.03,-43.57,-36.37,-33.24,-19.41,-9.03,3.52,15.37,26.15,24.63,29.76,43.44,34.64,35.83,29.34,12,5.49,-8.05,-22.29,-33.13,-48.59,-56.91,-68.1,-73.59,-71.28,-78.15,-79.06,-65.87,-56.76,-38.29,-28.77,-14.16,0.16,17.19,31.72,28.63,38.24,45.15,45.02,35.69,19.14,11.21,-4.02,-16.18,-29.15,-46.93,-60.6,-68.1,-74.84,-79.18,-79.34,-84.61,-81.48,-66.74,-56.72,-50.13,-38.78,-24.71,-14.74,1.32,12.41,19.03,17.46,13.14,14.2,18.47,9.9,3.37,-6.3,-13.54,-22.06,-31.42,-35.19,-41.17,-45.79,-47.81,-50.91,-50.45,-43.62,-44.97,-38.29,-30.59,-20.75,-14.82,-8.16,-0.79,2.13,3.9,9.88,12.49,8.8,4.95,7.91,-0.04,-3.13,-5.07,-9.82,-13.98,-16.58,-18.57,-21.92,-23.75,-21.74,-22.16,-21.07,-22.49,-19.39,-19.14,-17.06,-15.28,-13.66,-12.39,-11.85,-10.53,-10.69,-11.91,-12.54,-14.45,-15.09,-17.12,-18.26,-19.93,-21.43,-22.98,-24.06,-25.63,-26.36,-26.8,-27.18,-27.93,-27.55,-27.76,-27.65,-26.93,-26.73,-26.4,-26,-25.68,-25.28,-24.91,-24.84,-24.32,-24.28,-23.79,-23.72,-23.48,-23.31,-22.92,-22.59,-22.19,-21.75,-21.24,-20.73,-20.02,-19.35,-18.75,-18.03,-17.22,-16.45,-15.69,-14.93,-14.2,-13.48,-12.79,-12.12,-11.48,-10.91,-10.32,-9.82,-9.35,-8.94,-8.56,-8.24,-7.95,-7.71,-7.52,-7.38,-7.28,-7.24,-7.24,-7.29,-7.4,-7.55,-7.74,-8,-8.29,-8.64,-9.03,-9.46,-9.93,-10.43,-10.98,-11.55,-12.15,-12.77,-13.42,-14.08,-14.75,-15.43,-16.11,-16.8,-17.47,-18.15,-18.8,-19.44,-20.07,-20.66,-21.23,-21.77,-22.28,-22.74,-23.17,-23.55,-23.89,-24.18,-24.42,-24.61,-24.75,-24.84,-24.86,-24.84,-24.76,-24.63,-24.44,-24.19,-23.9,-23.56,-23.16,-22.72,-22.23,-21.71,-21.14,-20.53,-19.9,-19.23,-18.53,-17.82,-17.08,-16.33,-15.57,-14.81,-14.04,-13.27,-12.51,-11.76,-11.03,-10.31,-9.62,-8.95,-8.31,-7.71,-7.14,-6.61,-6.13,-5.69,-5.3,-4.96,-4.67,-4.44,-4.26,-4.13,-4.06,-4.05,-4.1,-4.2,-4.36,-4.57,-4.83,-5.15,-5.52,-5.93,-6.39,-6.89,-7.43,-8.01,-8.62,-9.26,-9.92,-10.61,-11.31,-12.03,-12.76,-13.49,-14.22,-14.95,-15.67,-16.37,-17.07,-17.74,-18.38,-19,-19.58,-20.13,-20.64,-21.11,-21.54,-21.91,-22.24,-22.51,-22.73,-22.9,-23.01,-23.06,-23.06,-22.99,-22.87,-22.69,-22.46,-22.17,-21.83,-21.43,-20.99,-20.5,-19.96,-19.38,-18.76,-18.11,-17.42,-16.71,-15.97,-15.21,-14.44,-13.65,-12.86,-12.06,-11.26,-10.47,-9.69,-8.92,-8.17,-7.44,-6.74,-6.07,-5.43,-4.83,-4.27,-3.76,-3.29,-2.87,-2.5,-2.18,-1.92,-1.71,-1.56,-1.47,-1.44,-1.46,-1.54,-1.68,-1.88,-2.13,-2.43,-2.78,-3.19,-3.64,-4.13,-4.67,-5.24,-5.85,-6.49,-7.16,-7.85,-8.55,-9.28,-10.01,-10.75,-11.49,-12.23,-12.96,-13.68,-14.39,-15.07,-15.73,-16.37,-16.97,-17.54,-18.07,-18.56,-19,-19.4,-19.75,-20.04,-20.29,-20.48,-20.61,-20.68,-20.7,-20.66,-20.57,-20.41,-20.2,-19.94,-19.62,-19.24,-18.82,-18.35,-17.84,-17.28,-16.68,-16.05,-15.38,-14.68,-13.96</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B215" t="str">
+        <v>[R_12_标记]</v>
+      </c>
+      <c r="C215" t="str">
+        <v>98.4uv</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B216" t="str">
+        <v>[L_12_名字]</v>
+      </c>
+      <c r="C216" t="str">
+        <v>FERG(12)_dOps</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B217" t="str">
+        <v>[L_12_放大器]</v>
+      </c>
+      <c r="C217" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B218" t="str">
+        <v>[L_12_闪光]</v>
+      </c>
+      <c r="C218" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B219" t="str">
+        <v>[L_12_闪光背景]</v>
+      </c>
+      <c r="C219" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B220" t="str">
+        <v>[L_12_采样]</v>
+      </c>
+      <c r="C220" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B221" t="str">
+        <v>[L_12_分析时间]</v>
+      </c>
+      <c r="C221" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B222" t="str">
+        <v>[L_12_数据长度]</v>
+      </c>
+      <c r="C222" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B223" t="str">
+        <v>[L_12_详细数据(uv)]</v>
+      </c>
+      <c r="C223" t="str">
+        <v>-2.47,-1.49,-0.58,0.24,1.07,1.8,2.48,3.13,3.76,4.28,4.72,5.1,5.45,5.81,6.11,6.26,6.33,6.35,6.3,6.33,6.03,5.62,5.26,4.71,4.09,3.39,2.74,1.93,1.27,0.29,-0.34,-1.09,-2.04,-2.62,-2.9,-3.59,-3.95,-4.33,-4.6,-5.14,-5.09,-5.82,-6.6,-7.01,-7.7,-8.98,-10.21,-11.37,-12.94,-14.7,-16.47,-18.1,-20.64,-21.92,-22.93,-25.14,-25.51,-26.27,-26.83,-25.84,-25.88,-24.16,-23.13,-21.05,-19.8,-17.79,-15.57,-14.55,-12.51,-9.23,-9.33,-11.27,-12.6,-13.91,-17.47,-20.27,-23.85,-26.52,-29.67,-32.18,-39.88,-37.34,-42.99,-42.42,-41.22,-34.86,-32.52,-28.85,-21.4,-14.29,-7.16,1.12,2.18,9.16,17.88,16.14,24,13.49,12.84,14.57,2.75,-2.15,-10.59,-20.79,-24.06,-31.48,-47.61,-46.49,-50.21,-50.85,-52.42,-46.45,-31.66,-25.1,-16.86,-3.34,9.06,17.05,30.95,48.05,42.54,51.05,47.65,45.72,37.42,34.8,21.93,13.47,0.48,-11.48,-28.36,-39.54,-44.66,-57.14,-54.98,-53.05,-54.49,-58.95,-36.26,-26.97,-16.37,-4.83,8.41,23.28,40.35,43.31,51.99,60.18,55.84,46.49,49.78,41.97,28.24,14.15,2.12,-13,-25.17,-38.36,-45.58,-62.46,-57.36,-69.19,-59.61,-49.02,-42.52,-35.46,-26.45,-12.69,-2.18,11.04,19.42,29.01,31.15,31.48,29.59,30.59,33.83,24.4,10.27,1.95,-6.35,-16.18,-25.33,-33.91,-39.93,-49.17,-44.71,-43.73,-47.08,-48.67,-40.7,-36.92,-28.85,-22.8,-15.79,-10.05,-6.48,0.42,-0.13,0.99,5.72,-1.19,1.64,-2.23,-5.74,-10.58,-14.13,-18.64,-21.97,-24.02,-27.12,-30.87,-29.05,-27.71,-26.49,-24.83,-24.74,-22.78,-19.28,-15.69,-12.59,-9.67,-7.38,-5.67,-4.24,-2.39,-0.99,0.2,-1.01,0.31,-1.27,-1.06,-1.47,-1.79,-2.17,-2.2,-1.93,-1.97,-0.96,0.22,0.79,1.9,2.74,4.28,5.79,6.71,8.02,9.15,10.07,10.85,11.49,12.23,12.19,12.69,12.56,12.5,12.45,12.19,12,11.62,11.26,10.85,10.45,9.98,9.47,9.07,8.56,8.06,7.51,7.01,6.31,5.66,4.92,4.12,3.29,2.36,1.45,0.42,-0.56,-1.68,-2.79,-3.92,-5.03,-6.19,-7.33,-8.48,-9.61,-10.73,-11.84,-12.91,-13.95,-14.96,-15.94,-16.88,-17.77,-18.62,-19.42,-20.17,-20.87,-21.51,-22.09,-22.61,-23.06,-23.46,-23.78,-24.03,-24.21,-24.32,-24.35,-24.3,-24.19,-23.99,-23.72,-23.37,-22.95,-22.46,-21.89,-21.26,-20.56,-19.79,-18.96,-18.07,-17.12,-16.12,-15.07,-13.98,-12.84,-11.67,-10.46,-9.22,-7.96,-6.68,-5.39,-4.08,-2.77,-1.46,-0.16,1.14,2.42,3.68,4.92,6.13,7.31,8.45,9.55,10.6,11.6,12.55,13.44,14.27,15.03,15.73,16.36,16.92,17.4,17.81,18.14,18.39,18.57,18.67,18.68,18.62,18.48,18.26,17.96,17.59,17.14,16.62,16.03,15.38,14.65,13.87,13.03,12.13,11.18,10.18,9.14,8.06,6.95,5.8,4.63,3.44,2.23,1.01,-0.22,-1.45,-2.68,-3.9,-5.11,-6.31,-7.48,-8.62,-9.74,-10.82,-11.86,-12.86,-13.82,-14.72,-15.58,-16.37,-17.11,-17.79,-18.4,-18.95,-19.43,-19.84,-20.18,-20.44,-20.64,-20.76,-20.82,-20.8,-20.7,-20.54,-20.31,-20,-19.63,-19.2,-18.7,-18.14,-17.52,-16.84,-16.12,-15.34,-14.51,-13.64,-12.74,-11.79,-10.81,-9.81,-8.78,-7.73,-6.66,-5.58,-4.49,-3.4,-2.3,-1.21,-0.13,0.94,2,3.04,4.05,5.04,6,6.93,7.82,8.68,9.49,10.26,10.99,11.66,12.29,12.87,13.4,13.87,14.29,14.65,14.96,15.21,15.41,15.55,15.63,15.66,15.64,15.56,15.44,15.26,15.03,14.76,14.44,14.07,13.67,13.22,12.74,12.23,11.68,11.11,10.51,9.88,9.24,8.57,7.89,7.2,6.49,5.78,5.07,4.35,3.64,2.93,2.22,1.52,0.83,0.16,-0.5,-1.14,-1.77,-2.37,-2.95,-3.51</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B224" t="str">
+        <v>[L_12_标记]</v>
+      </c>
+      <c r="C224" t="str">
+        <v>96.5uv</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B225" t="str">
+        <v>[R_13_名字]</v>
+      </c>
+      <c r="C225" t="str">
+        <v>FERG(13)_dMax</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B226" t="str">
+        <v>[R_13_放大器]</v>
+      </c>
+      <c r="C226" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B227" t="str">
+        <v>[R_13_闪光]</v>
+      </c>
+      <c r="C227" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B228" t="str">
+        <v>[R_13_闪光背景]</v>
+      </c>
+      <c r="C228" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B229" t="str">
+        <v>[R_13_采样]</v>
+      </c>
+      <c r="C229" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B230" t="str">
+        <v>[R_13_分析时间]</v>
+      </c>
+      <c r="C230" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B231" t="str">
+        <v>[R_13_数据长度]</v>
+      </c>
+      <c r="C231" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B232" t="str">
+        <v>[R_13_详细数据(uv)]</v>
+      </c>
+      <c r="C232" t="str">
+        <v>13.02,14.93,14.82,12.65,8.79,3.9,-1.1,-5.32,-8,-8.68,-7.31,-4.22,-0.1,4.18,7.65,9.62,9.6,7.63,3.85,-1.02,-5.95,-10.32,-12.95,-13.65,-12.49,-9.21,-5.22,-0.78,2.53,4.67,4.92,2.15,-1.88,-5.93,-11,-15.55,-19.05,-22.06,-19.7,-18.94,-14.34,-9.83,-7.04,-11.14,-10.28,-11.49,-16.35,-25.26,-27.62,-40.95,-40.66,-45.87,-51.03,-42.26,-41.23,-55.67,-46.87,-37.32,-42.09,-62.62,-65.89,-72.52,-63.76,-71.14,-88.15,-81.74,-96.52,-98.78,-75.73,-76.38,-66.4,-73.26,-73.59,-67.71,-66.87,-67.7,-85.9,-84.61,-92.62,-97.26,-47.84,-62.18,-60.32,-35.19,-40.59,-22.32,3.04,21.07,45.02,13.37,68.29,36.31,89.92,69.63,70.45,123.64,106.51,168.91,210.73,197.24,234.55,200.84,255.98,288.8,231.79,273.5,331.08,363.73,305.19,354.76,379.54,410.26,380.3,450.49,442.16,491.76,528.29,547.56,571.73,592.24,525.34,552.33,531.94,525.86,623.93,652.7,609.06,607.13,587.63,626.3,742.96,706.63,653.72,700.8,635.03,737.61,674.52,730.39,762.21,689.83,755.15,695.91,750.76,772.97,764.99,702.75,623.51,643.34,594.75,691.71,646.63,647.65,627.27,697.5,665.28,608.32,678.86,559.76,641.54,634.33,592.09,534.92,470.97,560.12,552.26,496.84,510.21,504.5,454.59,438.47,504.92,498.33,474.56,390.82,390.06,350.66,376.5,344.7,350.08,353.39,302.44,334.57,306.4,346.91,284.14,275.08,287.84,257.49,256.33,265.25,241.13,215.32,217.68,225.38,231.13,229.34,196.31,192.15,222.41,222.01,186.36,211.32,155.05,179.01,179.8,117.49,115.55,116.99,145.38,153.94,167.71,154.8,160.85,119.8,116.2,112.01,111.27,106.24,97.15,107.92,89.48,85.34,105.1,88.13,77.86,79.35,74.05,71.52,59.12,61.24,52.76,45.03,48.01,35.05,37.15,54.03,50.25,50.58,34.78,46.34,35.79,42.68,39.75,36.36,18.32,28.01,16.79,16.04,5.81,12.4,10.15,11.4,14.93,12.79,14.42,10.21,9.11,0.19,-0.28,-11.05,-11.98,-16.98,-22.71,-19.69,-17.67,-9.33,-11.02,-8.87,-8.88,-7.26,-9.16,-20.66,-24.9,-23.78,-30.37,-37.29,-40.47,-36.33,-38.16,-27.81,-30.32,-23.1,-29.59,-30.84,-25.48,-37.27,-35.05,-41.18,-51.32,-49.05,-46.37,-56.52,-48.61,-47.53,-39.78,-45.65,-42.97,-40.72,-37.34,-42.83,-40.45,-49.85,-62.05,-65.56,-57.82,-67.26,-51.31,-59.76,-57.42,-49.58,-52.28,-44.27,-55.36,-56.59,-59.27,-54.82,-57.33,-65.85,-63.26,-75.75,-63.88,-74.16,-54.84,-66.82,-64.25,-56.31,-48.63,-55.98,-76.72,-62.49,-85.04,-82.37,-86.52,-89.22,-65.69,-56.69,-72.65,-67.01,-52.73,-73.7,-65.66,-66.24,-63.58,-79.06,-95.77,-98.32,-71.01,-82.71,-89.48,-62.9,-66.41,-75.36,-72.01,-66.3,-60.99,-93.36,-74.87,-100.46,-101.72,-87.39,-93.78,-81.76,-104.74,-89.09,-82.68,-97.57,-86.07,-66.11,-100.61,-99.66,-76.77,-89.26,-115.08,-85.09,-91.35,-98.91,-93.35,-113.28,-92.06,-97.57,-83.53,-90.4,-102.66,-70.14,-94.17,-93.83,-119.13,-121.44,-121.18,-106.19,-83.71,-105.55,-88.67,-90.1,-69.47,-72.61,-95.74,-75.52,-86.92,-94.09,-85.4,-85.87,-104.12,-109.06,-106.6,-97.16,-72.11,-94.72,-81.18,-61.33,-84.92,-71.99,-67.01,-80.55,-82,-82.01,-96.57,-80.17,-85.69,-82.98,-62.5,-72.75,-48.32,-53.19,-64.97,-52.67,-79.03,-78.43,-72.76,-74.35,-71.38,-64.96,-70.08,-62.11,-64.78,-49.74,-58.09,-40.07,-58.52,-45.74,-52.54,-55.34,-73.15,-62.09,-75.4,-62.04,-74.22,-49.26,-50.69,-56.59,-43.8,-45.98,-45.89,-52.94,-59.16,-59.34,-51.11,-57.12,-60.9,-60.99,-54.31,-58.48,-53.23,-46.6,-37.61,-40.26,-36.42,-34.82,-37.75,-41.71,-53.32,-56.73,-60.72,-58.79,-49.53,-48.21,-45.38,-42.14,-35.97,-29.2,-26.49,-34.03,-37.71,-37.71,-38.81,-44.68,-50.35,-48.63,-43.67,-43.3,-31.18,-31.35,-23.46,-22.48,-25.84,-28.32,-27.2,-30.43,-33.19,-37.93</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B233" t="str">
+        <v>[R_13_标记]</v>
+      </c>
+      <c r="C233" t="str">
+        <v>a: 36.6ms -196.2uv b: 76.8ms 820.9uv</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B234" t="str">
+        <v>[L_13_名字]</v>
+      </c>
+      <c r="C234" t="str">
+        <v>FERG(13)_dMax</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B235" t="str">
+        <v>[L_13_放大器]</v>
+      </c>
+      <c r="C235" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B236" t="str">
+        <v>[L_13_闪光]</v>
+      </c>
+      <c r="C236" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B237" t="str">
+        <v>[L_13_闪光背景]</v>
+      </c>
+      <c r="C237" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B238" t="str">
+        <v>[L_13_采样]</v>
+      </c>
+      <c r="C238" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B239" t="str">
+        <v>[L_13_分析时间]</v>
+      </c>
+      <c r="C239" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B240" t="str">
+        <v>[L_13_数据长度]</v>
+      </c>
+      <c r="C240" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B241" t="str">
+        <v>[L_13_详细数据(uv)]</v>
+      </c>
+      <c r="C241" t="str">
+        <v>7.77,11.41,14.19,15.83,16.11,14.98,12.49,8.87,4.41,-0.47,-5.36,-9.8,-13.43,-15.95,-17.12,-16.89,-15.39,-12.66,-9.16,-5.27,-1.3,2.2,4.92,6.54,6.85,5.71,3.26,-0.5,-4.96,-9.5,-14.63,-18.52,-22.28,-25.04,-25.39,-26.29,-24.87,-21.42,-17.97,-13.58,-9.69,-7.78,-3.89,-2.67,-2.43,-3.2,-7.85,-13.75,-17.33,-19.57,-29.9,-31.48,-40.8,-45.74,-38.32,-48.89,-39.63,-39.97,-43.14,-48.2,-37.2,-35.3,-35.13,-24.03,-45.63,-45.47,-28.48,-47.68,-42.28,-46.7,-56.21,-68.84,-62.68,-62.95,-96.02,-89.39,-67.61,-64.78,-48.84,-49.68,-55.52,-50.21,-58.62,-26.78,-15.77,-19.26,8.23,-30.67,-4.46,-29.9,-16.08,-19.26,-27.49,15.08,46.55,38.75,28.1,91.44,111.3,100.8,128.05,118.45,187.6,171.08,203.15,181.96,224.85,218.73,209.63,234.85,268.29,269.82,240.52,285.89,300.46,368.76,371.66,365.94,418.59,417.4,446.99,427.95,406.89,463.52,494.5,448.42,513.22,507.91,559.33,552.68,572.47,605.34,639.41,575.87,591.29,546.28,613.64,630.48,642.61,702.49,695.68,749.05,654.95,718.24,667.43,671.7,739.4,696.24,771.77,625.9,651.11,672.64,595.57,674.92,636.43,737.16,634.1,646.46,681.26,706.54,691.08,670.08,608.08,605.81,682.88,704.73,592.47,662.08,609.41,630.16,515.64,516.87,541.12,528.98,536.77,576.61,468.27,540.66,451.5,471.02,458.23,487.58,476.51,413.76,397.09,383.81,403.16,423.95,397.25,398.68,368.07,388.78,355.87,304.69,338.24,310.63,328.98,307.14,308.52,294.8,298.31,293.95,264.73,317.37,278.24,240.81,236.98,222.46,226.84,191.34,184.89,221.62,202.77,144.72,161.84,176.15,152.15,174.37,181.92,175.59,138.8,153.08,128.41,177.16,123.55,168.14,127.51,136.84,126.33,126.26,91.97,109.9,87.52,85.45,71.05,67.74,73.41,70.6,70.42,60.73,73.13,69.58,54.06,56.14,66.37,61.7,53.04,59.38,51.09,44.62,37.24,34.54,20.35,17.98,11.42,-0.28,8.32,5.16,7.44,10.67,15.24,15.25,24.35,18.34,20.3,16.24,7.53,1.83,-4.6,-7.23,-12.5,-15.36,-19.69,-28.21,-26.38,-30.88,-28.35,-32.49,-22.8,-21.14,-18.78,-22.01,-17.42,-19.76,-19.2,-19.32,-23.6,-25.95,-30.85,-36.85,-35.07,-48.93,-45.88,-56.17,-59.08,-56.22,-60.08,-58.83,-49.31,-39.96,-44.81,-43.51,-34.63,-36.92,-35.23,-35.12,-29.33,-36.22,-52.67,-50.98,-56.16,-51.01,-68.51,-59.28,-72.78,-67.82,-69.98,-54,-66.71,-59.42,-61.89,-50.95,-52.25,-51.75,-51.46,-38.34,-46.47,-38.05,-50.93,-67.04,-58.08,-54.31,-82.29,-81.72,-69.81,-62.32,-69.86,-82.89,-71.51,-63.86,-50.2,-50.35,-57.34,-48.91,-47.03,-55.38,-40.73,-43.26,-79.74,-62.74,-79.29,-81.76,-71.57,-102.6,-87.8,-100.82,-99.37,-73.24,-91.65,-77.73,-87.01,-87.9,-59.87,-75.25,-74.28,-68.62,-89.03,-58.38,-89.35,-70.16,-101.2,-84.71,-84.26,-99.14,-94.56,-114.01,-117.41,-99.86,-81.77,-100.35,-76.8,-98.02,-83.88,-75,-87.95,-82.41,-93.14,-91.05,-72.35,-100.59,-97.23,-97.26,-102.23,-112.1,-108.66,-106.61,-116.47,-104.58,-104.53,-106.5,-87.41,-97.39,-93.85,-78.26,-63.97,-64.76,-87.12,-82.82,-95.25,-94.4,-105.59,-82.67,-90.2,-111.83,-103.4,-81.05,-82.64,-93.37,-85.56,-75.89,-66.74,-80.43,-47.42,-72.47,-51.21,-56.08,-43.11,-57.5,-77.77,-70.96,-61.49,-67,-63.92,-80.65,-90.81,-80.98,-63.24,-86.69,-82.76,-60.57,-68.96,-58.1,-42.43,-50.77,-43.66,-37.69,-45.44,-58.6,-54.54,-50.63,-56.31,-54.66,-63.02,-61.47,-62.45,-68.9,-65.07,-66.02,-72.29,-53.43,-56.57,-45.99,-38.54,-42.33,-38.29,-40.5,-48.54,-45.29,-39.29,-57.18,-47.9,-50.82,-54.63,-70.21,-69.64,-66.03,-68.47,-61.04,-50.91,-45.43,-50.11,-35.23,-36.51,-37.07,-35.42,-29.65,-31.69,-35.6,-32.48,-40.39,-42.96,-41.85,-47.45,-53.41,-50.48,-46.81,-45.46,-45.47,-41.69,-30.81</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B242" t="str">
+        <v>[L_13_标记]</v>
+      </c>
+      <c r="C242" t="str">
+        <v>a: 36.5ms -199.1uv b: 76.8ms 873.6uv</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B243" t="str">
+        <v>[R_14_名字]</v>
+      </c>
+      <c r="C243" t="str">
+        <v>FERG(14)_dOps</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B244" t="str">
+        <v>[R_14_放大器]</v>
+      </c>
+      <c r="C244" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B245" t="str">
+        <v>[R_14_闪光]</v>
+      </c>
+      <c r="C245" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B246" t="str">
+        <v>[R_14_闪光背景]</v>
+      </c>
+      <c r="C246" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B247" t="str">
+        <v>[R_14_采样]</v>
+      </c>
+      <c r="C247" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B248" t="str">
+        <v>[R_14_分析时间]</v>
+      </c>
+      <c r="C248" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B249" t="str">
+        <v>[R_14_数据长度]</v>
+      </c>
+      <c r="C249" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B250" t="str">
+        <v>[R_14_详细数据(uv)]</v>
+      </c>
+      <c r="C250" t="str">
+        <v>-13.92,-8.52,-8.7,-14.55,-22.48,-27.68,-27.04,-20.97,-13.53,-9.5,-11.45,-18.28,-25.73,-29.2,-26.43,-19.3,-12.33,-9.97,-13.71,-21.25,-27.81,-29.33,-24.74,-16.96,-10.78,-10.29,-15.23,-22.87,-27.68,-26.84,-20.47,-12.26,-7.15,-8,-14.07,-20.97,-24.37,-21.42,-13.63,-6.18,-3.16,-6.84,-14.32,-21.24,-23.38,-19.79,-12.49,-7.09,-6.62,-11.47,-19.3,-25.02,-24.46,-19.01,-10.41,-4.48,-4.04,-8.82,-14.99,-17.83,-13.84,-6.02,2.17,7.83,4.54,-4.13,-10.62,-14.29,-13.58,-8.51,-4.71,-6.5,-14.02,-23.87,-33.94,-37.26,-33.63,-28.72,-23.88,-21.45,-25.55,-30.53,-29.72,-23.92,-13.07,0.61,6.42,8.73,7.92,4.84,-3.31,-2.58,4.76,10.59,7.42,-5.13,-21.09,-34.58,-46.51,-43.39,-50.23,-45.17,-48.36,-58.58,-66.79,-69.42,-63.57,-41.46,-26.79,-12.78,-4.35,-1.91,5.77,11.51,24.02,27.11,46.6,36.7,33.12,19.26,7.23,-11.37,-16.95,-23.41,-30.27,-43.99,-61.07,-74.62,-90.23,-85.59,-70.73,-60.71,-55.5,-40.98,-33.38,-26.06,-16.53,2.31,18.97,43.5,50.87,55.32,59.79,34.86,28.35,35.34,23.1,17.09,5.72,-11.96,-34.57,-58.35,-61.93,-58.73,-63.18,-54.09,-53.5,-63.72,-66.96,-60.73,-45.55,-21.8,-4.12,8.26,19.52,13.19,19.4,14.02,19.99,27.7,34.77,32.18,11.79,-3.39,-18.15,-27.61,-32.87,-33.46,-37.65,-35.23,-46.35,-61.77,-62.49,-61.25,-41.77,-33.66,-24.47,-20.63,-20.75,-21.87,-17.63,-9.61,0.47,6.67,7.07,3.28,-4.84,-12.41,-15.2,-16.81,-11.93,-10.26,-13.89,-22.35,-31.48,-38.38,-37.19,-32.51,-25.42,-17.03,-19.12,-24.31,-29.11,-29.75,-23.53,-14.1,-5.65,-1.4,-5.01,-12.09,-16.62,-18.57,-13.27,-6.74,-1.59,-2.43,-8.33,-17,-22.85,-22.32,-16.69,-9.05,-5.45,-7.2,-13.71,-20.6,-23.61,-20.88,-12.96,-5.48,-2.79,-6.25,-13.6,-19.99,-21.47,-16.89,-9.22,-3.74,-3.37,-9.3,-17.4,-23.02,-23.06,-17.5,-10.25,-6.16,-8.06,-15,-22.77,-26.87,-24.71,-17.99,-11.04,-8.45,-12.06,-19.68,-26.66,-28.74,-24.76,-17.37,-11.33,-10.65,-15.81,-23.76,-29.51,-29.59,-24.01,-16.41,-11.64,-12.77,-19.14,-26.75,-30.81,-28.77,-21.89,-14.49,-11.19,-14.01,-21.11,-27.9,-30.01,-25.99,-18.25,-11.55,-9.98,-14.37,-21.8,-27.41,-27.48,-21.8,-13.76,-8.26,-8.58,-14.33,-21.69,-25.82,-23.92,-17.01,-9.26,-5.39,-7.66,-14.47,-21.35,-23.81,-20.14,-12.52,-5.64,-3.71,-7.85,-15.35,-21.39,-22.08,-16.93,-9.15,-3.61,-3.79,-9.58,-17.33,-22.17,-21.08,-14.8,-7.36,-3.53,-5.83,-12.89,-20.38,-23.69,-20.87,-13.84,-7.19,-5.29,-9.5,-17.35,-24.05,-25.57,-21.14,-13.75,-8.26,-8.34,-14.13,-22.18,-27.6,-27.16,-21.33,-13.97,-9.92,-11.89,-18.82,-26.48,-30.19,-27.74,-20.81,-13.89,-11.46,-15.14,-22.69,-29.42,-31.13,-26.78,-19.15,-13.07,-12.38,-17.5,-25.18,-30.52,-30.1,-24.12,-16.28,-11.43,-12.53,-18.77,-26.09,-29.73,-27.24,-20.05,-12.53,-9.26,-12.14,-19.16,-25.71,-27.47,-23.13,-15.25,-8.61,-7.2,-11.74,-19.16,-24.6,-24.45,-18.62,-10.63,-5.37,-5.99,-11.98,-19.4,-23.46,-21.47,-14.59,-7.08,-3.59,-6.27,-13.37,-20.37,-22.83,-19.18,-11.73,-5.2,-3.74,-8.32,-16.1,-22.24,-22.95,-17.87,-10.32,-5.18,-5.83,-12,-19.94,-24.8,-23.67,-17.45,-10.24,-6.77,-9.43,-16.73,-24.26,-27.46,-24.51,-17.47,-10.98,-9.34,-13.77,-21.66,-28.21,-29.47,-24.8,-17.32,-11.9,-12.11,-17.94,-25.85,-30.94,-30.11,-23.97,-16.46,-12.4,-14.39,-21.22,-28.59,-31.86,-28.95,-21.7,-14.63,-12.17,-15.8,-23.17,-29.53,-30.77,-26,-18.11,-11.95,-11.27,-16.35,-23.83,-28.81,-27.99,-21.7,-13.73,-8.93,-10.14,-16.41,-23.58,-26.94,-24.18,-16.85,-9.39,-6.33,-9.43,-16.56,-23.05,-24.65,-20.2,-12.37,-5.98,-4.94,-9.79,-17.39,-22.85,-22.64,-16.85</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B251" t="str">
+        <v>[R_14_标记]</v>
+      </c>
+      <c r="C251" t="str">
+        <v>97.9uv</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B252" t="str">
+        <v>[L_14_名字]</v>
+      </c>
+      <c r="C252" t="str">
+        <v>FERG(14)_dOps</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B253" t="str">
+        <v>[L_14_放大器]</v>
+      </c>
+      <c r="C253" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B254" t="str">
+        <v>[L_14_闪光]</v>
+      </c>
+      <c r="C254" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B255" t="str">
+        <v>[L_14_闪光背景]</v>
+      </c>
+      <c r="C255" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B256" t="str">
+        <v>[L_14_采样]</v>
+      </c>
+      <c r="C256" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B257" t="str">
+        <v>[L_14_分析时间]</v>
+      </c>
+      <c r="C257" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B258" t="str">
+        <v>[L_14_数据长度]</v>
+      </c>
+      <c r="C258" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B259" t="str">
+        <v>[L_14_详细数据(uv)]</v>
+      </c>
+      <c r="C259" t="str">
+        <v>-44.47,-42.21,-36.44,-29.84,-25.6,-25.66,-30.11,-37.14,-43.64,-46.74,-45.2,-39.78,-33,-27.84,-26.86,-30.43,-37.08,-43.69,-47.51,-46.72,-41.79,-34.95,-29.28,-27.4,-30.18,-36.2,-43.15,-47.28,-47.13,-42.73,-35.47,-28.89,-25.71,-27.04,-32.14,-38.42,-42.79,-43.19,-38.54,-31.19,-24.3,-20.44,-20.85,-26.01,-32.74,-38.63,-40.57,-38.08,-32.19,-25.91,-22.2,-23.04,-27.22,-34.7,-41.31,-44,-40.47,-33.83,-25.23,-19.23,-16.72,-18.89,-22.99,-27.55,-29.34,-25.78,-19.23,-15.08,-8.66,-5.78,-10.38,-20.98,-29.52,-36.73,-39.77,-38.19,-36.2,-31.56,-32.83,-37.11,-41.11,-53.61,-57.19,-51.44,-48.11,-35.81,-24.11,-14.93,-12.71,-10.99,-13.87,-12.03,-13.78,-6.81,-9.03,-4.15,3.89,-5.28,-18.65,-32.99,-47.88,-57.34,-64.59,-65.13,-70.98,-60.67,-61,-63,-71.64,-69.62,-66.85,-57.5,-41.44,-22.75,-7.59,9.87,9.84,5.59,13.71,7.2,7.85,20.17,12.62,4.01,1.11,-15.34,-35.23,-55.78,-74.19,-84.34,-85.27,-77.94,-70.75,-69.5,-83.32,-80.05,-67.35,-61.83,-48.47,-27.81,-10.03,15.39,35.08,42.92,48.74,25.84,35.73,26.01,18.06,9.5,4.79,-1.96,-15.44,-32.03,-48.49,-74.36,-78.87,-91.56,-88.56,-81.67,-73.18,-53.1,-49.85,-51.04,-40.77,-33.98,-20.8,-5.8,8.21,24.56,26.24,29,16.59,6.67,0.23,-7.16,-9.52,-16.13,-19.16,-25.63,-33.31,-50.43,-65.62,-65.47,-67.74,-65.63,-60.01,-45.37,-38.6,-37.06,-33.09,-35.14,-34.12,-29.43,-22.19,-14.07,-6.1,2.51,-2.14,-5.92,-14,-27.31,-32.91,-33.56,-30.97,-27.54,-26.01,-28.21,-33.15,-41.38,-45.18,-51.6,-48.7,-39.48,-31.83,-23.08,-18.99,-19.94,-23.67,-27.91,-30.16,-28.67,-23.86,-16.56,-10.67,-6.71,-9.42,-15.95,-24.07,-29.51,-31.04,-27.74,-21.58,-15.9,-12.66,-13.83,-19.58,-25.94,-30.81,-32.1,-28.47,-21.78,-14.37,-9.9,-9.95,-14.37,-21.04,-26.75,-29.04,-26.93,-21.19,-14.5,-10.14,-10,-14.37,-21.44,-28.27,-31.83,-30.77,-25.67,-19.15,-14.1,-13.04,-16.65,-23.33,-30.22,-34.35,-33.98,-29.37,-22.65,-16.99,-15.01,-17.69,-23.93,-31.01,-35.82,-36.28,-32.31,-25.71,-19.55,-16.67,-18.41,-24.03,-31.04,-36.31,-37.49,-34.04,-27.52,-20.83,-16.93,-17.56,-22.37,-29.12,-34.7,-36.53,-33.67,-27.32,-20.21,-15.42,-14.99,-18.96,-25.42,-31.32,-33.84,-31.71,-25.73,-18.42,-12.91,-11.52,-14.7,-20.87,-27.08,-30.38,-29.12,-23.71,-16.44,-10.42,-8.21,-10.68,-16.57,-23.11,-27.25,-27,-22.38,-15.37,-9.05,-6.17,-7.97,-13.59,-20.44,-25.43,-26.27,-22.57,-16,-9.52,-6.06,-7.2,-12.47,-19.54,-25.3,-27.21,-24.49,-18.44,-11.88,-7.85,-8.26,-13.04,-20.16,-26.52,-29.38,-27.6,-22.09,-15.46,-10.82,-10.39,-14.5,-21.41,-28.16,-31.82,-30.87,-25.85,-19.14,-13.85,-12.46,-15.69,-22.18,-29.08,-33.35,-33.15,-28.6,-21.8,-15.84,-13.42,-15.65,-21.52,-28.38,-33.13,-33.61,-29.55,-22.74,-16.18,-12.74,-13.9,-19.05,-25.77,-30.93,-32.1,-28.63,-21.95,-14.93,-10.59,-10.72,-15.13,-21.67,-27.23,-29.17,-26.44,-20.1,-12.85,-7.77,-7,-10.71,-17.08,-23.08,-25.87,-24.05,-18.28,-11.03,-5.44,-3.89,-6.96,-13.18,-19.63,-23.34,-22.55,-17.55,-10.53,-4.59,-2.37,-4.83,-10.86,-17.72,-22.34,-22.65,-18.53,-11.87,-5.71,-2.86,-4.68,-10.41,-17.55,-22.98,-24.34,-21.13,-14.89,-8.54,-5.05,-6.11,-11.37,-18.58,-24.64,-26.94,-24.58,-18.76,-12.21,-8.01,-8.18,-12.76,-19.81,-26.27,-29.34,-27.75,-22.3,-15.54,-10.59,-9.74,-13.45,-20.1,-26.75,-30.44,-29.55,-24.48,-17.54,-11.83,-9.91,-12.63,-18.72,-25.4,-29.61,-29.39,-24.77,-17.74,-11.36,-8.41,-10.1,-15.55,-22.19,-26.89,-27.41,-23.36,-16.42,-9.55,-5.7,-6.42,-11.23,-17.81,-23.03,-24.38,-21.08,-14.46,-7.34,-2.76,-2.62,-6.85,-13.39,-19.16,-21.44,-19.07,-13,-5.85</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B260" t="str">
+        <v>[L_14_标记]</v>
+      </c>
+      <c r="C260" t="str">
+        <v>93.5uv</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B261" t="str">
+        <v>[R_15_名字]</v>
+      </c>
+      <c r="C261" t="str">
+        <v>FERG(15)_dMax</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B262" t="str">
+        <v>[R_15_放大器]</v>
+      </c>
+      <c r="C262" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B263" t="str">
+        <v>[R_15_闪光]</v>
+      </c>
+      <c r="C263" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B264" t="str">
+        <v>[R_15_闪光背景]</v>
+      </c>
+      <c r="C264" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B265" t="str">
+        <v>[R_15_采样]</v>
+      </c>
+      <c r="C265" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B266" t="str">
+        <v>[R_15_分析时间]</v>
+      </c>
+      <c r="C266" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B267" t="str">
+        <v>[R_15_数据长度]</v>
+      </c>
+      <c r="C267" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B268" t="str">
+        <v>[R_15_详细数据(uv)]</v>
+      </c>
+      <c r="C268" t="str">
+        <v>-2.33,4.63,13.19,12.63,3.65,-2.46,2,11.53,14.32,6.99,-1.12,0.29,9.65,15.46,10.66,1.5,-0.32,7.75,15.85,14.16,5.02,0.17,6.02,15.41,16.96,9,1.66,4.43,14.08,18.56,12.68,3.48,2.74,11.67,18.36,15.38,5.33,1.21,7.67,16.19,15.22,7.1,-1.03,2.36,11.46,13.33,5.09,-5.44,-5.44,3.47,8.77,1.98,-9.25,-17.02,-10.2,-6.25,-8.9,-18.03,-23.13,-29.65,-14.35,-21.74,-37.35,-43.16,-49.29,-27.33,-37.73,-47.57,-57.13,-72.17,-65.55,-52.44,-44.91,-61.2,-58.88,-58.64,-71.82,-77.34,-75.73,-84.44,-80.83,-70.77,-74.02,-84.02,-58.39,-65.08,-71.6,-37.04,-70.62,-65.78,-61.46,-28.58,-0.43,-2.84,-28.46,0.2,44.35,26.71,46,66.2,63.57,55.91,104.82,121.38,148.9,103.66,180.7,187.14,190.06,237.48,206.86,226.05,265.83,315.95,321.04,295.89,314.14,334.44,388.82,442.38,375.35,448,404.19,531.7,508.91,548.88,539.61,563.12,581.63,632.46,568.81,654.72,623.66,679.8,699.61,631.24,633.55,601.92,710.1,737.76,692.78,771.16,719.01,747.1,745.2,750.18,706.77,771.05,670.22,806.94,752.54,749.45,713.82,684.6,741.59,759.07,788.03,689.65,783.66,719.14,738.04,696.01,701.42,718.71,666.81,709.65,711.87,693.91,655.44,637.96,588.75,680.83,618.02,639.13,623.28,547.37,549.18,494.63,545.85,508.59,462.39,528.18,515.75,435.5,461.63,459.89,397.91,418.08,394.8,401.17,433.66,370.93,382.85,420.43,395.51,339.91,339.56,334.2,360.92,380.34,312.6,301.32,309.41,322.52,316.11,268.4,254.45,244.29,289.56,259.66,244.45,212.61,223.56,240.91,220.91,196.36,178.82,167.89,188.28,198.35,189.78,161.43,191.53,137.29,178.11,169.7,136.93,154.96,156.27,132.24,115.59,132.22,131.59,94.77,124.34,120.94,97.08,112.46,92.64,79.91,83.84,76.26,90,68.35,69.43,79.29,66.74,66.46,47.25,55.59,49.63,43.81,54.17,39.77,29.67,25.51,42.06,44.15,31.99,9.81,22.83,23.58,22.12,9.68,6.98,9.37,11.53,15.49,8.33,-1.31,-9.28,1.66,7.86,3.5,-9.12,-12.38,-9,-1.82,2.75,-8.71,-17.32,-15.56,-3.43,1.44,-8.23,-17.54,-16.5,-10.21,-4.58,-7.38,-21.78,-27.43,-14.4,-6.24,-7.94,-20.13,-33.76,-26.3,-13.28,-15.69,-15.95,-34.25,-32.47,-28.95,-16.39,-22.9,-27.78,-28.55,-32.4,-23.23,-19.86,-23,-46.25,-26.73,-16.17,-32.83,-39.29,-47.56,-45.81,-39.47,-27.25,-24.29,-53.34,-45.19,-43.18,-34.46,-26.61,-55.34,-52.31,-44.57,-38.72,-48.91,-52.22,-72.21,-43.62,-56.09,-46.96,-42.88,-49.45,-77.3,-59.11,-39,-58.22,-55.91,-71.6,-73.64,-55.77,-57.27,-60.87,-65.45,-56.48,-59.01,-64.05,-74.73,-92.33,-82.11,-74.16,-46.71,-66.17,-61.62,-76.8,-77.36,-77.51,-50.77,-92.14,-85.83,-68.02,-59.01,-60.53,-73.01,-99.85,-86.9,-53.92,-77.74,-68.87,-79.12,-92.4,-93.82,-73.71,-87.35,-76.2,-88.33,-68.5,-77.36,-59.86,-58.2,-88.88,-77.23,-76.09,-48.15,-54.81,-65.41,-72.3,-58.37,-83.69,-74.91,-62.56,-97.47,-72.84,-75.69,-74.73,-59.79,-77.48,-57.72,-82.58,-71.21,-79.98,-59.7,-67.03,-68.67,-58.51,-57.3,-57.55,-91.58,-88.32,-53.72,-50.79,-67.95,-86.07,-65.55,-48.08,-48.1,-56.06,-85.11,-67.93,-56.37,-42.67,-72.01,-60.97,-64.62,-69.55,-61.43,-67.49,-64.11,-84.66,-50.51,-58.52,-69.57,-63.2,-67.02,-59.27,-54.41,-54.04,-44.7,-75.76,-59.98,-57.21,-40.26,-59.24,-59.3,-52.65,-41.98,-36.76,-36.82,-56.64,-63.39,-51.04,-27.79,-32.62,-45,-39.24,-41.67,-45.26,-37.74,-33.88,-43.27,-39.64,-36.89,-20.28,-32.35,-33.9,-40.89,-33.99,-19.32,-17.64,-36.26,-31.41,-27,-26.01,-22.48,-23.71,-28.01,-23.39,-19.8,-13.01,-18.41,-23.3,-22.06,-12.86,-6.37,-8.51,-22.28,-28.42,-17.49,-9.11,-2.56,-11.69,-20.67,-16.59,-12.52</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B269" t="str">
+        <v>[R_15_标记]</v>
+      </c>
+      <c r="C269" t="str">
+        <v>a: 40.4ms -213.1uv b: 84.3ms 964.3uv</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B270" t="str">
+        <v>[L_15_名字]</v>
+      </c>
+      <c r="C270" t="str">
+        <v>FERG(15)_dMax</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B271" t="str">
+        <v>[L_15_放大器]</v>
+      </c>
+      <c r="C271" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B272" t="str">
+        <v>[L_15_闪光]</v>
+      </c>
+      <c r="C272" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B273" t="str">
+        <v>[L_15_闪光背景]</v>
+      </c>
+      <c r="C273" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B274" t="str">
+        <v>[L_15_采样]</v>
+      </c>
+      <c r="C274" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B275" t="str">
+        <v>[L_15_分析时间]</v>
+      </c>
+      <c r="C275" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B276" t="str">
+        <v>[L_15_数据长度]</v>
+      </c>
+      <c r="C276" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B277" t="str">
+        <v>[L_15_详细数据(uv)]</v>
+      </c>
+      <c r="C277" t="str">
+        <v>14.34,11.36,13.73,18.97,21.71,19.1,13.74,11,13.63,18.94,21.56,18.84,13.54,11.05,13.9,19.29,21.77,18.89,13.61,11.31,14.38,19.69,21.96,19,13.75,11.66,14.61,19.9,21.94,18.48,13.2,10.8,13.41,18.21,19.85,15.6,10.71,8.4,11.07,14.13,13.87,10.26,3.11,1.29,5.05,7.56,2.83,-0.83,-6.06,-11.03,-16.81,-7.25,-9.94,-25.26,-25.84,-26.24,-39.18,-29.61,-43.82,-51.07,-64.08,-47.15,-49.93,-46.92,-63.2,-62.47,-87.9,-84.06,-82.05,-80.32,-67.46,-94.8,-97.49,-69.44,-106.51,-67.37,-62.84,-58.64,-64.63,-89.08,-87.23,-35.74,-57.08,-28.73,-47.51,-28.36,4.99,-22.86,-3.45,2.87,33.18,30.33,54.34,87.53,97.5,110.17,104.07,121.75,140.15,201.21,216.79,185.76,255.85,250.6,276.84,284.15,297.78,318.15,301.15,371.87,348.44,376.8,480.22,439.92,490.37,514.3,492.7,479.15,590.04,572.04,613.12,529.05,637.83,568.31,575.42,580.08,612.05,595.91,669.69,695.19,776.76,717.27,630.2,758.17,812.81,730.5,683.91,784.38,798.58,707.42,696.04,697.11,826.58,735.2,778.54,717.31,766.09,774.05,687.99,709.82,725.36,624.57,629.61,662.61,667.82,619.82,611.71,602.43,672.03,652.35,669.14,621.32,592.93,608.83,594.88,526.4,518.58,458.42,448.13,447.49,472.59,418.98,494.88,408.96,449.11,413.93,394.69,366.75,399.54,340.16,350.95,381.4,386.44,331.23,316.91,326.41,314.64,283.73,283.48,287.4,275.89,284.4,266.14,234.26,267.15,237.8,235.17,217.78,221.14,228.32,190.86,225.8,211.3,202.55,213.6,160.43,184.25,155.14,196.5,142.19,162.24,141.24,141.07,160.94,176.94,143.97,114.42,141.92,120.95,110.89,131.76,115.37,128.81,104.79,120.45,118.88,105.44,85.56,71.74,85,99.08,82.73,91.3,83.31,55.65,72.33,79.68,66.32,47.72,62.46,61.12,51.53,47,40.28,52.24,44.88,35.7,40.96,40.19,36.37,30.28,14.42,25.9,18.74,25.71,19.61,17.52,8.6,8.46,10.04,16.64,16.74,4.22,0.31,-2.21,7.65,-0.05,0.43,-7.43,-4.88,-9.62,-2.53,-5.82,-0.36,-10.56,-20.01,-18.78,-15,-1.39,-3.26,-10.11,-16,-16.08,-10.43,-17.24,-14.16,-15.55,-20.05,-18.22,-15.75,-17.14,-24.65,-31.22,-28.2,-21.74,-26.1,-12.62,-27.57,-18.81,-38.87,-33.44,-23.71,-31.03,-21.13,-26.09,-38.32,-42.19,-38.82,-29.44,-38.59,-37.11,-31.19,-35.1,-25.96,-40.07,-37.97,-36.37,-36.34,-41.82,-31.41,-49.04,-29.93,-40.6,-48.75,-59.38,-57.21,-42.59,-50.22,-50.51,-50.96,-41.9,-50.01,-50.55,-46.49,-48.62,-74.3,-51.53,-62.32,-39.13,-44.19,-50.82,-55.32,-70.76,-46.04,-61.75,-60.66,-63.68,-73.54,-60.93,-60.74,-67.13,-51.21,-66.67,-67.27,-76.46,-59.3,-78.33,-78.44,-70.68,-72.03,-55.36,-66.7,-64.94,-53.54,-88.08,-92,-56.46,-58.25,-62.96,-75.84,-96.94,-95.1,-58.34,-68.57,-50.92,-94.94,-90.94,-92.15,-73.04,-66.67,-62.61,-90.79,-77.79,-84.61,-83.8,-60.38,-68.06,-90.62,-72.65,-57.86,-66.24,-70.43,-51.49,-79.26,-94.42,-70.11,-63.04,-59,-56.2,-79.18,-53.97,-62.79,-49.7,-52.56,-52.16,-60.81,-83.24,-88.64,-75.88,-42.04,-53.81,-78.33,-68.03,-51.84,-75.17,-62.7,-47.92,-70.81,-72.96,-67.42,-45.99,-64.73,-58.25,-71.26,-52.79,-76.53,-62.88,-42.2,-60.98,-58.17,-59.87,-71.52,-39.43,-44.65,-56.75,-51.87,-64.36,-61.61,-37.22,-36.01,-50.38,-54.97,-46.85,-49.62,-36.49,-33.24,-31.24,-43.33,-41.14,-54.86,-41.55,-27.49,-35.78,-34.94,-52.86,-34.4,-41.34,-20.48,-38.3,-32.21,-42.54,-26.05,-26.77,-26.91,-19.01,-35.59,-37.76,-29.19,-20.79,-24.52,-16.02,-32.45,-33.19,-20.3,-24.6,-21.72,-11.34,-24.16,-22.65,-18.14,-19.62,-16.49,-16.73,-20.22,-18.39,-19.22,-8.3,-3.23,-10.19,-13.92,-15,-12.6,-4.5,-8.34,-6.31,-10.53,-16.41,-10.12,-6.25,-9.64</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B278" t="str">
+        <v>[L_15_标记]</v>
+      </c>
+      <c r="C278" t="str">
+        <v>a: 40.5ms -208.5uv b: 84.4ms 935.9uv</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B279" t="str">
+        <v>[R_16_名字]</v>
+      </c>
+      <c r="C279" t="str">
+        <v>FERG(16)_dOps</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B280" t="str">
+        <v>[R_16_放大器]</v>
+      </c>
+      <c r="C280" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B281" t="str">
+        <v>[R_16_闪光]</v>
+      </c>
+      <c r="C281" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B282" t="str">
+        <v>[R_16_闪光背景]</v>
+      </c>
+      <c r="C282" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B283" t="str">
+        <v>[R_16_采样]</v>
+      </c>
+      <c r="C283" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B284" t="str">
+        <v>[R_16_分析时间]</v>
+      </c>
+      <c r="C284" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B285" t="str">
+        <v>[R_16_数据长度]</v>
+      </c>
+      <c r="C285" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B286" t="str">
+        <v>[R_16_详细数据(uv)]</v>
+      </c>
+      <c r="C286" t="str">
+        <v>-17.44,-33.58,-23.32,-6.11,-15.08,-31.69,-22.3,-4.55,-12.54,-29.6,-21.16,-2.94,-9.94,-27.43,-19.96,-1.33,-7.4,-25.29,-18.9,-0.04,-5.21,-23.53,-18.29,0.71,-3.58,-22.31,-18.25,0.82,-2.48,-21.46,-18.49,0.65,-1.62,-20.85,-18.98,0.44,-0.81,-20.06,-19.22,0.14,0.02,-19.37,-19.5,-0.73,0.18,-19.56,-21.5,-3.02,-1.87,-22.09,-25.48,-7.3,-5.21,-25.8,-30.17,-12.06,-8.72,-28.47,-32.6,-13.17,-8.65,-26.46,-30.94,-11.52,-4.4,-22.05,-26.87,-6.54,-0.75,-16.43,-25.21,-7.2,-1.29,-21.22,-31.29,-16.02,-10.03,-29.06,-42.65,-27.97,-19.57,-40.52,-49.99,-31.33,-19,-36.17,-42.22,-21.99,-6.35,-16.43,-22.91,-4.22,16.82,4.31,-2.38,10.61,30.07,12.64,-6.25,3.37,11.16,-8.26,-29.67,-23.47,-20.21,-32.75,-61.02,-48.17,-40.91,-40.93,-60.74,-38.58,-19.72,-21.97,-27.56,-7.19,22.9,17.35,19.83,32.6,46.82,53.61,31.91,35.68,45.24,30.72,3.98,-1.85,1.29,-21.73,-46.88,-55.05,-44.26,-49.85,-81.44,-79.57,-63.87,-44.44,-62.32,-47.5,-14.76,-3.5,-8.12,10.94,37.94,47.31,23.68,34.9,58.11,39.43,20.87,18.54,20.01,4.4,-26.78,-39.78,-30.69,-41.64,-63.83,-78.85,-59.71,-58.23,-77.48,-76.58,-49.41,-28.74,-41.6,-31.13,-0.94,13.88,4.92,7.95,27.9,30.11,18.59,2.27,21.8,21.4,-0.9,-16.28,-5.84,-6.71,-31.81,-46.6,-33.3,-22.6,-47.07,-47.55,-31.22,-17.86,-28.81,-34.71,-12.97,2.64,-8.72,-14.3,4.73,20.08,3.72,-2.84,12.07,23.39,3.88,-9.98,3.98,13.55,-4.92,-19.7,-7.17,4.1,-13.21,-25.34,-12.65,1.07,-13.27,-26.02,-11.59,4.27,-7.41,-20.89,-7.64,8.08,-3.48,-18.52,-6.12,9.01,-3.13,-19.86,-9.38,5.34,-5.49,-23.23,-14.25,1.57,-8.55,-26.53,-18.32,-1.21,-10.22,-27.88,-20.36,-2.68,-10.22,-28.33,-21.36,-3.2,-9.61,-27.95,-22.03,-3.52,-8.91,-27.69,-22.7,-3.98,-8.38,-27.32,-23.39,-4.28,-7.51,-26.5,-23.51,-4.1,-6.14,-25.1,-22.98,-3.35,-4.16,-23.09,-21.97,-2.17,-1.89,-20.78,-20.66,-0.83,0.53,-18.33,-19.27,0.49,2.89,-15.9,-17.92,1.67,5.07,-13.62,-16.75,2.6,6.98,-11.58,-15.83,3.2,8.51,-9.89,-15.27,3.36,9.57,-8.62,-15.13,3.03,10.11,-7.84,-15.45,2.18,10.11,-7.53,-16.23,0.84,9.61,-7.65,-17.39,-0.93,8.68,-8.15,-18.87,-3.04,7.4,-8.9,-20.55,-5.36,5.91,-9.78,-22.29,-7.75,4.35,-10.66,-23.96,-10.09,2.84,-11.4,-25.41,-12.21,1.54,-11.87,-26.53,-14.02,0.54,-11.97,-27.2,-15.4,-0.07,-11.62,-27.38,-16.31,-0.23,-10.79,-27.02,-16.7,0.06,-9.47,-26.13,-16.61,0.78,-7.71,-24.76,-16.09,1.87,-5.59,-22.99,-15.22,3.22,-3.2,-20.95,-14.13,4.71,-0.68,-18.75,-12.93,6.21,1.83,-16.54,-11.77,7.58,4.18,-14.46,-10.79,8.69,6.26,-12.63,-10.1,9.42,7.94,-11.16,-9.8,9.69,9.15,-10.12,-9.94,9.44,9.84,-9.55,-10.55,8.67,10.01,-9.44,-11.61,7.41,9.68,-9.74,-13.07,5.71,8.94,-10.38,-14.82,3.67,7.88,-11.25,-16.77,1.43,6.63,-12.23,-18.77,-0.89,5.33,-13.17,-20.67,-3.14,4.11,-13.93,-22.36,-5.19,3.1,-14.4,-23.69,-6.91,2.41,-14.48,-24.58,-8.22,2.13,-14.08,-24.95,-9.05,2.3,-13.19,-24.79,-9.4,2.92,-11.79,-24.11,-9.28,3.96,-9.95,-22.95,-8.74,5.35,-7.74,-21.41,-7.89,6.98,-5.27,-19.6,-6.84,8.75,-2.67,-17.65,-5.73,10.49,-0.08,-15.7,-4.68,12.09,2.35,-13.89,-3.84,13.4,4.5,-12.35,-3.32,14.31,6.26,-11.17,-3.21,14.75,7.55,-10.41,-3.56,14.66,8.32,-10.12,-4.39,14.04,8.59,-10.27,-5.68,12.92,8.39,-10.82,-7.36,11.37,7.79,-11.69,-9.34,9.48,6.9,-12.76,-11.5,7.4,5.85,-13.91,-13.71,5.24</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B287" t="str">
+        <v>[R_16_标记]</v>
+      </c>
+      <c r="C287" t="str">
+        <v>90.7uv</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B288" t="str">
+        <v>[L_16_名字]</v>
+      </c>
+      <c r="C288" t="str">
+        <v>FERG(16)_dOps</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B289" t="str">
+        <v>[L_16_放大器]</v>
+      </c>
+      <c r="C289" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B290" t="str">
+        <v>[L_16_闪光]</v>
+      </c>
+      <c r="C290" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B291" t="str">
+        <v>[L_16_闪光背景]</v>
+      </c>
+      <c r="C291" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B292" t="str">
+        <v>[L_16_采样]</v>
+      </c>
+      <c r="C292" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B293" t="str">
+        <v>[L_16_分析时间]</v>
+      </c>
+      <c r="C293" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B294" t="str">
+        <v>[L_16_数据长度]</v>
+      </c>
+      <c r="C294" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B295" t="str">
+        <v>[L_16_详细数据(uv)]</v>
+      </c>
+      <c r="C295" t="str">
+        <v>-24.83,-28.84,-14.97,-6.62,-17.78,-29.04,-21.02,-7.34,-11.22,-26.32,-26.59,-11.86,-6.98,-20.3,-29.14,-18.05,-5.09,-12.25,-25.62,-21.27,-5.31,-3.11,-16.36,-20.99,-7.14,3.4,-6.92,-18.04,-10.38,2.93,0.9,-15.71,-17.85,-4.88,-0.36,-14.58,-25.81,-17.67,-6.24,-14.3,-28.9,-27.01,-11.62,-9.06,-22.18,-25.71,-11.77,1.21,-5.75,-15.85,-7.76,7.48,8.26,-2.97,-10.43,2.95,8,-5.41,-19.47,-15.38,-6.75,-16.59,-35.11,-42.44,-26.84,-31.49,-41.01,-51.33,-38.44,-26.09,-29.74,-40.54,-31.92,-9.72,-1.82,-11.2,-10.99,10.94,23.97,10.9,1.62,8.53,23.13,5.45,-13.19,-21.73,-15.74,-19.62,-42.45,-62.47,-54.38,-42.26,-52.34,-79.95,-67.77,-55.62,-43.21,-46.14,-38.57,-15.66,4.38,8.94,9.81,19.12,48.61,44.29,41.92,21.31,32.89,37.47,18.04,-6.29,-12.06,-11.09,-36.12,-55.19,-72.64,-55.06,-54.56,-71.85,-84.71,-65.87,-37.3,-38.94,-37.02,-20.31,9.28,18.49,23.83,22.23,38.2,55.75,57.4,24.97,40.15,42.41,21.76,1.48,-14.41,-15.6,-20.66,-45.59,-60.78,-59.2,-58.66,-76.58,-72.89,-64.79,-41.68,-36.04,-42.82,-34.68,-9.94,7,8.39,0.48,13.66,42.2,28.95,22.63,15.3,22.4,19.47,-7.69,-26.4,-25.58,-20.92,-37.31,-54.22,-55.39,-48.58,-46.67,-65.12,-60.99,-43.53,-28.08,-31.44,-36.61,-24.32,-4.14,1.56,-6.55,-6,7.48,20.59,3.7,-10.61,0.81,9.42,-4.02,-20.84,-24.73,-13.29,-15.77,-31.26,-40.52,-30.12,-17.33,-24.66,-36.94,-30.49,-11.7,-11.27,-21.98,-22.98,-6.73,4.55,-5.45,-16.54,-5.96,8.74,4.42,-11.76,-12.73,-0.27,3.02,-12.24,-22.68,-12.95,-3.43,-12.21,-26.35,-22.93,-8.22,-7.62,-23.59,-27.18,-13.98,-4.39,-14.76,-26.16,-18.56,-4.22,-7.41,-22.14,-23.43,-9.61,-4.14,-18,-27.79,-18.32,-6.5,-14.01,-28.93,-27.26,-12.88,-11.39,-26.18,-32.91,-20.41,-10.89,-20.48,-33.3,-27.27,-12.81,-14.36,-29.26,-31.86,-17.59,-10.63,-22.62,-32.99,-23.69,-10.54,-15.7,-30.23,-29.16,-14.05,-10.54,-24.32,-31.56,-19.57,-8.43,-16.7,-29.79,-24.82,-9.72,-9.69,-24.17,-27.82,-13.75,-5.34,-16.29,-27.26,-18.88,-4.84,-8.5,-23.05,-23.08,-8.02,-3.09,-16.23,-24.59,-13.49,-1.53,-8.79,-22.59,-19.11,-4.08,-2.98,-17.56,-22.83,-9.74,-0.64,-11.09,-23.33,-16.58,-2.53,-5.37,-20.5,-22.38,-8.12,-2.43,-15.43,-25.35,-15.73,-3.49,-10.05,-24.76,-23.07,-8.45,-6.47,-21.12,-28.02,-16.02,-6.24,-16.01,-29.29,-24.03,-9.83,-11.54,-26.83,-30.16,-16.4,-9.57,-21.83,-32.73,-24.1,-11.08,-16.27,-31.15,-30.6,-15.83,-12.27,-26.17,-33.94,-22.39,-11.29,-19.59,-33.07,-28.64,-13.72,-13.62,-28.28,-32.42,-18.67,-10.17,-21.07,-32.35,-24.33,-10.23,-13.63,-28.21,-28.53,-13.49,-8.19,-21.09,-29.57,-18.55,-6.23,-13.04,-26.74,-23.34,-8.04,-6.39,-20.63,-25.9,-12.67,-3.02,-12.94,-25.04,-18.23,-3.75,-5.95,-20.76,-22.61,-8.1,-1.8,-14.31,-24.14,-14.44,-1.73,-7.73,-22.25,-20.61,-5.75,-3.23,-17.58,-24.57,-12.58,-2.43,-11.83,-25.16,-20.1,-5.78,-7.15,-22.41,-26.06,-12.45,-5.41,-17.57,-28.79,-20.54,-7.54,-12.62,-27.74,-27.72,-13.21,-9.6,-23.65,-31.95,-20.9,-9.9,-18.25,-32.18,-28.37,-13.74,-13.67,-28.62,-33.39,-20.11,-11.69,-22.7,-34.5,-27.05,-13.14,-16.54,-31.42,-32.31,-17.58,-12.22,-25.19,-34.11,-23.47,-11.13,-17.8,-31.71,-28.69,-13.44,-11.52,-25.7,-31.24,-18.14,-8.19,-17.8,-29.97,-23.32,-8.6,-10.33,-24.94,-26.89,-12.24,-5.42,-17.49,-27.29,-17.53,-4.36,-9.76,-24.04,-22.38,-7.21,-4.05,-17.96,-24.89,-12.74,-2.03,-10.87,-24.02,-18.94,-4.25,-5.02,-19.97,-23.66,-9.91,-2.36,-14.12,-25.35,-17.18,-3.88,-8.53,-23.59,-23.78,-9.25,-5.3,-19.19,-27.76,-16.94,-5.79,-13.95,-28.11</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B296" t="str">
+        <v>[L_16_标记]</v>
+      </c>
+      <c r="C296" t="str">
+        <v>88.7uv</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B297" t="str">
+        <v>[R_17_名字]</v>
+      </c>
+      <c r="C297" t="str">
+        <v>FERG(17)_dMax</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B298" t="str">
+        <v>[R_17_放大器]</v>
+      </c>
+      <c r="C298" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B299" t="str">
+        <v>[R_17_闪光]</v>
+      </c>
+      <c r="C299" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B300" t="str">
+        <v>[R_17_闪光背景]</v>
+      </c>
+      <c r="C300" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B301" t="str">
+        <v>[R_17_采样]</v>
+      </c>
+      <c r="C301" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B302" t="str">
+        <v>[R_17_分析时间]</v>
+      </c>
+      <c r="C302" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B303" t="str">
+        <v>[R_17_数据长度]</v>
+      </c>
+      <c r="C303" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B304" t="str">
+        <v>[R_17_详细数据(uv)]</v>
+      </c>
+      <c r="C304" t="str">
+        <v>-1.74,11.15,11.61,-1.04,7.85,14.8,1.53,4.28,16.03,5.45,1.41,15.1,9.83,0.01,12.28,13.64,0.47,8.3,15.96,2.69,4.13,16.19,6.09,0.78,14.24,9.76,-1.02,10.49,12.71,-0.92,5.76,14.08,0.91,1.06,13.38,3.85,-2.63,10.56,7,-4.64,6.12,9.33,-4.61,0.91,9.94,-2.94,-4.03,8.48,-0.43,-7.88,4.74,2.03,-10.59,-0.87,2.92,-11.21,-7.06,2.84,-10.42,-14.43,-0.42,-9.9,-19.3,-7.93,-13.31,-23.09,-20.72,-11.15,-33.4,-30.62,-17.86,-35.9,-41.51,-31.21,-37.14,-48.92,-38.05,-42.04,-73.28,-59.72,-68,-74.99,-88.7,-80.86,-68.18,-106.55,-89.13,-84.54,-91.34,-85.36,-100.31,-115.25,-104.79,-83.59,-115.62,-84.48,-94.18,-79.74,-99.76,-63.33,-94.4,-94.54,-78.46,-78.95,-54.49,-17.3,-12.82,-22.82,8.15,-19.35,16.9,40.62,33.37,78.21,77.18,68.98,118.53,101.35,100.83,154.67,165.79,188.15,216.97,219.85,245.32,307.57,255.23,332.14,360.73,391.23,403.19,414.55,418.53,389.16,391.81,438.01,436.24,541.79,572.23,477.43,505.21,586.45,539.41,606,671.91,574.67,556.68,657.23,622.75,598.07,703.96,740.17,688.59,619.92,650.04,754.61,743.51,674.41,745.04,785.19,706.86,659.86,691.67,666.73,738.34,751.75,683.97,729.4,769.17,701.06,722.39,707.51,726.82,612.64,633.54,652.89,600.11,686.49,637.05,586.72,614.88,597.97,625.69,559.11,601.76,553.25,552.11,555.87,532.97,460.89,518.76,439.96,435.95,486.05,438.04,428.11,426.66,429.42,351.79,315.38,337.09,334.65,364.94,304.02,304.35,277.05,279.73,294.34,289.1,284.16,305.87,259.61,238.96,249.55,241.23,190.67,225.05,212.03,232.56,205.17,197.43,177.6,164.09,193.67,163.96,194.42,195.85,143.37,174.97,159.17,146.92,140.28,136.95,135.27,141.38,146.57,150.32,144.11,98.46,135.8,89.33,74.55,114.45,86.77,70.15,97.19,99,61.36,76,80.05,69.5,74.22,79.48,68.39,60.49,58.17,63.67,41,43.12,46.2,30.7,22.97,44.18,36.4,12.34,21.66,32.34,11.1,20.03,23.94,12.85,4.4,25.76,10.98,7.33,11.43,6.86,-3.38,2.69,6.46,-7.93,-4.46,3.62,-8.9,-11.8,1.32,-9.2,-18.4,-9.17,-12.42,-24.54,-15.57,-9.02,-18.84,-19.06,-8.56,-24.63,-24.44,-18.97,-30.3,-32.81,-23.08,-20.62,-38.54,-31.58,-24.64,-43.52,-37.46,-31.16,-45.22,-50.07,-36.33,-35.77,-56.26,-37.5,-36.15,-42.74,-46.12,-42.02,-53.22,-56.99,-45.36,-54.34,-63.94,-40.16,-59,-58.2,-50.25,-44.25,-71.77,-53.31,-38.33,-73.4,-50.63,-51.4,-58.03,-73.21,-58.41,-54.99,-66.39,-63.44,-55.67,-61.84,-71.94,-48.58,-67.55,-68.99,-57.97,-57.03,-85.49,-65.9,-59.23,-83.43,-66.1,-77.43,-62.47,-86.68,-55.92,-80.64,-87.37,-70.28,-64.27,-88.64,-86.66,-58.55,-83.49,-90.96,-78.73,-81.83,-87.59,-73.51,-85.39,-83.8,-68.45,-76.97,-97.17,-88.93,-89.65,-76.81,-66.71,-64.95,-78.8,-75.86,-72.49,-79.03,-77.34,-98.24,-91.59,-96.43,-85.8,-70.69,-80.5,-101.28,-92.43,-95.09,-105.1,-80.76,-97.96,-93.6,-68.3,-94.03,-113.84,-73.58,-68.78,-117.65,-95.65,-89.79,-104.42,-94.37,-84.74,-82.29,-120.94,-71.58,-111.72,-85.8,-82.99,-69.89,-117.52,-79.72,-83.44,-97.79,-86.46,-83.7,-83.88,-84.78,-93.35,-99.98,-107.22,-82.38,-76.27,-82.15,-73.49,-77.25,-85.51,-98,-58.35,-76.06,-89.25,-82.16,-81.88,-97.92,-77.8,-57.63,-80.36,-83.26,-51.74,-71.64,-70.13,-65.94,-65.8,-83.47,-60.71,-52.43,-70.79,-68.86,-71.31,-76.4,-53.89,-66.98,-57.69,-73.08,-57.35,-66.73,-61.98,-51.8,-40.41,-53.75,-50.35,-47.14,-71.11,-50.04,-53.04,-47.49,-47.78,-47.7,-44.39,-48.84,-44.45,-35.2,-48.07,-57.21,-34.07,-52.46,-50.11,-38.87,-55.49,-50.57,-40.33,-43.83,-49.12,-40.5,-32.28,-49.53,-42.79,-39.38,-42.92,-41.15,-31.75,-36.44,-42.15</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B305" t="str">
+        <v>[R_17_标记]</v>
+      </c>
+      <c r="C305" t="str">
+        <v>a: 44.2ms -212.9uv b: 91.1ms 1079.2uv</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B306" t="str">
+        <v>[L_17_名字]</v>
+      </c>
+      <c r="C306" t="str">
+        <v>FERG(17)_dMax</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B307" t="str">
+        <v>[L_17_放大器]</v>
+      </c>
+      <c r="C307" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B308" t="str">
+        <v>[L_17_闪光]</v>
+      </c>
+      <c r="C308" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B309" t="str">
+        <v>[L_17_闪光背景]</v>
+      </c>
+      <c r="C309" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B310" t="str">
+        <v>[L_17_采样]</v>
+      </c>
+      <c r="C310" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B311" t="str">
+        <v>[L_17_分析时间]</v>
+      </c>
+      <c r="C311" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B312" t="str">
+        <v>[L_17_数据长度]</v>
+      </c>
+      <c r="C312" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B313" t="str">
+        <v>[L_17_详细数据(uv)]</v>
+      </c>
+      <c r="C313" t="str">
+        <v>15.46,-3.55,-3.79,16.27,8.57,-7.16,8.4,18.12,-0.9,-1.39,18.62,10.99,-4.95,10.37,20.12,1.01,0.19,20.05,12.42,-3.8,11.2,20.89,1.63,0.43,20.11,12.38,-4.17,10.52,19.95,0.64,-1.09,18.18,10.5,-6.66,7.49,17.2,-2.28,-4.63,14.04,5.89,-11.11,3.14,11.31,-8.17,-11.73,6.62,-1.02,-19.58,-6.99,1.56,-21.53,-20.57,-5.55,-11.76,-33.88,-18.5,-16.97,-32.93,-39.41,-21.68,-28.4,-59.71,-36.5,-28.32,-60.44,-67.63,-51.06,-56.12,-80.66,-54.68,-61.49,-90.47,-88.37,-80.52,-75.89,-99.89,-85.2,-66.51,-96.8,-78.66,-63.4,-65.33,-113.4,-80.53,-65.78,-88.74,-105.03,-83.87,-78.73,-78.91,-40.87,-48.29,-35.17,-34.33,21.22,-30.26,8.01,-0.68,26.22,11.53,40.01,75.56,83.2,120.74,134.62,111.92,132.34,154.97,208.35,188.25,177.93,254.19,286.38,269.86,252.12,304.37,373.27,371.69,412.04,372.21,390.1,459.58,503.43,510.59,458.9,442.62,475.87,579.65,538.74,610.26,524.61,518.12,564.01,653.03,673.05,674.57,580.8,687.63,599.08,608.76,709.49,634.66,761.04,754.17,717.51,674.12,755.15,767.2,714.49,671.33,692.92,775.94,648.31,767.67,776.92,767.28,680.88,772.3,656.76,718.28,670.03,746.84,631.49,673.83,654.82,639,723.28,575.69,624.9,655.42,639.76,607.1,662.36,521.1,556.39,597.53,503.47,556.32,541.74,477.79,489.17,480.36,473.88,492.95,441.87,451.98,416.65,392.55,425.85,427.29,346.69,339.09,411.32,333.96,339.59,373.22,333.5,291.47,332.22,289.06,315.32,272.88,269.17,274.33,295.09,249.14,226.63,235.89,261.01,239.81,270.82,194.51,228.3,197.68,194.7,187.86,218.33,202.6,140.82,137.42,180.34,146.93,167.64,125.49,180.69,149.27,101.54,159.21,118.77,108.31,110.93,110.45,113.14,106.83,108.17,111.49,75.72,83.72,74.36,54.06,40.79,73.03,84.6,56.47,58.99,67.87,44.12,21.88,40.96,56.04,14.44,27.52,36.23,28.21,16.57,26.91,30.8,10.25,19.04,30.75,17.5,-3.64,15.97,10.73,-10.33,3.3,17.46,5.34,-10.49,3.44,1.17,-9.92,-6.11,11.01,-5.99,-21.91,2.19,3.84,-15.35,-5.93,-2.31,-15.25,-23.49,-4.48,-8.62,-24.58,-15.78,0.47,-25.28,-34.08,-8.25,-12.24,-32.47,-23.35,-9.03,-32.21,-35.53,-24.03,-22.93,-40.6,-38.2,-22.87,-40.64,-44.77,-26.74,-29.46,-40.2,-32.83,-32.2,-38.2,-51.43,-29.21,-39.25,-46.46,-48.63,-29.88,-47.36,-57.56,-42.71,-53.53,-72.3,-56.31,-51.64,-62.93,-64.57,-38.58,-49.33,-63.44,-74.4,-44.72,-63.73,-88.3,-44.53,-64.02,-65.36,-75.36,-69.04,-59.69,-91.51,-68.15,-64.9,-69.52,-73.22,-69.68,-59.98,-71.87,-67.9,-76.87,-89.11,-83.34,-75.49,-69.2,-90.83,-67.23,-63.27,-80.64,-84.25,-50.08,-64.52,-91.66,-70.25,-86.64,-99.55,-84.55,-65.11,-78.96,-83.36,-60.64,-56.99,-108.71,-95.55,-57.11,-65.04,-100.56,-69.34,-68.92,-72.06,-102.81,-53.58,-87.91,-80.3,-84.04,-56.56,-107.48,-96.26,-54.93,-76.57,-98.71,-75.3,-88.73,-91.52,-75.63,-66.81,-76.73,-117.66,-64.65,-88.71,-85.63,-108.66,-68.14,-93.06,-116.02,-99.65,-61.99,-117.57,-87.56,-62.01,-89.46,-100.84,-76.64,-83.67,-92.53,-86.59,-83.03,-95.85,-95.42,-82.46,-69.27,-114.19,-72.32,-63.45,-74.29,-78.91,-63.31,-89.41,-80.51,-98.59,-74.57,-86.75,-96.35,-81.28,-80.37,-77.29,-76.86,-75.61,-80.77,-90.64,-76.64,-58.77,-76.42,-65.91,-53.12,-61.37,-89.43,-50.11,-66.16,-71.71,-58.4,-58.69,-65.65,-76.32,-40.63,-36.37,-62.73,-58.75,-33.49,-47.02,-62.24,-32.4,-37.15,-66.27,-39.52,-33.49,-52.73,-50.5,-25.35,-40.83,-46.59,-35.86,-22,-46.74,-46.03,-22.48,-35.34,-44.64,-39.08,-17.7,-40.38,-39.92,-28.62,-16.74,-43.99,-39.33,-16.5,-26.44,-41.24,-29.86,-20.28,-42.22,-37.24,-15.06,-29.73,-47.11,-25.22,-18.96,-43.63,-38.61,-20.96,-26.15,-41.09</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B314" t="str">
+        <v>[L_17_标记]</v>
+      </c>
+      <c r="C314" t="str">
+        <v>a: 44.3ms -211.3uv b: 91.0ms 996.9uv</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B315" t="str">
+        <v>[R_18_名字]</v>
+      </c>
+      <c r="C315" t="str">
+        <v>FERG(18)_dOps</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B316" t="str">
+        <v>[R_18_放大器]</v>
+      </c>
+      <c r="C316" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B317" t="str">
+        <v>[R_18_闪光]</v>
+      </c>
+      <c r="C317" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B318" t="str">
+        <v>[R_18_闪光背景]</v>
+      </c>
+      <c r="C318" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B319" t="str">
+        <v>[R_18_采样]</v>
+      </c>
+      <c r="C319" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B320" t="str">
+        <v>[R_18_分析时间]</v>
+      </c>
+      <c r="C320" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B321" t="str">
+        <v>[R_18_数据长度]</v>
+      </c>
+      <c r="C321" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B322" t="str">
+        <v>[R_18_详细数据(uv)]</v>
+      </c>
+      <c r="C322" t="str">
+        <v>-5.35,-14.08,-9,-6.92,-14.96,-6.3,-9.77,-14.2,-5.87,-14.05,-13.59,-8.35,-18.08,-13.17,-12.67,-20.83,-12.39,-17.33,-19.98,-11.36,-18.94,-16.31,-10.43,-18.42,-10.26,-9.77,-14.53,-5.14,-10.94,-11.82,-3.26,-11.97,-9.37,-6.41,-17.17,-11.08,-14.97,-22.79,-16.52,-24.25,-28.35,-21.83,-33.34,-29.85,-25.61,-32.72,-22.49,-23.51,-24.95,-12.52,-16.49,-11.08,-1.49,-7.23,2.7,4.61,-4.15,6.03,1.27,-7.06,0.58,-13.56,-16.2,-16.66,-31.05,-31.81,-32.16,-41.56,-36.04,-39.59,-47.24,-31.47,-39.18,-30.99,-19.52,-22.08,-7.33,-1.97,0.09,13.82,12.59,18.46,25.46,23.23,24.36,18.13,2.65,3.93,-7.97,-23.01,-26.71,-37.85,-45.19,-44.21,-60.15,-58.32,-50.09,-68.86,-51.95,-42.19,-36.42,-17.62,-11.11,-0.66,21.6,24.67,39.08,31.98,40.11,41.08,26.23,20.49,28.03,0.34,-5.73,-17.05,-38.07,-42.12,-54.72,-80.13,-62.35,-79.19,-81.29,-63.82,-62.58,-60.26,-41.15,-34.06,-14.04,-2.33,11.48,24.26,25.17,37.68,47.55,46.21,44.31,27.59,17.61,14.73,-4.12,-23.42,-29.8,-44.92,-64.36,-72.82,-72.73,-85.55,-76.03,-88.47,-58.79,-57.92,-46.75,-28.48,-22.67,-5.22,12.4,17.6,26.56,30.93,34.78,37.91,23.81,19.36,19.69,1.78,-2.32,-9.25,-30.97,-31.51,-40.48,-53.88,-58.34,-62.43,-61.28,-47.57,-53.84,-43.16,-30.9,-33.12,-15.71,-9.34,-7.77,11.46,5.63,12.7,15.37,12.12,16.77,8.99,-0.08,3.9,-7.04,-17.63,-15.7,-29.24,-31.16,-31.89,-41.1,-41.14,-34.81,-48.32,-35.29,-32.79,-35.01,-21.41,-25.52,-18.44,-9.08,-16.98,-5.17,-3.35,-10.12,-1.64,-9.01,-11.79,-5.92,-16.52,-16.58,-14.77,-26.65,-21.97,-25.93,-32.84,-25.82,-32.15,-33.95,-23.9,-31.8,-26.62,-22.74,-29.26,-19.56,-20.35,-23.5,-12.78,-19.21,-17.9,-10.77,-20.21,-14.38,-13.15,-22.02,-13.61,-17.85,-22.49,-14.71,-23.11,-21.85,-16.97,-26.2,-19.85,-19.5,-26.38,-16.74,-21.47,-23.03,-14.48,-22.11,-18.64,-13.82,-22.13,-14.58,-15.07,-21.2,-11.99,-17.86,-19.53,-12.23,-21.09,-17.11,-14.13,-22.9,-15.19,-17.54,-22.98,-14.23,-21.13,-21.08,-14.51,-23.52,-18.44,-16.41,-24.49,-16.02,-19.42,-23.58,-14.96,-22.61,-21.5,-15.8,-24.96,-19.03,-18.4,-25.89,-17.3,-21.9,-25.08,-16.94,-25.25,-22.98,-18.29,-27.36,-20.51,-20.98,-27.62,-18.72,-24.24,-26.09,-18.34,-26.96,-23.41,-19.63,-28.3,-20.63,-22.19,-27.79,-18.76,-25.1,-25.63,-18.47,-27.3,-22.56,-19.83,-27.97,-19.63,-22.28,-26.78,-17.81,-24.86,-24.08,-17.66,-26.55,-20.73,-19.13,-26.63,-17.82,-21.57,-24.95,-16.27,-23.98,-21.99,-16.51,-25.39,-18.7,-18.35,-25.17,-16.16,-21.03,-23.32,-15.18,-23.51,-20.43,-16.06,-24.85,-17.49,-18.46,-24.54,-15.54,-21.5,-22.71,-15.31,-24.13,-20.05,-16.92,-25.47,-17.58,-19.88,-25.12,-16.29,-23.23,-23.32,-16.77,-25.91,-20.87,-18.98,-27.1,-18.79,-22.31,-26.54,-18,-25.71,-24.62,-18.96,-28.16,-22.18,-21.5,-28.94,-20.27,-24.86,-27.93,-19.74,-28,-25.64,-20.9,-29.92,-23.01,-23.47,-30.03,-21.09,-26.59,-28.38,-20.62,-29.22,-25.59,-21.81,-30.43,-22.7,-24.24,-29.78,-20.71,-27.02,-27.48,-20.29,-29.09,-24.27,-21.53,-29.62,-21.24,-23.89,-28.34,-19.35,-26.41,-25.59,-19.18,-28.06,-22.23,-20.65,-28.15,-19.34,-23.13,-26.5,-17.85,-25.6,-23.61,-18.18,-27.09,-20.42,-20.13,-26.98,-17.99,-22.93,-25.24,-17.16,-25.55,-22.49,-18.2,-27.03,-19.7,-20.75,-26.86,-17.91,-23.94,-25.17,-17.83,-26.71,-22.64,-19.58,-28.16,-20.3,-22.65,-27.9,-19.11,-26.09,-26.18,-19.66,-28.82,-23.77,-21.92,-30.03,-21.71,-25.26,-29.46,-20.92,-28.64,-27.49,-21.84,-31.02,-24.99,-24.31,-31.71,-23,-27.58,-30.58,-22.36,-30.59,-28.16,-23.4,-32.36,-25.39,-25.82,-32.31,-23.32,-28.8,-30.5,-22.71,-31.27,-27.57,-23.76,-32.33</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B323" t="str">
+        <v>[R_18_标记]</v>
+      </c>
+      <c r="C323" t="str">
+        <v>95.9uv</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B324" t="str">
+        <v>[L_18_名字]</v>
+      </c>
+      <c r="C324" t="str">
+        <v>FERG(18)_dOps</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B325" t="str">
+        <v>[L_18_放大器]</v>
+      </c>
+      <c r="C325" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B326" t="str">
+        <v>[L_18_闪光]</v>
+      </c>
+      <c r="C326" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B327" t="str">
+        <v>[L_18_闪光背景]</v>
+      </c>
+      <c r="C327" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B328" t="str">
+        <v>[L_18_采样]</v>
+      </c>
+      <c r="C328" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B329" t="str">
+        <v>[L_18_分析时间]</v>
+      </c>
+      <c r="C329" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B330" t="str">
+        <v>[L_18_数据长度]</v>
+      </c>
+      <c r="C330" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B331" t="str">
+        <v>[L_18_详细数据(uv)]</v>
+      </c>
+      <c r="C331" t="str">
+        <v>-13.01,-12.2,-25.38,-10.98,-13.52,-24.77,-9.35,-15.12,-23.94,-8.29,-16.9,-22.95,-7.65,-18.85,-21.75,-7.38,-20.66,-20.5,-7.9,-22.74,-19.43,-9.14,-24.98,-18.67,-11.09,-27.08,-18.14,-13.38,-29.01,-17.47,-15.58,-29.92,-16.3,-17.77,-29.8,-14.7,-19.16,-28.6,-13.1,-20.59,-27.29,-11.77,-22.31,-26.52,-12.12,-24.88,-26.49,-13.76,-28.95,-27.51,-17.11,-32.93,-28.18,-20.73,-37.4,-28.99,-20.98,-37.15,-24.55,-20.62,-33.32,-18.25,-16.41,-27.54,-10.96,-11.81,-21.16,-2.51,-10.24,-17.19,-3.08,-13.26,-19.69,-8.36,-22.4,-28.28,-17.44,-34.31,-35.53,-27.25,-38.88,-38.97,-28.03,-39.3,-32.1,-20.79,-30.25,-15.1,-4.28,-13.38,1.7,12.89,4.82,17.63,16.99,4.16,17.21,13.57,-2.34,2.02,-13.38,-29.03,-21,-39.42,-51.29,-44.69,-56.98,-60.23,-48.45,-63.7,-52.91,-36.62,-37.28,-23.11,-2.21,-9.12,14.32,30.8,19.46,28.57,36.38,28.4,28.1,33.13,1.73,8.93,-11.92,-35.88,-36.43,-49.47,-79.52,-70.39,-84.89,-90.22,-75.09,-86.3,-70.27,-54.89,-51.02,-34.75,-9.05,-12.53,5.64,32.48,31.6,40.95,44.24,21.07,27.38,27.34,12.91,5.69,-5.79,-31.74,-29.86,-48.42,-71.18,-52.65,-72.72,-90.55,-58.62,-78.74,-62.44,-42.54,-41.18,-35.12,-7.38,-6.68,5.01,21.51,13.36,24.66,43.83,29.73,34.35,26.05,1.21,5.46,1.41,-21.78,-19.73,-24.26,-49.4,-37.63,-36.97,-50.7,-35.91,-38.66,-49.85,-30.94,-29.16,-29.88,-6.76,-10.51,-8.21,8.7,-2.12,-0.29,16.15,1.15,1.64,13.41,-8.73,-8.56,-3.53,-22.65,-17.97,-17.43,-34.3,-27.2,-27.02,-41.85,-27.52,-25.73,-39.11,-22.37,-22.46,-31.72,-13.61,-18.17,-24.4,-7.89,-15.26,-18.98,-3.62,-17.41,-20.11,-5.47,-20.47,-21.02,-10.24,-26.42,-22.57,-13.81,-30.44,-22.46,-15.66,-31.24,-20.53,-16.93,-31.26,-17.52,-16,-28.64,-13.62,-15.34,-25.93,-10.18,-15.1,-23.83,-7.86,-15.92,-21.74,-6.23,-17.57,-20.31,-5.84,-19,-18.55,-5.71,-20.19,-16.51,-5.78,-21.01,-14.16,-5.9,-21.27,-11.53,-6.26,-21.13,-9.12,-7.08,-20.88,-7.1,-8.43,-20.55,-5.56,-10.24,-20.13,-4.64,-12.34,-19.6,-4.23,-14.66,-18.93,-4.31,-17,-18.08,-4.87,-19.26,-17.11,-5.86,-21.35,-16.04,-7.25,-23.17,-14.97,-9.03,-24.68,-13.93,-11.1,-25.8,-12.98,-13.37,-26.5,-12.15,-15.74,-26.71,-11.45,-18.1,-26.44,-10.93,-20.33,-25.68,-10.59,-22.35,-24.47,-10.45,-24.04,-22.85,-10.51,-25.36,-20.89,-10.77,-26.22,-18.68,-11.22,-26.61,-16.32,-11.83,-26.49,-13.9,-12.59,-25.88,-11.53,-13.44,-24.79,-9.31,-14.37,-23.28,-7.33,-15.32,-21.41,-5.69,-16.25,-19.26,-4.44,-17.13,-16.92,-3.65,-17.91,-14.49,-3.35,-18.56,-12.08,-3.55,-19.05,-9.8,-4.24,-19.36,-7.73,-5.39,-19.48,-5.97,-6.94,-19.39,-4.59,-8.84,-19.1,-3.65,-10.98,-18.61,-3.18,-13.29,-17.96,-3.21,-15.65,-17.15,-3.73,-17.96,-16.23,-4.71,-20.12,-15.22,-6.11,-22.02,-14.18,-7.87,-23.59,-13.14,-9.89,-24.74,-12.14,-12.1,-25.44,-11.22,-14.39,-25.64,-10.42,-16.67,-25.33,-9.77,-18.82,-24.52,-9.3,-20.75,-23.25,-9.02,-22.38,-21.56,-8.95,-23.63,-19.54,-9.08,-24.46,-17.26,-9.4,-24.81,-14.82,-9.91,-24.68,-12.33,-10.58,-24.06,-9.89,-11.38,-22.99,-7.61,-12.27,-21.51,-5.59,-13.22,-19.69,-3.91,-14.18,-17.6,-2.65,-15.11,-15.33,-1.86,-15.98,-12.98,-1.58,-16.73,-10.66,-1.81,-17.34,-8.45,-2.54,-17.79,-6.46,-3.74,-18.04,-4.77,-5.36,-18.09,-3.45,-7.33,-17.93,-2.56,-9.55,-17.56,-2.12,-11.93,-17.01,-2.17,-14.36,-16.28,-2.68,-16.73,-15.42,-3.64,-18.94,-14.44,-5,-20.88,-13.4,-6.7,-22.47,-12.32,-8.66,-23.64,-11.26,-10.79,-24.33,-10.26,-13,-24.51,-9.36,-15.19,-24.17,-8.59,-17.26,-23.32,-7.98,-19.11,-21.99,-7.56,-20.67,-20.24</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B332" t="str">
+        <v>[L_18_标记]</v>
+      </c>
+      <c r="C332" t="str">
+        <v>91.5uv</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B333" t="str">
+        <v>[R_19_名字]</v>
+      </c>
+      <c r="C333" t="str">
+        <v>FERG(19)_lCone</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B334" t="str">
+        <v>[R_19_放大器]</v>
+      </c>
+      <c r="C334" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B335" t="str">
+        <v>[R_19_闪光]</v>
+      </c>
+      <c r="C335" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B336" t="str">
+        <v>[R_19_闪光背景]</v>
+      </c>
+      <c r="C336" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B337" t="str">
+        <v>[R_19_采样]</v>
+      </c>
+      <c r="C337" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B338" t="str">
+        <v>[R_19_分析时间]</v>
+      </c>
+      <c r="C338" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B339" t="str">
+        <v>[R_19_数据长度]</v>
+      </c>
+      <c r="C339" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B340" t="str">
+        <v>[R_19_详细数据(uv)]</v>
+      </c>
+      <c r="C340" t="str">
+        <v>27.32,10.66,20.04,19.04,10.41,25.69,6.02,24.58,10.04,16.13,18.6,6.87,24.01,3.99,21.22,9.35,12.01,17.94,3.55,22.08,2.41,17.82,9.07,8.28,17.54,1.02,20.39,1.76,14.92,9.6,5.44,17.77,-0.32,19.3,2.33,12.85,11.12,3.72,18.78,-0.32,18.86,4.1,11.55,13.47,3.15,20.18,0.73,18.89,6.77,10.83,15.96,2.9,21.36,2.25,18.41,8.89,8.79,17.89,1.85,21.47,1.71,16.75,9.05,5.7,18.44,-2.5,16.69,-0.99,11.72,6.4,-0.07,13.1,-8.47,8.92,-10.03,2.87,-2.2,-10.24,1.26,-20.8,-0.6,-17.36,-7.77,-11.79,-28.49,-12.78,-22.31,-10.67,-15.73,-26.2,-12.29,-22.92,-3.93,-26.4,-12.87,-16.84,-25.67,-19.94,-28.9,-10.66,-15.47,-0.91,-10.94,-20.48,7.42,-14.55,0.94,-18.61,10.65,8.78,-2.58,19.85,15.35,39.64,20.82,35.33,29.33,37.22,46.52,41.53,67.66,67.78,61.08,67.9,74.09,89.47,76.43,106.94,99.08,94.61,108.87,126.01,136.78,122.59,124.05,157.11,150.15,185.83,147.17,170.36,154.53,167.68,168.71,158.07,186.95,213.21,213.28,176.41,222.46,217.29,194.68,266.81,219.22,244.38,230.15,269.05,267.95,231.97,229.27,238.07,233.81,256.65,287.8,304.32,257.6,285.56,254.05,251.24,231.7,258.07,273.41,231.5,281.13,227.09,263.29,234.17,242.4,232.67,274.43,249.43,228.96,261.32,226.09,240.86,262.65,203.2,230.65,213.99,194.11,227.48,199.66,193.97,202.33,179.24,172.79,197.11,186.38,191.12,160.47,145.82,163.6,158.37,143.29,146.24,147.22,163.7,132.18,117.1,128.23,116.64,114.94,94.79,117.75,90.93,109.58,84.74,91.11,85.1,68.7,82.5,65.67,69.77,77.26,58.63,80.01,51.88,64.2,55.99,57.98,51.98,40.59,56.32,39.17,53.15,39.88,37.92,45.28,28.15,45.01,24.14,36.52,32.97,27.2,40.34,18.44,35.19,17.6,27.66,27.94,15.35,32.9,11.02,29.1,15.98,19.72,21.88,9.71,28.31,4.91,23.86,12.78,12.99,17.81,5.32,21.18,2.97,18.05,8.1,7.4,16.93,-3.95,16.84,-0.65,9.99,5.58,-0.48,10.43,-8.9,14.08,-5.75,0.61,-0.21,-6.42,5.21,-14.88,7.28,-6.69,-3.78,0.49,-13.62,3.96,-17.9,0.02,-14.36,-5.45,-3.56,-17.5,1.08,-23.87,-6.63,-10.15,-9.25,-2.69,-17.49,-3.71,-19.49,-12.19,-11.52,-19.23,-9.54,-21.83,-1.86,-17.32,-9.95,-13.76,-26.17,-2.09,-29.66,-0.87,-22.36,-11.03,-6.41,-28.99,-2.59,-26.06,-14.56,-29.87,-9.53,-6.11,-22.99,-1.68,-30.08,-12.65,-23.64,-27.62,-15.03,-31.03,-9.32,-26.72,-13.17,-28.61,-30.08,-15.26,-22.77,-7.03,-33.5,-12.85,-21.86,-21.88,-21.88,-40.75,-23.37,-37.85,-29.37,-23.09,-34.25,-23.35,-28.75,-18.5,-31.81,-18.36,-24.7,-40.3,-22.4,-33.43,-20.65,-46.73,-43.26,-27.03,-32.18,-16.25,-52.05,-30.68,-39.88,-47.46,-35.36,-42.68,-18.99,-35.88,-41.44,-42.14,-30.46,-23.33,-43.2,-31.97,-50.71,-40.6,-42.08,-30.71,-15.54,-41.45,-15.38,-43.28,-29.91,-34.78,-31.81,-22.37,-49.95,-16.78,-35.45,-37.34,-16.89,-29.09,-10.6,-32.47,-28.87,-26.73,-30.99,-24.81,-38.06,-15.73,-35.25,-12.61,-20.03,-32.9,-16.14,-22.51,-10.56,-25.48,-17.92,-17.14,-29.54,-6.89,-31.39,-4.31,-14.69,-16.17,-12.52,-17.28,3.78,-22.16,-1.78,-12.24,-5.97,1.14,-11.05,1.99,-17.34,-6.75,-10.89,-5.14,2.63,-19.45,8.29,-15.08,-3.99,-10.03,-10.4,-1.59,-14.78,7.1,-10.13,-5.21,-1.38,-12.72,5.63,-11.71,2.88,-10.67,-0.13,-5.01,-8.52,5.46,-14.79,2.18,-10.36,-3.4,1.21,-9.81,5.67,-12.69,1.39,-5.21,-6.06,2.4,-11.26,7.02,-13.24,4.36,-2.15,-5.61,7.54,-12.2,8.46,-9.22,5.7,-0.07,-5.12,10.46,-9.15,12.36,-4.77,4.8,5.52,-2.33,13.5,-4.51,14.19,1,7.61</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B341" t="str">
+        <v>[R_19_标记]</v>
+      </c>
+      <c r="C341" t="str">
+        <v>a: 47.3ms -48.0uv b: 98.6ms 148.6uv</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B342" t="str">
+        <v>[L_19_名字]</v>
+      </c>
+      <c r="C342" t="str">
+        <v>FERG(19)_lCone</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B343" t="str">
+        <v>[L_19_放大器]</v>
+      </c>
+      <c r="C343" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B344" t="str">
+        <v>[L_19_闪光]</v>
+      </c>
+      <c r="C344" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B345" t="str">
+        <v>[L_19_闪光背景]</v>
+      </c>
+      <c r="C345" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B346" t="str">
+        <v>[L_19_采样]</v>
+      </c>
+      <c r="C346" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B347" t="str">
+        <v>[L_19_分析时间]</v>
+      </c>
+      <c r="C347" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B348" t="str">
+        <v>[L_19_数据长度]</v>
+      </c>
+      <c r="C348" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B349" t="str">
+        <v>[L_19_详细数据(uv)]</v>
+      </c>
+      <c r="C349" t="str">
+        <v>-9.86,-15.31,-0.75,-19.71,-3.71,-11.67,-15.31,-2.14,-20.94,-4.11,-13.86,-15.64,-3.96,-22.38,-4.86,-16.27,-16.14,-6.04,-23.85,-5.79,-18.7,-16.62,-8.17,-25.14,-6.7,-20.95,-16.9,-10.16,-26.08,-7.43,-22.83,-16.82,-11.84,-26.51,-7.82,-24.18,-16.28,-13.09,-26.34,-7.8,-24.94,-15.21,-13.84,-25.54,-7.35,-25.1,-13.66,-14.14,-24.17,-6.57,-24.75,-11.81,-14.16,-22.45,-5.63,-24.13,-10,-14.08,-20.67,-5.11,-23.83,-8.6,-15.07,-19.65,-5.18,-23.87,-8.43,-16.93,-19.68,-7.29,-26.41,-11.12,-21.57,-24.33,-13.47,-33.43,-16.34,-25.15,-26.57,-23.21,-40.99,-23.59,-36.22,-33.28,-27.31,-49.6,-30.87,-53.42,-45.51,-41.64,-60.91,-35.36,-53.9,-49.33,-42.11,-58.39,-42.71,-56.98,-57.64,-60.28,-69.17,-48.61,-56.43,-44.92,-54.38,-50.94,-44.73,-62.28,-35.78,-35.83,-41.69,-22.7,-36.17,-24.73,-21,-29.02,-5.29,-20.64,4.74,2.41,-1.85,16.49,1.53,24.97,20.74,13.98,42.81,19.45,55.78,49.1,49.16,78.12,61.52,76.15,70.38,68.26,93.41,73.88,97.78,89.59,125.1,134.04,131.87,158.05,153.2,156.16,145.01,146.92,188.95,171.73,183.51,162.48,189.35,219.81,176.71,184.36,218.06,182.17,221.97,225.72,215.5,197.56,247.49,246.84,229.7,237.29,235.57,260.28,216.9,264.03,214.6,215.39,253.71,237.61,217.81,271.83,244.98,241.95,256.36,203.86,212.03,222.32,191.33,209.42,200.18,195.22,196.61,174.75,191.09,179.45,158.71,155.46,168.03,173.8,149.03,149.6,160.66,124.19,156.28,134.27,116.87,100.86,104.8,113.1,73.53,87.17,71.75,91.31,85.82,49.75,84.5,47.12,54.84,59.64,39.43,47.14,30.57,45.25,37.28,27.37,41.92,21.08,21.65,19.22,11.7,22.81,3.96,15.16,12.1,-2.06,17.37,-3.89,9.63,4.89,-7.46,10.42,-9.53,2.63,-2.56,-9.66,6.58,-12.88,0.11,-4.41,-10.28,2.95,-15.95,1.17,-7.62,-10.45,1.76,-17.71,-0.06,-10.55,-11.66,-0.82,-17.26,-1.66,-13.21,-13.57,-1.97,-21.15,-0.3,-15.02,-12,-4.97,-22.24,-4.3,-19.02,-15.02,-6.36,-24.75,-3.18,-22.99,-14.33,-9.72,-27.26,-7.61,-22.48,-14.94,-13.25,-28.06,-11.72,-30.16,-16.46,-20.11,-30.76,-14.44,-32.25,-18.68,-20.71,-31.13,-17.53,-33.39,-21.55,-26.89,-32.86,-20.4,-39.88,-29.37,-28.97,-39.92,-25.62,-42.72,-24.97,-35.68,-35.38,-19.24,-47.76,-26.95,-33.66,-37.79,-27.96,-40.15,-33.87,-36.29,-34.34,-24.41,-44.57,-32.33,-43.88,-34.33,-27.92,-45.99,-30.83,-46.34,-36.66,-25.06,-53.38,-24.97,-45.69,-38.79,-27.28,-51.75,-33.59,-40.82,-46.71,-28.78,-51.29,-28.39,-47.43,-31.84,-26.54,-41.56,-34.48,-54.28,-31.5,-42.11,-55.86,-22.99,-53.26,-49.27,-49.52,-59.12,-33.1,-48.86,-33.86,-44.18,-47.64,-44.55,-48.12,-43.82,-42.35,-48.68,-39.54,-59.24,-31.81,-57.43,-55.45,-34.5,-70.08,-38.83,-41.75,-56.66,-38.88,-55.83,-45.44,-45.58,-64.49,-45.13,-73.87,-37.24,-47.5,-64.01,-50.28,-69.63,-46.15,-46.88,-49.52,-40.15,-69.06,-42.02,-51.04,-57.74,-47.5,-65.02,-38.12,-63.78,-49.08,-42.71,-54.53,-29.63,-59.43,-40.36,-46.41,-63.54,-32.11,-44.46,-39.92,-36.47,-51.1,-25.31,-59.11,-43.3,-36.67,-45.82,-21.1,-47.8,-26.59,-30.81,-36.03,-28.35,-45.79,-30.68,-40.3,-33.16,-15.81,-35.17,-22.94,-23.65,-29.25,-17.74,-39.23,-22.09,-24.14,-34.39,-15.58,-33.16,-14.76,-26.14,-25.84,-12.22,-36.32,-18.61,-29.7,-22.48,-14.06,-28.94,-13.63,-28.87,-26.69,-14.01,-34.04,-10.13,-24.96,-23.79,-12.7,-31,-11.56,-24.9,-17.87,-13.69,-28.62,-10.49,-26.1,-16.76,-13.11,-30.93,-7.71,-25.74,-17.13,-16.87,-29.77,-8.04,-26.32,-16.55,-14.83,-26.62,-7.69,-26.17,-13.06,-15.62,-24.05,-8.96,-25.42,-11.21,-16.1,-21.98,-5.01,-25.94,-9.83,-16.8,-19.32,-3.97,-22.66,-6.21,-13.84,-15.32,-2.29,-20.34</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B350" t="str">
+        <v>[L_19_标记]</v>
+      </c>
+      <c r="C350" t="str">
+        <v>a: 47.2ms -43.1uv b: 98.5ms 101.0uv</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B351" t="str">
+        <v>[R_20_名字]</v>
+      </c>
+      <c r="C351" t="str">
+        <v>FERG(20)_lFlicker</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B352" t="str">
+        <v>[R_20_放大器]</v>
+      </c>
+      <c r="C352" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B353" t="str">
+        <v>[R_20_闪光]</v>
+      </c>
+      <c r="C353" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B354" t="str">
+        <v>[R_20_闪光背景]</v>
+      </c>
+      <c r="C354" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B355" t="str">
+        <v>[R_20_采样]</v>
+      </c>
+      <c r="C355" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B356" t="str">
+        <v>[R_20_分析时间]</v>
+      </c>
+      <c r="C356" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B357" t="str">
+        <v>[R_20_数据长度]</v>
+      </c>
+      <c r="C357" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B358" t="str">
+        <v>[R_20_详细数据(uv)]</v>
+      </c>
+      <c r="C358" t="str">
+        <v>-60.9,-63.4,-73.8,-70.24,-64.17,-67.88,-69.33,-69.15,-73.89,-61.17,-71.94,-63.83,-73.66,-56.13,-61.13,-54.92,-61.34,-48.52,-54.7,-47.9,-55.45,-40.92,-44.21,-33.22,-34.89,-24.45,-26.59,-17.34,-15.83,-10.43,-5.73,-2.28,5.91,4.37,13.1,15.83,23.74,17.14,32.72,31.58,36.34,38.06,44.71,40.91,53.5,50.73,60.8,51.08,61.19,59.89,63.84,55.17,65.42,56.21,68.94,64.34,57.88,54.1,58.46,55.08,59.55,50.32,42.26,44.47,46.02,41.4,36.45,38.15,35.1,34.55,30.1,28.27,21.05,32.77,13.33,17.56,12.71,14.3,0.46,11.72,0.55,8.93,-0.76,-0.57,-6.29,-0.91,-13.37,-9.19,-12.57,-11.93,-12.68,-17.28,-14.75,-19.65,-17.93,-21.68,-19.84,-25.64,-20.76,-32.64,-21.94,-29,-20.3,-33.4,-27.06,-35.07,-29.62,-33.38,-39.35,-41.48,-35.8,-44.97,-44.41,-41.56,-38.93,-43.85,-41.66,-52.9,-54.6,-52.04,-46.28,-60.44,-55.11,-62,-55.65,-49.36,-68.24,-62.27,-73.46,-62.21,-75.22,-59,-71.92,-61.97,-69.66,-52.58,-60.43,-52.04,-53.81,-42.9,-54.99,-40.47,-49.1,-43.18,-44.4,-35.92,-34.74,-30.6,-26.9,-21.74,-17.31,-14.11,-7.07,-7.99,1.28,1.22,10.11,7.66,18.72,16.24,26.06,24.32,38.31,29.13,47.6,36.69,47.75,44.1,58.97,52.6,60.4,57.28,57.97,58.59,70.92,60.62,66.46,66.42,64.66,62.88,62.66,61.69,53.34,65.01,48.16,62.57,49.71,50.32,45.73,53.54,43.11,37.61,24.35,44.48,21.36,32.08,18.68,25.41,10.45,22.83,9.77,17.9,8.68,11.76,2.34,0.59,-0.16,4.5,-5.22,-5.2,-5.58,-9.99,-8.41,-9.07,-8.05,-13.22,-9.34,-16.5,-9.3,-18.15,-12.02,-19.35,-8.81,-18.75,-16.23,-19.05,-18.32,-22.66,-16.42,-22.95,-16.13,-30.54,-24.67,-28.59,-25.27,-31.69,-29.24,-37.48,-27.61,-31.12,-36.58,-29.07,-48.29,-39.83,-55.1,-48.84,-46.33,-45.56,-55.54,-46.26,-58.45,-42.67,-66.71,-54.45,-61.04,-49.84,-64.43,-56.09,-70.31,-54.41,-66.46,-53.67,-63.68,-43.17,-47.83,-52.91,-54.01,-46.56,-42.15,-38.6,-32.15,-30.5,-24.03,-25.43,-19.42,-20.07,-11.37,-13.23,-1.96,-3.53,8.44,2.67,18.23,10.02,25.02,23.38,33.7,33.16,42.25,37.05,47.09,40.31,48.22,50.68,62.88,57.58,58.52,55.8,73.4,56.78,60.51,73.24,59.21,71.18,60.58,62.58,60.43,76.98,63.59,71.18,53.03,64.97,45.05,56.69,49.12,54.67,44.07,50.45,32.35,40.63,37.34,31.39,28.96,30.18,28.58,25.21,18.08,24.34,12.13,14.85,16.62,12.36,6.86,-0.44,7.48,0.59,5.86,-1.98,0.54,-8.51,-1.34,-11.33,-1.15,-13.59,-3.32,-15.67,-9,-18.2,-10.38,-14.84,-10.92,-25.98,-13.89,-17.33,-13.23,-22.14,-25.47,-20.13,-31.36,-33.19,-38.65,-30.68,-26.31,-29.17,-46.2,-40.35,-42.41,-33.88,-48.25,-44.69,-44.65,-47.18,-55.23,-41.84,-55.64,-49.93,-63.96,-44.41,-54.38,-52.91,-57.29,-55.69,-64.17,-47.51,-59.95,-45.69,-52.3,-46.19,-52.15,-45.31,-44.32,-43.39,-35.23,-39.29,-34.16,-30.47,-21.78,-24.75,-16.61,-20.13,-5.72,-10.14,4.78,-0.6,14.05,7.21,23.47,18.52,31.91,29.68,39.46,36.96,47.89,45.39,56.3,53.52,61.67,56.12,56.98,70.43,66.84,66.95,70.76,78.65,73.56,71.3,72.48,82.68,62.05,77.82,61.55,78.35,59.62,80.7,67.12,72.65,50.2,67.42,54.21,54.42,45.27,49.71,49.14,45.58,33.55,45.04,39.69,38.65,32.3,19.96,26.47,21.25,19.3,18.76,13.05,12.21,11.71,3.96,8.29,3.07,4.64,-6.06,6.31,-7.78,0.34,-10.19,0.9,-9.95,-2.92,-14.21,-3.33,-12.84,-6.12,-17,-14.24,-14.25,-17.68,-12.47,-21.5,-17.54,-18.79,-22.37,-19.13,-15.78,-15.23,-13.14,-29.48,-26.11,-37.12,-29,-33.76,-29.95,-44.37,-36.46,-50.7,-41.68,-39.52,-29.36,-53.47,-33.14</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B359" t="str">
+        <v>[R_20_标记]</v>
+      </c>
+      <c r="C359" t="str">
+        <v>幅值: 53.9uv 相位: 33.9°</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B360" t="str">
+        <v>[L_20_名字]</v>
+      </c>
+      <c r="C360" t="str">
+        <v>FERG(20)_lFlicker</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B361" t="str">
+        <v>[L_20_放大器]</v>
+      </c>
+      <c r="C361" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B362" t="str">
+        <v>[L_20_闪光]</v>
+      </c>
+      <c r="C362" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B363" t="str">
+        <v>[L_20_闪光背景]</v>
+      </c>
+      <c r="C363" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B364" t="str">
+        <v>[L_20_采样]</v>
+      </c>
+      <c r="C364" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B365" t="str">
+        <v>[L_20_分析时间]</v>
+      </c>
+      <c r="C365" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B366" t="str">
+        <v>[L_20_数据长度]</v>
+      </c>
+      <c r="C366" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B367" t="str">
+        <v>[L_20_详细数据(uv)]</v>
+      </c>
+      <c r="C367" t="str">
+        <v>-72.29,-90.33,-78.88,-90.88,-82.08,-76.86,-73.62,-69.04,-69.03,-62.95,-64.35,-53.05,-56.34,-47.05,-52.61,-38.36,-41.08,-29.81,-30.89,-25.48,-20.53,-18.23,-8.4,-10.96,-1.8,-8.08,3.52,3.2,13.32,10.33,16.49,14.99,18.59,25.54,22.27,24.18,22.62,28.72,19.22,31.13,21.09,35.25,23.45,36.39,26.19,28.35,32.84,26.01,32.54,22.67,38.5,22.89,29.56,22.66,35.86,21.11,35.76,16.5,20.95,25.04,22.05,15.96,20.87,22.37,12.18,25.56,9.92,26.28,3.58,19.5,10.43,17.64,17.17,10.9,16.21,5.62,17.05,2.29,14.44,4.54,11.86,4.59,7.65,0.97,1.88,-1.01,-0.42,-1.87,-9.03,-2.71,-10.76,-9.66,-19.6,-10.79,-26.55,-17.58,-26.88,-28.46,-34.88,-35.94,-34.55,-50.4,-38.07,-59.52,-44.67,-59.02,-51.86,-74.56,-67.07,-75.74,-77.78,-73.69,-81.03,-80.35,-82.66,-78.97,-81.67,-84.94,-88.19,-74.88,-99.08,-77.85,-87.6,-89.44,-77.25,-87.78,-84.48,-80.74,-78.36,-77.7,-71.93,-72.28,-65.02,-62.42,-55.43,-58.3,-50.81,-47.68,-46.11,-41.56,-36.37,-29.88,-28.83,-16.74,-20.52,-10.27,-13.27,-0.03,-7.14,6.19,6.99,9.81,11.59,11.34,22.66,23.14,27.69,24.15,35.86,27.41,36.23,29.34,39.78,38.54,39.04,39.72,33.27,41.45,36.92,45.48,26.48,35.32,30.77,42.33,27.4,35.06,32.77,31.75,25.98,27.44,34.92,22.54,29.17,21.9,20.31,22.39,29.45,18.35,20.85,13.08,15.28,21.09,20.2,11.59,15.15,21.85,12.35,20,7.96,14.22,4.52,13.41,7.59,11.42,9.19,7.06,8.76,-0.07,5.35,-2.71,6.83,-7.82,5.45,-13.03,1.77,-13.76,-8.9,-15.34,-15.66,-17.12,-23.72,-19.15,-31.7,-28.17,-38.9,-32.19,-44.6,-36.05,-49.08,-49.6,-56.68,-56.99,-55.2,-63.97,-55.95,-72.37,-57.22,-77.36,-59.18,-86.8,-72.89,-76.63,-81.87,-78.2,-75,-72.95,-81.29,-80.81,-77.68,-73.57,-80.82,-76.33,-72.22,-63.55,-69.85,-57.1,-65.62,-65.73,-54.72,-60.37,-48.8,-52.9,-35.78,-42.31,-30.59,-33.79,-21.82,-24.57,-13.44,-17.72,-9.4,-4.74,-2.37,2.41,2.13,13.94,2.7,23.96,7.89,24.2,20.86,33.56,27.46,25.64,36.78,35.72,36.1,25.35,44.22,33.53,43.9,36.8,42.74,36.6,36.74,36.86,38.52,39.04,39.73,39.49,24.17,31.73,30.51,37.29,23.04,35.83,20.92,37.85,17.74,32.62,33.17,33.76,29.38,27.74,26.59,19.48,28.08,15.97,22.17,19.65,23.94,17.05,17.6,22.61,15.85,18.72,11.73,20.99,11.64,21.85,7.13,17.02,10.73,12.81,7.43,12.38,8.27,6.97,0.73,0.9,3.94,-11.94,1.73,-16.04,-10.4,-20.91,-14.37,-26.26,-29.65,-30.83,-32.99,-36.14,-38.65,-41.34,-46.93,-51.3,-64.89,-44.96,-62.43,-53.84,-63.04,-70.89,-66.41,-80.32,-75.64,-81.71,-80.92,-90.11,-73.36,-81.12,-69.4,-93.62,-73.47,-88.78,-81.76,-87.58,-76.68,-72.32,-74.21,-62.78,-70.3,-54.14,-63.35,-56.72,-57.23,-47.59,-51.94,-37.38,-40.99,-31.41,-25.68,-25.35,-17.31,-16.73,-4.35,-12.8,6.58,-5.16,11.85,8.86,17.1,15.46,19.33,21.74,25.14,33.79,25.95,39.78,35.92,41.55,36.04,42.7,38.14,44.86,43.79,51.53,50.48,38.18,54.2,45.41,53.54,34.95,45.15,33.52,48.84,33.78,40.91,39.45,38.49,29.16,42.86,27.08,32.72,32.14,24.7,37.78,22.81,38.73,24.44,36.88,19.88,27.82,21.07,24.54,28.64,16.76,29.19,16.19,22.55,17.28,22.45,15.91,19.25,12.38,19.45,13.58,13.48,12.79,8.2,14.14,1.93,8.14,-3.37,2.02,-8.89,-3.37,-6.55,-7.61,-9.37,-13.81,-13.67,-19,-19.65,-29.35,-22.19,-37.53,-31.05,-43.88,-36.64,-47.96,-45.85,-50.14,-55.89,-61.86,-54.86,-60.56,-67.44,-69.84,-77.42,-68.94,-80,-67.24,-78.79,-71.9,-73.05,-70.75,-77.21,-69.48,-66.43,-75.35</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B368" t="str">
+        <v>[L_20_标记]</v>
+      </c>
+      <c r="C368" t="str">
+        <v>幅值: 54.7uv 相位: 33.9°</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B369" t="str">
+        <v>[R_21_名字]</v>
+      </c>
+      <c r="C369" t="str">
+        <v>FERG(21)_lCone</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B370" t="str">
+        <v>[R_21_放大器]</v>
+      </c>
+      <c r="C370" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B371" t="str">
+        <v>[R_21_闪光]</v>
+      </c>
+      <c r="C371" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B372" t="str">
+        <v>[R_21_闪光背景]</v>
+      </c>
+      <c r="C372" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B373" t="str">
+        <v>[R_21_采样]</v>
+      </c>
+      <c r="C373" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B374" t="str">
+        <v>[R_21_分析时间]</v>
+      </c>
+      <c r="C374" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B375" t="str">
+        <v>[R_21_数据长度]</v>
+      </c>
+      <c r="C375" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B376" t="str">
+        <v>[R_21_详细数据(uv)]</v>
+      </c>
+      <c r="C376" t="str">
+        <v>-9.38,3.4,-11.36,3.95,-11.17,2.44,-8.89,-0.75,-5.18,-4.75,-1.06,-8.46,2.34,-10.83,4.13,-11.16,3.85,-9.32,1.65,-5.75,-1.8,-1.33,-5.46,2.79,-8.22,5.58,-9.23,6.38,-8.1,5.06,-5.05,2.12,-0.78,-1.57,3.59,-4.85,6.97,-6.78,8.53,-6.7,7.9,-4.58,5.25,-0.99,1.42,3.11,-2.57,6.51,-5.62,8.48,-6.95,8.02,-6.33,5.74,-3.81,1.23,-0.53,-3.81,2.05,-7.71,4.19,-11.56,3.87,-12.97,0.78,-11.8,-5.28,-11.53,-10.66,-8.46,-15.96,-9.28,-24,-11.3,-25.75,-13.08,-28.25,-19.14,-26.67,-25.06,-29.75,-28.04,-30.79,-36.49,-28.58,-37.72,-34.22,-49.78,-37.12,-45.74,-34.11,-42.5,-51.68,-40.45,-43.63,-38.86,-53.57,-37.61,-47.12,-28.76,-49.34,-39.15,-31.8,-43.96,-29.69,-34.38,-27.58,-31.42,-12.94,-25.15,-17.18,-22.45,-9.45,-16.7,2.12,14.83,4.37,24.63,9.76,31.86,22.7,33.94,47.16,58.26,55.75,75.62,67.34,82.05,77.34,82.61,88.62,94.76,118.18,112.7,111.87,125.49,131.84,140.98,118.64,145.39,156.4,169.07,169.11,183.5,142.06,173.66,170.99,195.22,203.96,166.8,219.77,183.26,194.44,207.79,234.23,227.69,220.1,216.71,207.38,220.98,250.77,198.18,248.28,214.6,250.72,233.56,255.97,220.2,206.51,219.14,228.04,267.66,209.64,214.9,248.08,254.12,261.99,221.56,220.96,230.87,241.05,211.76,235.52,216.01,231.89,212.73,206.45,242.22,185.96,200.08,210.13,181.5,202.62,202.72,176.13,195.66,164.75,156.75,144.24,152,163.53,133.15,172.73,123.38,151.31,145.76,140.23,120.68,131.05,111.32,119.9,122.22,91.98,111.16,91.21,107.88,69.76,89.13,78.97,80.14,67.9,60.27,56.89,54.28,54.61,40.72,49.33,38,47.41,37.85,40.73,34.57,35.51,31.62,26.65,24.4,18.68,26.33,14.5,23.72,5.1,18.2,7.04,13.56,6.32,8.16,3.84,-3.79,4.37,-8.19,6.08,-10.49,3.35,-12.19,-0.92,-13.1,-6.9,-10.48,-11.29,-6.39,-17.5,-6.71,-20.57,-6.11,-23.33,-9.75,-22.1,-13.51,-20.04,-17.24,-18.56,-22.9,-15.5,-26.93,-12.12,-30,-14.32,-26.75,-14.89,-23.6,-22.27,-22.16,-22.72,-18.61,-28.71,-17.64,-33.85,-14.29,-29.39,-17.4,-30.43,-21.14,-26.96,-27.35,-19.76,-33.91,-21.91,-31.7,-15.65,-29.85,-23.5,-32.18,-20.26,-31.8,-29.55,-30.66,-28.56,-23.61,-29.69,-22.42,-35.77,-27.53,-42.82,-25.53,-38.75,-26.28,-33.53,-29.45,-32.68,-38.49,-28.71,-49.5,-24.34,-41.98,-24.69,-41.87,-33.61,-33.59,-35.91,-37.94,-38.27,-28.4,-41.36,-37.43,-54.79,-32.25,-54.14,-45.56,-52.26,-40.05,-54.35,-54.22,-51.81,-52.56,-45.28,-53.03,-35.3,-58.73,-40.59,-61.63,-54.66,-59.06,-48.41,-57.86,-59.75,-41.53,-64.53,-51.69,-72.44,-40.33,-59.97,-48.68,-71.92,-67.81,-54.3,-70.84,-58.8,-61.4,-59.06,-66.09,-62.12,-70.12,-46.04,-61.49,-47.88,-63.8,-70.33,-62.62,-51.75,-53.66,-62,-47.35,-70.77,-58.09,-68.53,-49.37,-48.3,-50.82,-53.04,-53.84,-52.98,-57.17,-36.12,-58.95,-45.85,-50.61,-47.49,-63.09,-42.3,-47.02,-57.65,-51.53,-55.33,-48.01,-46.56,-42.47,-55.73,-35.82,-46.01,-39.2,-40.33,-41.25,-40.23,-49.05,-36.71,-50.7,-45.2,-47.79,-36.53,-54.44,-40.53,-52.25,-42.67,-41.74,-49.07,-33.21,-54.06,-36.52,-56.42,-32.78,-55.69,-32.27,-54.63,-34.38,-50.14,-42.59,-44.57,-42.08,-41.02,-46.64,-30.87,-43.03,-27.94,-42.84,-39.69,-40.67,-34.18,-36.66,-42.16,-33.15,-43.11,-26.03,-45.59,-30.16,-41.1,-33.51,-40.47,-33.87,-36.87,-31.57,-28,-35.33,-27.71,-37.86,-25.4,-36.56,-23.69,-34.01,-22.59,-31.38,-29.83,-23.59,-31.71,-21.29,-32.3,-19.73,-30.15,-14.31,-29.64,-17.31,-26.94,-19.44,-22.64,-23.73,-18.39,-27.88,-12.12,-27.61,-12.43,-27.97,-13.65,-25.1,-15.15,-20.57,-20.46,-16.12,-23.75,-11.87,-26.77,-10.56</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B377" t="str">
+        <v>[R_21_标记]</v>
+      </c>
+      <c r="C377" t="str">
+        <v>a: 51.8ms -39.5uv b: 106.4ms 187.5uv</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B378" t="str">
+        <v>[L_21_名字]</v>
+      </c>
+      <c r="C378" t="str">
+        <v>FERG(21)_lCone</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B379" t="str">
+        <v>[L_21_放大器]</v>
+      </c>
+      <c r="C379" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B380" t="str">
+        <v>[L_21_闪光]</v>
+      </c>
+      <c r="C380" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B381" t="str">
+        <v>[L_21_闪光背景]</v>
+      </c>
+      <c r="C381" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B382" t="str">
+        <v>[L_21_采样]</v>
+      </c>
+      <c r="C382" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B383" t="str">
+        <v>[L_21_分析时间]</v>
+      </c>
+      <c r="C383" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B384" t="str">
+        <v>[L_21_数据长度]</v>
+      </c>
+      <c r="C384" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B385" t="str">
+        <v>[L_21_详细数据(uv)]</v>
+      </c>
+      <c r="C385" t="str">
+        <v>-30.4,-17.51,-29.18,-19.39,-27.52,-21.51,-25.55,-23.75,-23.4,-25.93,-21.23,-27.92,-19.19,-29.56,-17.4,-30.73,-15.99,-31.34,-15.03,-31.33,-14.58,-30.69,-14.65,-29.42,-15.2,-27.61,-16.19,-25.35,-17.5,-22.76,-19.03,-19.99,-20.61,-17.24,-22.16,-14.62,-23.52,-12.33,-24.51,-10.5,-25.17,-9.2,-25.3,-8.67,-24.9,-8.72,-24.22,-9.47,-23.15,-10.66,-21.34,-12.68,-20.18,-15.07,-18.16,-17.66,-16.73,-20.24,-16.04,-23.97,-14.5,-27.63,-16.52,-28.85,-16.34,-33.84,-16.75,-33.52,-20.59,-38.58,-24.88,-37.19,-30.96,-38.31,-32.75,-42.27,-34.4,-47.06,-42.62,-47.48,-50.32,-43.16,-57.93,-48.93,-59.4,-46.65,-62.1,-46.45,-60.1,-58.26,-62.87,-47.15,-70.48,-46.15,-70.78,-57.44,-63.4,-49.86,-64.19,-36.09,-48.83,-37.75,-39.41,-40.76,-38.93,-31.82,-36.66,-30.02,-18.71,-22.31,-6.09,-23.5,13.13,0.72,8.06,13.92,33.65,24.15,35.49,23.28,35.25,57.43,51.07,49.78,64.95,61.34,93.57,83.8,92.8,116.02,96.03,100.13,125.84,145.62,135.05,135.45,107.63,165.14,121.06,164.41,145.06,190.11,160.03,156.85,175.52,210.45,204.07,200.06,187.21,223.05,189.83,222.31,194.21,182.88,245.96,211.43,261.16,240.62,233.93,222.46,261.83,199.08,272.17,240.54,234.96,238.66,225.38,258.93,237.12,266.79,230.97,202.53,257.18,247.4,235.81,201.25,204.91,229.71,195.12,243.95,207.59,200.98,200.66,196.68,196.74,185.92,162.81,226.4,193.75,204.59,173.85,161.91,171.13,159.77,140.38,140.6,132.94,146.42,148.56,145.56,130.64,141.75,139.82,94.76,103.52,109.78,104.03,89.4,119.38,89.71,88.58,84.18,95.65,72.18,68.74,56.54,68.33,58.13,72.67,46.51,47.64,45.9,50.06,51.88,34.65,42.32,35.42,35.5,26.41,38.83,14.62,31.39,16.97,26.23,6.43,22.57,4.09,21.67,2.92,16.67,4.62,12.92,3.61,4.53,0.33,0.99,1.72,-4.63,2.02,-7.85,1.15,-11.94,0.48,-16.55,-1.36,-18.92,-2.1,-20.93,-5.08,-22.5,-7.09,-23.26,-10.96,-20.14,-13.22,-21.31,-13.54,-19.18,-16.59,-18.9,-23.81,-17.51,-23.64,-19.13,-29.9,-18.51,-30.96,-14.04,-28.89,-13.38,-34.95,-14.26,-31.03,-16.87,-30.9,-18.86,-29.24,-18.05,-31.58,-23.92,-30.08,-25.07,-25.69,-26.7,-20.96,-33.4,-18.81,-35.32,-23.75,-34.75,-24.48,-36.59,-24.48,-38.3,-21.18,-31.88,-22.63,-40.94,-20.16,-40.07,-19.4,-35.11,-31.65,-31.28,-26.27,-28.46,-33.11,-27.89,-26.93,-34.32,-39.22,-23.85,-32.13,-29.55,-33.46,-21.61,-40.11,-35.27,-42.04,-25.46,-40.7,-31.75,-54.3,-30.59,-43.64,-32.07,-49.47,-30.75,-51.27,-50.87,-37.73,-37.59,-46.34,-55.92,-34.39,-57.91,-44.94,-59.14,-50.62,-52.64,-38.89,-48.73,-43.13,-54.68,-51.32,-53.27,-39.03,-64.36,-56.95,-65.74,-52.5,-47.5,-60.57,-57.61,-43.86,-49.72,-47.82,-57.77,-50.38,-38.56,-54.04,-54.73,-67.84,-48.28,-51.37,-45.84,-67.81,-36.1,-56.85,-43.61,-53.16,-42.34,-59.56,-43.2,-49.72,-43.82,-54.04,-48.32,-39.94,-58.22,-34.24,-56.81,-45.15,-45.24,-45.62,-49.48,-36.85,-42.88,-34.47,-47.74,-35.73,-44.09,-23.69,-45.75,-31.84,-37.96,-24.12,-33.66,-35.58,-42.91,-41.75,-43.2,-42.34,-39.23,-45.03,-21.79,-33.53,-19.95,-43.9,-24.98,-44.2,-27.57,-45.7,-28.02,-34.54,-19.89,-34.4,-25.4,-34.47,-18.28,-36.17,-28.99,-36.94,-28.05,-28.54,-27.2,-20.66,-26.6,-22.11,-32.47,-17.39,-34.29,-23.9,-35.21,-12.06,-29.73,-20.22,-27.95,-15.51,-27.53,-15.56,-25.64,-13.04,-26.45,-20.05,-23.01,-14.9,-20.27,-19.1,-14.86,-20.37,-14.38,-21.99,-12.94,-21.22,-10.24,-18.91,-4.27,-22.28,-5.61,-19.03,-4.15,-19.01,-1.73,-19.51,-1.98,-12.9,-3.18,-13.48,-5.56,-9.48,-3.74,-5.09,-5.22,-1.21,-5.78,-1.08,-7.68,1.86,-9.97,4.96,-9.94,7.52,-8.9,8,-9.73,8.49,-7.09,6.96,-7.61</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B386" t="str">
+        <v>[L_21_标记]</v>
+      </c>
+      <c r="C386" t="str">
+        <v>a: 51.7ms -43.2uv b: 106.3ms 151.2uv</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B387" t="str">
+        <v>[R_22_名字]</v>
+      </c>
+      <c r="C387" t="str">
+        <v>FERG(22)_lFlicker</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B388" t="str">
+        <v>[R_22_放大器]</v>
+      </c>
+      <c r="C388" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B389" t="str">
+        <v>[R_22_闪光]</v>
+      </c>
+      <c r="C389" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B390" t="str">
+        <v>[R_22_闪光背景]</v>
+      </c>
+      <c r="C390" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B391" t="str">
+        <v>[R_22_采样]</v>
+      </c>
+      <c r="C391" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B392" t="str">
+        <v>[R_22_分析时间]</v>
+      </c>
+      <c r="C392" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B393" t="str">
+        <v>[R_22_数据长度]</v>
+      </c>
+      <c r="C393" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B394" t="str">
+        <v>[R_22_详细数据(uv)]</v>
+      </c>
+      <c r="C394" t="str">
+        <v>-50.58,-39.15,-41.15,-33.43,-31.07,-40.04,-26.29,-29.53,-28.02,-24.49,-27.76,-11.68,-20.31,-13.4,-14.89,-13.15,-3.86,-10.13,4.08,4.57,-4.64,7.25,0.46,3.98,10.22,4.05,14.23,6.57,13.35,14.65,9.57,19.78,13.38,19.17,19.88,13.83,27.14,17.37,27.82,27.18,22.28,29.57,27.42,28.02,40.12,28.41,46.67,34.25,44.22,43.78,29.43,53.78,52.09,49.08,51.64,47.27,58,57.5,56.89,57.71,64.45,67.17,63.83,70.36,69.67,61.56,77.35,64.85,75.9,69.65,59.13,74.55,65.43,67.82,74.8,63.85,60.28,59.78,48.54,53.6,46.9,53.65,40.26,43.96,39.95,29.21,31.99,25,20.25,20.63,6.57,12.43,1.54,-2.22,-2.9,-14.21,-7.94,-20.03,-25.02,-21.91,-35.49,-27.27,-33.59,-40.33,-35.78,-50.65,-41.24,-56.57,-56.03,-52.21,-58.81,-53.86,-58.11,-60.04,-45.62,-52.54,-54.56,-59.2,-51.19,-49.33,-47.19,-39.94,-48.37,-43.76,-37.53,-47.82,-31.73,-28.94,-28.87,-21.89,-23.41,-21.32,-25.44,-17.99,-5.79,-19.51,-4.86,-8.64,-15.5,-0.15,-12.06,3.15,-2.4,1.02,6.66,0.89,7.91,6,3.19,14.98,5,12.8,12.1,9.26,18.02,10.29,16.69,17.21,14.97,25.08,15.45,21.24,26.65,18.68,25.89,23.39,30.24,31.92,29.67,34.33,28.55,36.79,37.23,33.1,46.57,39.12,55.35,41.66,48.84,56.95,55.32,55.77,60.37,63.08,73.56,54.41,73.84,75.64,64.33,76.93,69.11,69.52,73.2,68.35,74.82,73.25,75.17,73.44,69.68,80.48,69.14,70.24,74.1,59.36,63.33,55.9,50.51,56.07,42.93,47.13,33.6,36.97,32.59,24.4,28.58,15.04,14.83,11.2,0.05,5.36,-5.75,-11.04,-6.9,-23.84,-15.92,-25.06,-25.35,-25.13,-39.31,-31.64,-39.6,-37.63,-38.66,-47.22,-42.1,-58.68,-50.54,-54.76,-54.36,-42.97,-54.45,-54.26,-48.74,-55.02,-39.39,-47.54,-47.53,-47.17,-54.53,-37.76,-35.65,-41.06,-23.06,-34.5,-28.42,-29.28,-20.59,-14.31,-32.3,-12.56,-10.08,-7.16,-9.17,-19.95,-5.2,-2.47,-8.84,5.56,-0.58,9.2,1.59,2.76,13.95,4.48,16.16,10.48,12.95,19,12.4,21.89,18.12,18.32,26.83,18.2,28.11,26.04,21.61,29.14,23.9,40.04,28.98,29.67,46.84,37.38,42.16,35.4,38.83,46.65,46.39,50.1,49.54,48.71,58.58,52.07,56.31,59.35,56.58,77.33,59.32,68.28,73.88,72.18,84.33,71.31,85.3,73.65,77.86,86.99,72.47,85.35,84.13,76.28,75.43,71.63,77.55,71.75,64.78,73.33,61.95,64.16,54.58,54.68,54.63,44,42.53,40.95,29.62,33.59,19.16,23.97,16.63,8.41,11.95,-2.53,1.41,-3.6,-13.91,-5.45,-23.31,-21.02,-20.83,-32.95,-20.83,-43.82,-31.03,-41.54,-47.15,-40.43,-51.35,-39.62,-50.43,-44.57,-34.92,-54.38,-48.92,-47.44,-42.22,-36.31,-47.96,-38.67,-42.46,-42.58,-27.18,-42.05,-25.33,-35.8,-30.49,-26.73,-32.54,-24,-16.5,-20.23,-11.87,-15.08,-1.36,-3.22,-6.97,-3.89,-3.5,7.66,12.04,-0.45,8.42,8.05,10,13.7,8.29,18.85,12.61,18.28,21.58,15.8,25.88,18.86,22.79,27.8,21.53,31.21,22.57,29.47,31.14,22.76,35.38,25.68,35.09,36.73,34.8,41.3,33.93,37.38,55.33,44.14,44.87,48.05,54.39,59.24,43.62,55.62,60.16,59.48,69.52,60.73,64,67.87,68.87,82.72,71.9,83.98,76.67,81.4,83.22,70.96,86.89,80.88,82.39,81.69,81.17,80.94,69.83,69.71,79.57,62.99,65.19,65.22,58.91,62.01,54.37,56.97,45.73,45.53,45.37,32.97,38.96,29.95,25.51,26.06,12.65,17.37,7.13,2.97,4.98,-7.91,-1.76,-9.82,-19.98,-10.22,-23.67,-20.24,-26.78,-34.76,-29.84,-46.71,-33.02,-33.77,-43.2,-44.42,-43,-38.16,-45.84,-53.81,-39.18,-48.32,-36.89,-44.01,-47.92,-27.27,-46.4,-26.37,-29.78,-31.07</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B395" t="str">
+        <v>[R_22_标记]</v>
+      </c>
+      <c r="C395" t="str">
+        <v>幅值: 55.9uv 相位: 35.1°</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B396" t="str">
+        <v>[L_22_名字]</v>
+      </c>
+      <c r="C396" t="str">
+        <v>FERG(22)_lFlicker</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B397" t="str">
+        <v>[L_22_放大器]</v>
+      </c>
+      <c r="C397" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B398" t="str">
+        <v>[L_22_闪光]</v>
+      </c>
+      <c r="C398" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B399" t="str">
+        <v>[L_22_闪光背景]</v>
+      </c>
+      <c r="C399" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B400" t="str">
+        <v>[L_22_采样]</v>
+      </c>
+      <c r="C400" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B401" t="str">
+        <v>[L_22_分析时间]</v>
+      </c>
+      <c r="C401" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B402" t="str">
+        <v>[L_22_数据长度]</v>
+      </c>
+      <c r="C402" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B403" t="str">
+        <v>[L_22_详细数据(uv)]</v>
+      </c>
+      <c r="C403" t="str">
+        <v>-34.43,-61.28,-48.12,-57.16,-52.67,-31.65,-54.44,-30.85,-48.06,-30.29,-21.62,-34.14,-10.78,-30.59,-6.29,-12.78,-5.02,7.66,-5.4,21.06,4.91,25.58,22.55,21.93,44.5,24.75,48.84,38.18,49.33,60.81,53.1,74.65,59.59,76.51,72.89,65.58,83.46,59.96,87.75,64.6,82.3,91.17,66.95,93.23,75.44,91.94,73.22,71.89,84.94,63.69,76.56,58.24,69.31,62.6,54.99,76.08,52.18,59.98,39.01,50.97,48.53,29.29,53.57,24.67,40.72,25.25,25.71,30.92,8.42,29.82,8.03,21.32,12.41,3.28,18.26,-3.31,12.78,-2.56,3.97,4.93,-10.46,10.2,-14.25,5.38,-8.33,-8.86,-0.6,-20.09,0.64,-18.04,-1.93,-9.62,-18.37,-5.39,-27.12,-7.18,-17.48,-9.29,-7.02,-27.22,-9.09,-29.68,-13.64,-22.92,-25.79,-23.38,-45.31,-16.45,-47.99,-31.98,-39.92,-52.44,-31.43,-52.41,-38.75,-52.27,-36.8,-33.07,-56,-25.47,-55.77,-46,-46.38,-55.47,-38.72,-49.11,-31.73,-43.03,-37.52,-32.7,-47.82,-18.23,-39.93,-18.71,-26.83,-22.29,-10.38,-21.8,1.61,-15.79,2.13,4.69,-0.1,19.99,3.24,29.44,18.27,25.64,38.63,27.01,48.83,32.81,55.4,46.92,45.29,69.01,47.35,80.33,61.17,67.06,72.54,61.22,73.64,64.73,76.88,61.98,79.73,85.26,57.86,85.41,57.62,80.64,69.39,64.09,71.59,53.22,69.14,59.05,53.55,61.05,39.25,60.9,33.75,62.01,46.48,36.83,50.66,26.63,40.93,23.51,32.77,26.18,23.19,30.66,13.48,32.52,14.9,20.26,21.02,7.05,25.33,-0.9,18.35,9.71,5.18,17.76,-3.47,19.35,-1.79,9.48,7.63,-2.04,16.17,-5.55,9.77,-3.28,-3.73,3.68,-14.24,11.71,-19.97,-9.48,-8.2,-17.43,2.59,-24.11,0.67,-31.77,-13.47,-26.3,-24.75,-10.88,-32.33,-18.23,-39.95,-37.75,-28.23,-55.09,-27.36,-46.78,-35.35,-50.04,-48.04,-39.47,-56.41,-44.27,-48.98,-47.07,-42.51,-60.75,-37.36,-59.05,-44.8,-40.77,-47.54,-33.63,-51.88,-25.43,-40.88,-27.74,-22.89,-26.83,-11.24,-27.14,-2.54,-12.12,-5.44,6.82,-3.63,21.45,5.22,25.36,22.59,23.81,44.54,25.19,51.72,41.32,53.42,52.75,52.2,74.18,54.09,79.19,63.57,71.49,81.73,71.22,95.01,70.44,94.1,84.57,79.46,99.41,74.79,93.49,75.05,74.38,77.86,65.04,92.92,60.66,78.83,73.04,64.08,66.27,46.84,69.34,45.41,58.63,52.04,36.89,51.69,31.63,54.18,36.32,28.94,35.3,14.31,35.7,17.25,32.31,16.9,10.25,24.9,3.3,22.33,2.41,13.12,10.68,-0.84,16.9,-7.98,11.22,-4.4,-2.09,3.34,-16.57,6.13,-13.96,1.36,-2.82,-16.22,-1.36,-26.87,-5.13,-21.03,-12.18,-7.75,-33.44,-11.22,-34.79,-19.65,-22.18,-34.29,-25.39,-51.38,-20.55,-42.06,-26.56,-33.58,-50.12,-28.25,-56.69,-41.11,-53.59,-46.84,-42.35,-60.23,-31.91,-60.86,-42.06,-44.38,-44.27,-32.57,-53.8,-30.67,-42.52,-29.42,-28.97,-41.43,-16.03,-31.67,-15.01,-25.63,-20.39,-0.87,-16.1,8.51,-6.82,9.36,9.96,7.89,27.58,10.62,38.33,26.21,37.06,43.61,35.3,61.11,36.8,65.33,56.32,59.61,75.5,57.34,80.91,66.92,78.09,77.06,63.05,95.07,69.11,82.84,81.02,80.72,88.9,71.96,95.54,58.2,79.21,70.9,68.84,72.99,54.55,75.12,63.33,58.76,61.08,48.79,66.67,41.18,49.69,35.94,41.43,49.36,29.82,48.79,18.02,36.34,29.99,19.75,34.91,6.76,27.29,12.35,15.77,21.01,2.72,22.36,-1.58,15.45,4.13,3.74,14.6,-4.91,16.36,-5.88,6.93,4.99,-6.06,9.53,-10.16,11.49,-5.1,4.46,-0.38,-12.99,3.07,-15.48,0.05,-3.93,-20.24,3.09,-25.88,-1.19,-15.36,-12.47,-16.49,-34.85,-7.28,-35.21,-10.58,-32.41,-24.14,-28.06,-49.3,-27.17,-43.85,-34.17,-32.6,-38.44,-26.59,-48.67,-36.26,-39.58,-44.85,-40.78,-50.12</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B404" t="str">
+        <v>[L_22_标记]</v>
+      </c>
+      <c r="C404" t="str">
+        <v>幅值: 56.2uv 相位: 35.3°</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B405" t="str">
+        <v>[R_23_名字]</v>
+      </c>
+      <c r="C405" t="str">
+        <v>FERG(23)_lCone</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B406" t="str">
+        <v>[R_23_放大器]</v>
+      </c>
+      <c r="C406" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B407" t="str">
+        <v>[R_23_闪光]</v>
+      </c>
+      <c r="C407" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B408" t="str">
+        <v>[R_23_闪光背景]</v>
+      </c>
+      <c r="C408" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B409" t="str">
+        <v>[R_23_采样]</v>
+      </c>
+      <c r="C409" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B410" t="str">
+        <v>[R_23_分析时间]</v>
+      </c>
+      <c r="C410" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B411" t="str">
+        <v>[R_23_数据长度]</v>
+      </c>
+      <c r="C411" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B412" t="str">
+        <v>[R_23_详细数据(uv)]</v>
+      </c>
+      <c r="C412" t="str">
+        <v>-14.4,-24.13,-11.17,-14.55,-23.13,-9.81,-14.76,-22.06,-8.6,-15.06,-20.97,-7.59,-15.46,-19.89,-6.79,-15.96,-18.85,-6.25,-16.57,-17.88,-5.96,-17.28,-16.98,-5.95,-18.08,-16.19,-6.21,-18.97,-15.5,-6.73,-19.91,-14.93,-7.49,-20.89,-14.46,-8.48,-21.88,-14.1,-9.65,-22.84,-13.84,-10.98,-23.76,-13.64,-12.48,-24.61,-13.55,-14.07,-25.4,-13.58,-15.84,-26.18,-13.83,-17.66,-27.05,-14.39,-19.76,-27.75,-15.37,-22.26,-28.72,-16.74,-25.25,-30.87,-18.76,-28.93,-31.46,-22.42,-30.79,-34.07,-25.76,-36.61,-41.01,-26.88,-41.42,-40.51,-39.35,-52.53,-47.82,-44.68,-56.32,-55.08,-47.32,-61.05,-61.96,-52.33,-60.55,-55.2,-61.65,-71.08,-67.3,-63.11,-67.65,-59.97,-57.15,-71.19,-62.72,-50.68,-71.04,-47.33,-44.67,-54.67,-47.86,-48.13,-49.18,-34.62,-30.38,-35.52,-23.42,-24.15,-19.05,-10.99,-13.08,-6.04,2.41,1.01,2.2,25.34,14.42,19.31,33.09,30.89,41.9,47.19,42.46,61.25,76.54,70.32,70.66,99.51,75.8,74.45,90.75,96.53,117.25,137.15,103.37,140.56,151.74,149.22,144.57,152.7,153.35,187.8,193.14,142.66,172.2,188.29,168.87,177.97,180.25,210.17,211.04,192.72,220.22,198.27,246,248.42,251.37,240.99,237.06,217.35,201.77,197.05,219.4,221.65,206.17,204.47,244.61,219.47,214.06,255.2,199.68,232.91,233.25,205.12,235.31,204.89,197.72,192.84,167.61,176.7,178.6,161.65,145.08,166.11,160.83,136,143.39,122.88,134.5,148.12,117.65,103.76,117.88,99.09,92,105.02,80.77,77.47,78.72,77.93,86.45,60.99,60.66,54.33,45.54,46.47,53.77,32.66,30.7,42.41,27.43,13.78,26.76,17.85,7.57,17,11.14,0.32,16.06,2.6,-1.09,6.66,-7.6,-6.44,3.11,-10.86,-9,-2.06,-15.48,-13.12,-5.42,-18.89,-13.58,-8.28,-22.39,-15.43,-10.36,-24.58,-16.3,-11.76,-26.12,-17.08,-13.83,-26.01,-16.5,-15.82,-28.23,-16.5,-18.36,-29.25,-17.19,-18.42,-28.1,-14.77,-18.6,-29.7,-14.49,-22.78,-26.5,-12.8,-23.25,-26.62,-13.58,-21.34,-24.86,-13.82,-25.8,-27.44,-15.6,-23.3,-26.61,-16.65,-23.37,-24.39,-12.36,-28.83,-24.67,-14.37,-25.95,-27.35,-15.63,-26.8,-25.88,-20.88,-34.35,-24.33,-21.81,-31.3,-28.3,-17.22,-34.68,-23.4,-23.04,-35.87,-21.13,-22.73,-37.45,-24.36,-28.15,-36.24,-32.63,-30.92,-47.58,-30.36,-40.37,-45.9,-30.06,-33.77,-38.48,-37.81,-37.34,-42.37,-34.81,-49.09,-50.88,-41.29,-40.41,-56.72,-30.84,-46.35,-46.66,-43.34,-47.87,-45.46,-40.45,-57.7,-43.25,-49.56,-58.94,-55.97,-50.06,-61.21,-49.61,-44.98,-63.67,-59.65,-48.46,-55.1,-52.57,-49.15,-54.85,-48.56,-59.37,-70.7,-48.93,-40.88,-68.47,-41.36,-42.55,-71,-40.23,-59.06,-55.56,-47.46,-41.51,-50.45,-36.42,-64.32,-70.43,-55.57,-49.92,-56.53,-36.38,-58.31,-47.8,-37.95,-61.49,-59.17,-53.83,-48.91,-58.42,-50.63,-49.51,-44.78,-55.27,-66.27,-50.6,-54.58,-54.18,-60.33,-50.17,-63.91,-60.77,-39.71,-49.47,-56.85,-41.54,-56.2,-57.46,-53.31,-47.3,-41.3,-40.35,-58.87,-48.04,-40.47,-55.91,-37.62,-52.93,-51.02,-38.5,-49.58,-60.66,-47.05,-55.46,-57.03,-46.33,-40.04,-55.5,-47.61,-44.54,-49.75,-35.27,-40.55,-56.33,-42.35,-46.33,-46.63,-35.81,-38.74,-41.25,-37.32,-43.88,-41.12,-38.3,-38.79,-47.72,-34.08,-41.65,-35.81,-26.92,-43.54,-32.54,-28.13,-44.44,-34.85,-27.13,-39.6,-29.09,-21.88,-40.06,-25.65,-21.56,-37.1,-27.44,-24.27,-32.55,-18.49,-18.22,-33.28,-21.87,-21.53,-29.7,-16.69,-16.86,-30.73,-16.16,-20.27,-27.34,-13.92,-16.26,-26.31,-9.02,-16.08,-24.49,-10.74,-20.76,-20.8,-9.17,-18,-20.01,-6.72,-20.78,-20.52,-8.36,-20.3,-17.76,-6.81,-22.04,-16.41,-8.08,-21.76,-15.77,-9.09,-22.9,-15.95,-8.74,-21.82,-14.73,-10.66,-22.13,-13.92,-10.57,-22.91,-13.5,-12.66,-23.1,-12.05</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B413" t="str">
+        <v>[R_23_标记]</v>
+      </c>
+      <c r="C413" t="str">
+        <v>a: 54.3ms -55.5uv b: 112.8ms 227.5uv</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B414" t="str">
+        <v>[L_23_名字]</v>
+      </c>
+      <c r="C414" t="str">
+        <v>FERG(23)_lCone</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B415" t="str">
+        <v>[L_23_放大器]</v>
+      </c>
+      <c r="C415" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B416" t="str">
+        <v>[L_23_闪光]</v>
+      </c>
+      <c r="C416" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B417" t="str">
+        <v>[L_23_闪光背景]</v>
+      </c>
+      <c r="C417" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B418" t="str">
+        <v>[L_23_采样]</v>
+      </c>
+      <c r="C418" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B419" t="str">
+        <v>[L_23_分析时间]</v>
+      </c>
+      <c r="C419" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B420" t="str">
+        <v>[L_23_数据长度]</v>
+      </c>
+      <c r="C420" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B421" t="str">
+        <v>[L_23_详细数据(uv)]</v>
+      </c>
+      <c r="C421" t="str">
+        <v>13.07,12.42,5.76,15.5,10.16,7.82,16.7,8.15,10.79,16.46,7.04,13.99,14.95,7.22,16.64,12.68,8.75,18.13,10.33,11.28,18.13,8.61,14.21,16.69,8.03,16.78,14.24,8.77,18.32,11.44,10.63,18.41,9.03,13.09,16.99,7.63,15.44,14.4,7.54,16.99,11.25,8.71,17.22,8.3,10.73,15.98,6.24,12.95,13.48,5.5,14.64,10.27,6.16,15.23,7.1,7.89,14.41,4.65,10.15,12.31,3.45,12.07,9.25,3.67,13.1,6.04,5.28,12.65,3.22,7.38,10.91,1.34,8.68,7.88,0.88,10.23,3.4,0.51,8.97,-1.49,1.48,4.77,-5.92,0.84,1.25,-7.03,0.67,-4.97,-10.83,-2.86,-13.6,-14.76,-7.13,-23.7,-14.98,-19.25,-22.7,-22.24,-26.08,-36.11,-29.22,-36.65,-30.69,-24.29,-40.63,-31.2,-36.81,-42.88,-34.09,-36.49,-34.37,-31.35,-26.91,-40.37,-23.59,-26.16,-28.8,-29.54,-37.01,-21.66,-15.51,-24.25,-4.04,-5.07,-6.21,11.83,5.36,6.72,30.56,17.21,32.37,36.66,27.82,42.93,51.82,39.12,66.4,52.54,56.12,81.52,69.35,76.49,91.61,94.27,114.04,104.6,100.53,120.54,125.27,120.69,153.62,129.26,164.36,146.07,139.06,150.23,152.86,189.66,166.88,187.18,196.26,230.42,190.26,183.99,247.33,193.34,225.73,248.68,198.39,226.67,251.19,270.78,228.2,283.16,255.52,282.9,255.62,280.87,273.37,227.08,268.72,300.39,227.82,283.34,285.19,261.02,239.37,280.6,240.64,241.48,252.91,288.57,276.83,228.99,249.2,261.59,226.17,245.37,246.71,250.76,204.09,198.6,186.85,179.34,208.44,193.23,205.84,153.73,163.9,161.48,167.04,176.99,166.19,160.35,150.6,115.4,144.9,139.73,112.65,121.13,106.32,87.88,110.34,78.82,96.87,95.45,72.26,70.63,82.4,61.32,60.84,62.65,47.33,58.91,47.5,46.5,43.55,37.02,41.22,41.44,31.76,37.98,30.37,21.22,31.99,22.06,22.73,23.39,13.51,19.26,20.41,11.34,16.67,14.12,8.92,17.16,8.8,8.87,14.92,4.62,7.93,11.79,2.49,8.59,8.71,0.73,10.68,5.05,1.79,10.11,3.57,2.88,10.55,1.24,5.76,7.83,0.68,7.63,4.1,1.5,10.35,2.46,1.47,8.56,-2.63,2.92,6.54,-0.64,3.41,1.73,-5.2,5.26,-0.36,-5.68,6.18,-4.66,0.67,0.85,-6.59,1.52,0.3,-11.57,4.19,-6.75,-9.51,-3.35,-11.48,-3.7,-4.58,-9.36,-2.89,-3.22,-11.18,-9.26,-10.61,-12.88,-11.89,-12.45,-10.46,-9.54,-23.59,-10.7,-7.21,-25.47,-17.35,-22.36,-17.18,-15.48,-27.03,-16.39,-16.67,-21.85,-25.84,-15.82,-24.17,-23.06,-23.68,-22.52,-22.94,-26.92,-25.56,-12.39,-30.77,-35.39,-18.2,-23.93,-21.99,-27.7,-35.68,-20,-19.44,-34.03,-26.41,-37.79,-32.67,-17.42,-36.55,-37.06,-21.66,-40.89,-19.95,-19.26,-25.29,-21.57,-25.45,-32.77,-20.71,-38.26,-41.45,-31.7,-43.88,-40.51,-36.03,-44.82,-22.48,-44.59,-25.41,-33.51,-34.24,-38.87,-31.17,-42.66,-21.36,-39.46,-48.14,-40.19,-35.01,-35.79,-23.76,-43.11,-28.93,-20.78,-39.25,-24.67,-39.69,-45.23,-35.8,-27.62,-44.69,-33.39,-42.06,-31.24,-25.34,-33.79,-29.89,-20.01,-47.32,-22.72,-41.96,-48.54,-19.92,-32.16,-37.31,-30.17,-27.44,-32.62,-26.67,-43.42,-34.8,-25.58,-33.62,-18.86,-34.25,-28.09,-18.39,-32.61,-24.48,-20.38,-26.07,-33.1,-21.78,-34.67,-30.3,-24.18,-31.74,-13.53,-29.38,-20.95,-12.03,-29.83,-25.25,-19.33,-18.33,-19.96,-19.87,-25.05,-17.51,-18.56,-21.84,-15.89,-16.81,-20.4,-3.04,-22.52,-15.72,-12.82,-17.61,-3.92,-14,-15.11,-5.8,-10.32,-13.97,-2.53,-11.59,-1.65,0.99,-8.91,-0.08,-5.03,-8.76,0.44,-1.89,-8.81,3.07,-8.66,-2.5,4.48,-9.4,3.36,0.65,-7.06,3.38,0.25,-6.94,2.32,-4.01,-0.31,3.36,-5.96,0.24,2.02,-4.97,3.5,-1.54,-5.53,3.76,-1.62,-1.51,6.34</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B422" t="str">
+        <v>[L_23_标记]</v>
+      </c>
+      <c r="C422" t="str">
+        <v>a: 54.2ms -60.5uv b: 113.0ms 145.3uv</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B423" t="str">
+        <v>[R_24_名字]</v>
+      </c>
+      <c r="C423" t="str">
+        <v>FERG(24)_lFlicker</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B424" t="str">
+        <v>[R_24_放大器]</v>
+      </c>
+      <c r="C424" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B425" t="str">
+        <v>[R_24_闪光]</v>
+      </c>
+      <c r="C425" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B426" t="str">
+        <v>[R_24_闪光背景]</v>
+      </c>
+      <c r="C426" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B427" t="str">
+        <v>[R_24_采样]</v>
+      </c>
+      <c r="C427" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B428" t="str">
+        <v>[R_24_分析时间]</v>
+      </c>
+      <c r="C428" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B429" t="str">
+        <v>[R_24_数据长度]</v>
+      </c>
+      <c r="C429" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B430" t="str">
+        <v>[R_24_详细数据(uv)]</v>
+      </c>
+      <c r="C430" t="str">
+        <v>-42.05,-28.58,-32.19,-34.75,-23.09,-13.79,-19.46,-14.45,0.46,1.17,-3.4,6.75,16.43,9.57,16.46,26.68,26.49,21.96,37.36,45.05,36.11,37.44,54.14,42.8,42.06,41.24,52.25,47.69,52.29,52.38,51.31,36.06,50.14,55.8,47.76,47.34,49.34,45.09,43.77,34.29,48.17,29.53,28.2,34.51,38.46,23.07,13.7,14.95,18.42,10.26,9.55,17.27,0.33,-8.33,7.79,-5.2,-11.49,-14.21,-3.71,-16.17,-19.06,-17.17,-11.77,-24.78,-25.4,-14.95,-21.67,-30.33,-24.65,-20.08,-30.9,-30.96,-24.12,-26.33,-35.43,-27.6,-22.42,-34.88,-39.17,-25.9,-33.12,-38.48,-35.54,-28.1,-36.88,-46.46,-36.65,-31.37,-41.65,-46.36,-46.18,-53.25,-64.64,-42.32,-41.89,-58.64,-63.87,-57.88,-59.13,-74.2,-65.03,-57.62,-71.19,-74.01,-56.06,-70.87,-72.69,-68.49,-59.09,-67.86,-77.56,-61.84,-70.75,-76.4,-65.1,-58.08,-65.63,-65.52,-57.68,-54.45,-70.33,-57.99,-50.86,-48.42,-51,-43.97,-36.84,-39.53,-34.22,-19.57,-23.05,-24.92,-13.52,-3.13,-9.35,-5.27,8.85,8.88,2,15.89,20.33,15.29,20.39,29.29,33.87,29.47,37.04,40.08,42.67,33.21,50.81,49.07,49.16,43.98,49.41,45.8,49.5,45.55,49.9,41.51,49.53,54.23,42.63,39.91,41.17,44.17,27.99,32.33,39.63,24.32,25.96,26.43,24.75,16.5,9.92,13.7,10.95,6.36,2.49,8.48,-0.54,-1.4,3.87,1.11,-10.53,-10.78,-4.52,-11.38,-17.74,-13.39,-10.13,-21.39,-25.1,-14.81,-21.07,-30.78,-24.12,-19.28,-29.36,-35.55,-21.54,-30,-38.09,-37.21,-32.06,-35.11,-41.09,-41.54,-43.08,-43.47,-45.27,-42.16,-40.7,-53.24,-44.38,-47.7,-59.3,-65.84,-53.1,-49.8,-67.96,-58.33,-57.67,-67.66,-67.33,-58.96,-69.11,-80.5,-68.62,-65.86,-83.45,-86.95,-68.88,-75.53,-77.69,-81.12,-62.77,-76.09,-83.77,-67.23,-67.88,-77,-69.88,-60.14,-61.91,-59.02,-55.62,-50.66,-55.8,-44.99,-33.18,-34.35,-40.55,-27.66,-18.74,-22.28,-17.86,-4.53,-2.53,-5.33,3.43,14.26,11.58,14.24,23.5,25.81,24.33,36.11,42.02,39.17,36.5,45.81,53.74,47.23,45.16,56.63,50.07,50.35,57.95,54.28,45.19,50.61,58.33,54.1,38.32,50.39,52.42,45.25,42.63,41.82,33.63,25.96,36.37,40.57,29.93,14.4,19.61,26.59,6.02,7.66,16.54,9.9,0.51,-0.6,0.83,-6.01,-10.03,-3.62,-8.3,-20.76,-8.71,-13.24,-19.48,-22.05,-15.92,-23.56,-32.04,-25.77,-20.2,-30.52,-35.11,-24.93,-29.52,-37.45,-35.1,-25.23,-39.52,-42.55,-34.62,-31.3,-42.06,-37.67,-32.15,-42.19,-51.46,-42.25,-33.46,-46.44,-46.33,-45.95,-50.2,-63.1,-55.12,-40.72,-61.56,-60.64,-49.63,-55.28,-71.39,-56.18,-59.8,-69.01,-77.44,-58.47,-62.62,-73.44,-74.26,-65.88,-63.59,-70.27,-63.67,-66.97,-73.99,-74.19,-58.97,-58.62,-73.14,-50.97,-54.29,-61.37,-55.17,-44.38,-45.8,-47.58,-35.4,-34.05,-40.05,-34.49,-20.5,-21.19,-23.32,-12.51,-3.25,-7.21,-5.27,8.69,12.46,5.25,13.53,27.64,20.29,24.26,30.24,36.27,33.39,31.73,50.79,39.59,44.95,44.04,48.85,42.04,40.73,49.54,58.1,40.86,43.79,48.81,39.16,42,48.5,49.33,37.52,43.54,45.67,38.71,31.23,30.92,32.64,23.05,20.86,27.49,16.45,11.73,19.61,9.42,6.75,5.58,9.15,-3.18,-4.41,-2.94,-3.88,-10.71,-15.4,-4.96,-13.43,-20.27,-15.13,-10.33,-23.78,-24.54,-14.89,-19.14,-29.68,-24.39,-16.29,-27.32,-32.7,-22.15,-23.17,-33.06,-27.25,-24.9,-35.53,-43.91,-37.85,-27.26,-43.27,-39.29,-32.9,-47.41,-51.97,-46.2,-40.24,-45.48,-54.6,-50.35,-46.27,-60.77,-56.61,-57.57,-68.78,-59.88,-55.29,-66.76,-72.59,-74.34,-57.03,-80.13,-82.54,-62.25,-67.66,-83.89,-72.58,-65.83,-74.04,-83.08,-67.05,-62.86,-76.52,-64.57,-57.74,-65.68,-70.76,-59.37,-50.74,-57.64,-51.02,-38.68</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B431" t="str">
+        <v>[R_24_标记]</v>
+      </c>
+      <c r="C431" t="str">
+        <v>幅值: 56.1uv 相位: 35.1°</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B432" t="str">
+        <v>[L_24_名字]</v>
+      </c>
+      <c r="C432" t="str">
+        <v>FERG(24)_lFlicker</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B433" t="str">
+        <v>[L_24_放大器]</v>
+      </c>
+      <c r="C433" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B434" t="str">
+        <v>[L_24_闪光]</v>
+      </c>
+      <c r="C434" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B435" t="str">
+        <v>[L_24_闪光背景]</v>
+      </c>
+      <c r="C435" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B436" t="str">
+        <v>[L_24_采样]</v>
+      </c>
+      <c r="C436" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B437" t="str">
+        <v>[L_24_分析时间]</v>
+      </c>
+      <c r="C437" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B438" t="str">
+        <v>[L_24_数据长度]</v>
+      </c>
+      <c r="C438" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B439" t="str">
+        <v>[L_24_详细数据(uv)]</v>
+      </c>
+      <c r="C439" t="str">
+        <v>-22.01,-31.89,-10.63,-15.47,-27.22,-4.5,-4.55,-11.68,-9.23,4.18,-10.99,-6.78,11.86,0.62,-8.7,7.77,9.28,-7.26,5.53,16.48,-0.8,2,17.54,6.43,0.48,19.6,19.44,4.48,18.54,23.99,4.75,9.3,27.37,27.29,16.44,41.75,35.44,18.53,32.3,41.09,29.65,41.26,55.46,37.66,38.44,55.14,43.53,45.04,62.02,67,39.8,51.12,68.52,48.76,56.72,70.31,54.89,49.99,69.04,65.45,47.03,63.79,66.46,47.86,51.63,62.29,45.85,37.76,56.7,46.69,26.13,38.68,42.8,21.74,20.94,34.08,16.51,3.19,18.6,9.27,-9.39,1.74,2.62,-21.58,-17.57,-9.86,-24.26,-30.22,-23.15,-30.91,-50.28,-35.15,-37.29,-54.9,-48.43,-38.5,-57.4,-60.75,-39.56,-52.61,-66.59,-42.61,-50.6,-69.25,-57.45,-42.24,-68.07,-61.55,-45.68,-58.1,-58.69,-34.12,-40.08,-56.64,-45.53,-31.99,-50.01,-43.65,-19.04,-29.71,-39.51,-16.67,-26.2,-36.64,-25.4,-15.98,-37.57,-27.68,-7.39,-24.94,-25.58,-3.73,-12.29,-27.48,-9.53,-6.39,-19.91,-8.59,1.64,-12.95,-15.49,3.19,-5.09,-15.08,3.19,2.12,-12.5,0.86,10.19,-6.24,3.09,16.62,4.92,-0.39,20.81,15.56,3.7,23.39,27.74,10.8,17.37,41.31,32.63,25.81,41.52,36.28,27.58,41.68,56.99,34.24,40.62,60.61,46.77,52.99,73.84,62.8,50.01,78.33,78.68,57.17,72.06,77.22,71.18,63.21,84.16,62.96,56.27,73.29,66.88,56.29,64.27,70.03,44.61,42.27,62.79,40.9,31.75,46.1,36.63,18.98,26.42,30.45,7.9,8.06,18.35,-0.73,-12.44,1.75,-10.4,-29.35,-15.96,-13.84,-39.44,-32.11,-27.28,-44.97,-49.88,-35.09,-45.16,-63.84,-49.36,-46.55,-64.07,-67.88,-48.35,-72.39,-68.68,-57.77,-55.99,-72.24,-62.3,-54.26,-74.88,-64.89,-45.23,-61.06,-68.62,-37.35,-51.46,-57.64,-38.73,-39.61,-60.08,-39.67,-30.81,-37.04,-35.75,-26.91,-25.95,-35.46,-10.62,-25.91,-37.2,-10.37,-3.67,-25.58,-22.44,1.66,-12.93,-19.22,3.93,-4.02,-14.57,2.7,8.4,-8.98,-0.02,14.31,-1.02,-0.54,18.54,9.35,-1.34,16.69,24.28,2.55,18.77,25.53,16.93,13.8,36.73,25.23,9.5,28.27,43.82,21.51,34.4,41.88,22.27,43.57,46.86,41.56,42.5,52.29,54.77,35.8,61.24,65.22,52.15,55.3,75.24,52.76,53.17,72.27,66.63,51.79,63.99,75.57,53.73,57.64,75.72,47.63,50.55,69.69,62.16,46.12,50.21,52.36,34.86,37.7,46.12,23.85,21.59,32.57,21.86,6.2,18.02,12.96,-7.75,0.48,4.21,-17.17,-17.35,-5.51,-25.11,-32.89,-19.84,-27.34,-48.58,-33.22,-32.63,-54.9,-49.67,-39.04,-60.98,-61.19,-49.61,-46.04,-65.38,-55.33,-52.97,-69.28,-59.79,-46.96,-63.15,-55.87,-41.74,-47.6,-55.71,-39.96,-41.94,-58.01,-51.9,-24.44,-50.79,-40.67,-23.33,-33.05,-48.29,-15.73,-24.36,-37.09,-21.52,-12.48,-22.85,-19.76,-2.41,-17.23,-20.96,-4.76,-5.9,-19.97,-7.42,1.9,-15.85,-9.96,5.24,-10.58,-13.68,6.21,-0.55,-12.81,3.22,7.19,-10.16,-0.48,11.31,-4.52,-2.12,15.24,6.64,-4.97,17.55,12.66,1.21,16.51,25.48,14.76,19.32,34.3,22.87,11.88,32.1,39.4,23.31,33.45,40.93,36.48,43.94,62.87,44.02,42.09,62.01,56.96,44.98,60.68,71.14,54.79,62.66,72.48,61.66,51.76,75.29,64.95,50.97,64.21,68.25,55,63.82,67.85,56.79,52.75,60.72,52.29,41.9,47.72,48.25,22.86,35.16,39.63,18.7,13.44,25.89,11.19,-2.72,9.83,4.07,-16.78,-9.92,-4.03,-27.87,-31.1,-13.65,-33.7,-43.91,-26.36,-31.59,-56.13,-46.79,-36.45,-61.25,-59.79,-42.83,-59.04,-71.3,-53.04,-62.55,-66.84,-57.15,-48.96,-73.4,-57.13,-49.3,-56.8,-61.96,-49.64,-55.92,-64.64,-44.1,-41.74,-64.16,-39.35,-41,-53.53,-39.9,-31.05,-36.17,-41.53,-19.38,-19.68</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B440" t="str">
+        <v>[L_24_标记]</v>
+      </c>
+      <c r="C440" t="str">
+        <v>幅值: 55.4uv 相位: 35.7°</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C440"/>
   </ignoredErrors>
 </worksheet>
 </file>